--- a/data/Overall Collection Summary - May 2026.xlsx
+++ b/data/Overall Collection Summary - May 2026.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr updateLinks="always" codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr updateLinks="always" codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://raghavgroup.sharepoint.com/sites/CRM/Shared Documents/General/LAKSHYA TRACKERS MONTHLY/LAKSHYA CRM TRACKER/LAKSHYA CRM Tracker - May'26/Overall Summary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DEFF17-3C96-4DD9-994C-C9C8AA86CC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9943" documentId="8_{AED7C0B6-5B33-4314-A282-567B12F8F8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1960BDF-DBEA-4975-949E-EA98429D7ABA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="917" firstSheet="2" activeTab="2" xr2:uid="{3D2F352B-9E05-401C-B527-666CFC22F994}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="917" activeTab="2" xr2:uid="{3D2F352B-9E05-401C-B527-666CFC22F994}"/>
   </bookViews>
   <sheets>
-    <sheet name="Overall" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="Overall" sheetId="1" r:id="rId1"/>
     <sheet name="Overall - Testing" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="Overall_Draft" sheetId="8" r:id="rId3"/>
     <sheet name="Reporting" sheetId="3" r:id="rId4"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="153">
   <si>
     <t>Overall Summary (Daily)</t>
   </si>
@@ -574,9 +574,6 @@
   <si>
     <t>RAGHAV 
 Ananta</t>
-  </si>
-  <si>
-    <t>e</t>
   </si>
 </sst>
 </file>
@@ -2445,6 +2442,15 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2458,15 +2464,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3150,16 +3147,16 @@
                   <c:v>1.337979</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.4831453238095236</c:v>
+                  <c:v>2.5260024666666663</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.2196234523809526</c:v>
+                  <c:v>2.3628282142857149</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1.8878342857142858</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.701121138095238</c:v>
+                  <c:v>3.8064526714285716</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -3471,16 +3468,16 @@
                         <c:v>0.38077896646428716</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0.41448565895669942</c:v>
+                        <c:v>0.42163935669956537</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.29850201653840408</c:v>
+                        <c:v>0.31776064806918003</c:v>
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>0.26765947829386499</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0.24497300153963639</c:v>
+                        <c:v>0.3452189252037709</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
@@ -3515,7 +3512,7 @@
                           <c:extLst>
                             <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                              <c16:uniqueId val="{00000002-D2CD-4A88-A813-25F37CF1D0C0}"/>
+                              <c16:uniqueId val="{00000002-5B51-40AB-9028-F204091FB0C3}"/>
                             </c:ext>
                           </c:extLst>
                         </c15:dLbl>
@@ -4249,22 +4246,22 @@
                 <c:formatCode>_("₹"* #,##0.00_);_("₹"* \(#,##0.00\);_("₹"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>5.9421200047619047</c:v>
+                  <c:v>6.6289399190476193</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5549061904761905</c:v>
+                  <c:v>0.62403561904761906</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.82428523809523813</c:v>
+                  <c:v>0.78628523809523809</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2.8716789761904766</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.24822390476190476</c:v>
+                  <c:v>0.55087066666666673</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9275055238095238</c:v>
+                  <c:v>2.1603028571428569</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4430,22 +4427,22 @@
                       <c:formatCode>0.00%</c:formatCode>
                       <c:ptCount val="6"/>
                       <c:pt idx="0">
-                        <c:v>0.34730958929797462</c:v>
+                        <c:v>0.38745336663015251</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0.3831657997550435</c:v>
+                        <c:v>0.43090005329157366</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.39629097985347983</c:v>
+                        <c:v>0.37802174908424907</c:v>
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>0.71565110678046417</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>2.6893164112882419E-2</c:v>
+                        <c:v>5.9682629107981222E-2</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0.22864834208891149</c:v>
+                        <c:v>0.25626368412133532</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -7059,16 +7056,16 @@
                   <c:v>1.337979</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.4831453238095236</c:v>
+                  <c:v>2.5260024666666663</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.9911221190476192</c:v>
+                  <c:v>1.9911221190476196</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1.8878342857142858</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.4223353285714286</c:v>
+                  <c:v>3.6017421952380952</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -7380,16 +7377,16 @@
                         <c:v>0.38077896646428716</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0.41714651821240034</c:v>
+                        <c:v>0.42434614030135703</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.27517367712009266</c:v>
+                        <c:v>0.27517367712009277</c:v>
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>0.28808177322484135</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0.23056247643916561</c:v>
+                        <c:v>0.34282066162956709</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
@@ -7424,7 +7421,7 @@
                           <c:extLst>
                             <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                              <c16:uniqueId val="{00000002-25E7-41F8-A756-946390BADF0E}"/>
+                              <c16:uniqueId val="{00000002-F287-4E1C-B845-1A467D1A64F1}"/>
                             </c:ext>
                           </c:extLst>
                         </c15:dLbl>
@@ -8182,22 +8179,22 @@
                 <c:formatCode>_("₹"* #,##0.00_);_("₹"* \(#,##0.00\);_("₹"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>5.9421200047619047</c:v>
+                  <c:v>6.6289399190476193</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.3519880904761905</c:v>
+                  <c:v>1.4211175190476191</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.98451043809523808</c:v>
+                  <c:v>0.94651043809523805</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2.8716789761904766</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.24822390476190476</c:v>
+                  <c:v>0.55087066666666673</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9275055238095238</c:v>
+                  <c:v>2.1603028571428569</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8364,22 +8361,22 @@
                       <c:formatCode>0.00%</c:formatCode>
                       <c:ptCount val="6"/>
                       <c:pt idx="0">
-                        <c:v>0.35204216837542379</c:v>
+                        <c:v>0.39273296083919096</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0.67106477250489904</c:v>
+                        <c:v>0.70537744477210818</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.47332232600732599</c:v>
+                        <c:v>0.45505309523809517</c:v>
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>0.71565110678046417</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>2.6893164112882419E-2</c:v>
+                        <c:v>5.9682629107981222E-2</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0.2241285492801772</c:v>
+                        <c:v>0.25119800664451825</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -17338,6 +17335,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Overall"/>
@@ -17360,12 +17358,12 @@
       <sheetName val="Working Sheet"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6">
         <row r="7">
           <cell r="B7">
@@ -17469,7 +17467,7 @@
             <v>3</v>
           </cell>
           <cell r="F21">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="I21">
             <v>0</v>
@@ -17489,17 +17487,17 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -17510,6 +17508,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Overall"/>
@@ -17529,12 +17528,12 @@
       <sheetName val="Working Sheet"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6">
         <row r="3">
           <cell r="Q3">
@@ -17552,7 +17551,7 @@
             <v>0</v>
           </cell>
           <cell r="E7">
-            <v>2.4831453238095245</v>
+            <v>2.5260024666666676</v>
           </cell>
           <cell r="F7">
             <v>0</v>
@@ -17561,7 +17560,7 @@
             <v>5.9526933952380956</v>
           </cell>
           <cell r="J7">
-            <v>2.4831453238095236</v>
+            <v>2.5260024666666663</v>
           </cell>
           <cell r="L7">
             <v>3.15</v>
@@ -17600,16 +17599,16 @@
             <v>103.07414780000001</v>
           </cell>
           <cell r="D13">
-            <v>100.53227582380951</v>
+            <v>100.57513296666666</v>
           </cell>
           <cell r="E13">
-            <v>3.3030415523809524</v>
+            <v>3.2601844095238097</v>
           </cell>
           <cell r="I13">
             <v>5.9909076952380955</v>
           </cell>
           <cell r="J13">
-            <v>2.4831453238095236</v>
+            <v>2.5260024666666663</v>
           </cell>
           <cell r="L13">
             <v>3.15</v>
@@ -17617,7 +17616,7 @@
         </row>
         <row r="18">
           <cell r="L18">
-            <v>3.2648272523809525</v>
+            <v>3.2219701095238098</v>
           </cell>
         </row>
         <row r="19">
@@ -17647,14 +17646,14 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -17665,6 +17664,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Overall"/>
@@ -17700,16 +17700,16 @@
         </row>
         <row r="7">
           <cell r="B7">
-            <v>76</v>
+            <v>77</v>
           </cell>
           <cell r="D7">
             <v>0</v>
           </cell>
           <cell r="E7">
-            <v>2.2269107523809528</v>
+            <v>2.7321155142857152</v>
           </cell>
           <cell r="F7">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="I7">
             <v>1.6341805</v>
@@ -17726,7 +17726,7 @@
             <v>0.2</v>
           </cell>
           <cell r="J8">
-            <v>0.22850133333333336</v>
+            <v>0.37170609523809517</v>
           </cell>
           <cell r="L8">
             <v>0.2</v>
@@ -17737,7 +17737,7 @@
             <v>1</v>
           </cell>
           <cell r="J9">
-            <v>1.4189999999999999E-2</v>
+            <v>0.1857138095238095</v>
           </cell>
         </row>
         <row r="10">
@@ -17778,16 +17778,16 @@
             <v>49.654334429999999</v>
           </cell>
           <cell r="D13">
-            <v>48.900917852380957</v>
+            <v>49.215646423809524</v>
           </cell>
           <cell r="E13">
-            <v>1.5123963585714286</v>
+            <v>1.4952999300000001</v>
           </cell>
           <cell r="I13">
             <v>7.4358742299999996</v>
           </cell>
           <cell r="J13">
-            <v>2.2196234523809526</v>
+            <v>2.3628282142857149</v>
           </cell>
           <cell r="L13">
             <v>7.03</v>
@@ -17800,15 +17800,15 @@
         </row>
         <row r="19">
           <cell r="L19">
-            <v>1.7096528571428567E-2</v>
+            <v>9.9999999999999995E-8</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>17</v>
+            <v>16</v>
           </cell>
           <cell r="F20">
-            <v>10</v>
+            <v>9</v>
           </cell>
           <cell r="L20">
             <v>0</v>
@@ -17842,6 +17842,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Overall"/>
@@ -17879,10 +17880,10 @@
             <v>54</v>
           </cell>
           <cell r="D7">
-            <v>0.23809523809523811</v>
+            <v>0</v>
           </cell>
           <cell r="E7">
-            <v>2.1198986666666664</v>
+            <v>2.1389462857142854</v>
           </cell>
           <cell r="F7">
             <v>2</v>
@@ -17913,7 +17914,7 @@
             <v>0.7</v>
           </cell>
           <cell r="J9">
-            <v>0.23206438095238097</v>
+            <v>0.251112</v>
           </cell>
         </row>
         <row r="10">
@@ -17954,7 +17955,7 @@
             <v>36.135609299999999</v>
           </cell>
           <cell r="D13">
-            <v>35.67853306666666</v>
+            <v>35.697580685714279</v>
           </cell>
           <cell r="E13">
             <v>1.4995108952380953</v>
@@ -18017,6 +18018,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Overall"/>
@@ -18056,19 +18058,19 @@
             <v>56</v>
           </cell>
           <cell r="D7">
-            <v>0.2628301904761905</v>
+            <v>0</v>
           </cell>
           <cell r="E7">
-            <v>3.1068084714285713</v>
+            <v>3.8064526714285707</v>
           </cell>
           <cell r="F7">
-            <v>1</v>
+            <v>4</v>
           </cell>
           <cell r="I7">
             <v>2.410911</v>
           </cell>
           <cell r="J7">
-            <v>0.81702142380952358</v>
+            <v>1.4609841952380953</v>
           </cell>
           <cell r="L7">
             <v>2.1</v>
@@ -18079,7 +18081,7 @@
             <v>0.52</v>
           </cell>
           <cell r="J8">
-            <v>0.27878580952380949</v>
+            <v>0.20471047619047619</v>
           </cell>
           <cell r="L8">
             <v>0.52</v>
@@ -18090,7 +18092,7 @@
             <v>0.18</v>
           </cell>
           <cell r="J9">
-            <v>0.22857142857142854</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="10">
@@ -18109,7 +18111,7 @@
             <v>2.02</v>
           </cell>
           <cell r="J11">
-            <v>0</v>
+            <v>0.30264676190476192</v>
           </cell>
           <cell r="L11">
             <v>2.02</v>
@@ -18120,7 +18122,7 @@
             <v>4.3600000000000003</v>
           </cell>
           <cell r="J12">
-            <v>0.58587628571428574</v>
+            <v>0.81867361904761904</v>
           </cell>
           <cell r="L12">
             <v>3.49</v>
@@ -18128,19 +18130,19 @@
         </row>
         <row r="13">
           <cell r="C13">
-            <v>29.2764867</v>
+            <v>34.304362699999999</v>
           </cell>
           <cell r="D13">
-            <v>28.113926766666662</v>
+            <v>28.990686871428569</v>
           </cell>
           <cell r="E13">
-            <v>2.9578329428571428</v>
+            <v>6.2245148047619034</v>
           </cell>
           <cell r="I13">
             <v>11.026199300000002</v>
           </cell>
           <cell r="J13">
-            <v>2.701121138095238</v>
+            <v>3.8064526714285716</v>
           </cell>
           <cell r="L13">
             <v>9.84</v>
@@ -18148,20 +18150,20 @@
         </row>
         <row r="18">
           <cell r="L18">
-            <v>1.8667736714285712</v>
+            <v>4.1346330333333334</v>
           </cell>
         </row>
         <row r="19">
           <cell r="L19">
-            <v>0.30473239047619044</v>
+            <v>0.38415322380952377</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>12</v>
+            <v>9</v>
           </cell>
           <cell r="F20">
-            <v>6</v>
+            <v>5</v>
           </cell>
           <cell r="L20">
             <v>0</v>
@@ -18169,12 +18171,12 @@
         </row>
         <row r="21">
           <cell r="L21">
-            <v>0.69585068095238101</v>
+            <v>0.79152638095238093</v>
           </cell>
         </row>
         <row r="22">
           <cell r="L22">
-            <v>9.0476200000000007E-2</v>
+            <v>0.91420216666666665</v>
           </cell>
         </row>
       </sheetData>
@@ -18196,6 +18198,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Overall"/>
@@ -18369,6 +18372,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Overall"/>
@@ -18406,13 +18410,13 @@
             <v>25</v>
           </cell>
           <cell r="D7">
-            <v>7.1428571428571438E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E7">
             <v>1.2641908285714285</v>
           </cell>
           <cell r="F7">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="I7">
             <v>1.54</v>
@@ -18472,13 +18476,13 @@
         </row>
         <row r="13">
           <cell r="C13">
-            <v>20.2332444</v>
+            <v>24.316816500000002</v>
           </cell>
           <cell r="D13">
             <v>19.54784562857143</v>
           </cell>
           <cell r="E13">
-            <v>1.8083477666666665</v>
+            <v>4.8549033190476196</v>
           </cell>
           <cell r="I13">
             <v>4.9799999999999995</v>
@@ -18495,7 +18499,7 @@
         </row>
         <row r="18">
           <cell r="L18">
-            <v>1.783109619047619</v>
+            <v>4.8191245476190474</v>
           </cell>
         </row>
         <row r="19">
@@ -18505,13 +18509,13 @@
         </row>
         <row r="20">
           <cell r="D20">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="F20">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="L20">
-            <v>2.5238147619047597E-2</v>
+            <v>3.5778771428571408E-2</v>
           </cell>
         </row>
         <row r="21">
@@ -18537,6 +18541,9 @@
 <file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Overall"/>
       <sheetName val="Summary"/>
@@ -18658,6 +18665,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19028,7 +19039,7 @@
       <c r="H1" s="97"/>
       <c r="I1" s="98">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="L1" s="110"/>
       <c r="M1" s="110" t="s">
@@ -19057,16 +19068,16 @@
     <row r="3" spans="2:32" ht="134.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="100" t="str">
         <f>CONCATENATE("₹ ",ROUND($N$27,2)," / ",ROUND($M$27,2)," (",ROUND($O$27,3)*100,"%)")</f>
-        <v>₹ 11.54 / 40.23 (28.7%)</v>
+        <v>₹ 12.84 / 40.23 (31.9%)</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="85" t="str">
-        <f>CONCATENATE("₹ ",ROUND($N$11,2), "  |  ", "₹ ",ROUND($O$11,2))</f>
-        <v>₹ 0.57  |  ₹ 12.54</v>
+        <f ca="1">CONCATENATE("₹ ",ROUND($N$11,2), "  |  ", "₹ ",ROUND($O$11,2))</f>
+        <v>₹ 0  |  ₹ 13.81</v>
       </c>
       <c r="G3" s="242" t="str">
-        <f>CONCATENATE($U$11, "    |    ", $T$11)</f>
-        <v>22    |    43</v>
+        <f ca="1">CONCATENATE($U$11, "    |    ", $T$11)</f>
+        <v>20    |    38</v>
       </c>
       <c r="H3" s="243"/>
       <c r="I3" s="244"/>
@@ -19162,7 +19173,7 @@
       </c>
       <c r="U4" s="69">
         <f>'[1]Project Summary'!$F$21</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V4" s="69">
         <f>'[1]Project Summary'!$Q$3</f>
@@ -19193,7 +19204,7 @@
       </c>
       <c r="O5" s="102">
         <f>'[2]Project Summary'!$E$7</f>
-        <v>2.4831453238095245</v>
+        <v>2.5260024666666676</v>
       </c>
       <c r="P5" s="105">
         <f>'[2]Project Summary'!$F$7</f>
@@ -19205,11 +19216,11 @@
       </c>
       <c r="R5" s="82">
         <f>'[2]Project Summary'!$D$13</f>
-        <v>100.53227582380951</v>
+        <v>100.57513296666666</v>
       </c>
       <c r="S5" s="82">
         <f>'[2]Project Summary'!$E$13</f>
-        <v>3.3030415523809524</v>
+        <v>3.2601844095238097</v>
       </c>
       <c r="T5" s="69">
         <f>'[2]Project Summary'!$D$20</f>
@@ -19239,7 +19250,7 @@
     <row r="6" spans="2:32" ht="135" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="84">
         <f>$S$11</f>
-        <v>13.569449115714285</v>
+        <v>19.822732958571429</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="9"/>
@@ -19249,7 +19260,7 @@
       </c>
       <c r="G6" s="248" t="str">
         <f>CONCATENATE($P$11," / ",V11)</f>
-        <v>3 / 15</v>
+        <v>9 / 15</v>
       </c>
       <c r="H6" s="249"/>
       <c r="I6" s="250"/>
@@ -19258,19 +19269,19 @@
       </c>
       <c r="M6" s="69">
         <f>'[3]Project Summary'!$B$7</f>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N6" s="102">
-        <f>'[3]Project Summary'!$D$7</f>
+        <f ca="1">'[3]Project Summary'!$D$7</f>
         <v>0</v>
       </c>
       <c r="O6" s="102">
         <f>'[3]Project Summary'!$E$7</f>
-        <v>2.2269107523809528</v>
+        <v>2.7321155142857152</v>
       </c>
       <c r="P6" s="105">
         <f>'[3]Project Summary'!$F$7</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="82">
         <f>'[3]Project Summary'!$C$13</f>
@@ -19278,19 +19289,19 @@
       </c>
       <c r="R6" s="82">
         <f>'[3]Project Summary'!$D$13</f>
-        <v>48.900917852380957</v>
+        <v>49.215646423809524</v>
       </c>
       <c r="S6" s="82">
         <f>'[3]Project Summary'!$E$13</f>
-        <v>1.5123963585714286</v>
+        <v>1.4952999300000001</v>
       </c>
       <c r="T6" s="69">
         <f>'[3]Project Summary'!$D$20</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U6" s="69">
-        <f>'[3]Project Summary'!$F$20</f>
-        <v>10</v>
+        <f ca="1">'[3]Project Summary'!$F$20</f>
+        <v>9</v>
       </c>
       <c r="V6" s="69">
         <f>'[3]Project Summary'!$Q$3</f>
@@ -19328,12 +19339,12 @@
         <v>54</v>
       </c>
       <c r="N7" s="102">
-        <f>'[4]Project Summary'!$D$7</f>
-        <v>0.23809523809523811</v>
+        <f ca="1">'[4]Project Summary'!$D$7</f>
+        <v>0</v>
       </c>
       <c r="O7" s="102">
         <f>'[4]Project Summary'!$E$7</f>
-        <v>2.1198986666666664</v>
+        <v>2.1389462857142854</v>
       </c>
       <c r="P7" s="105">
         <f>'[4]Project Summary'!$F$7</f>
@@ -19345,7 +19356,7 @@
       </c>
       <c r="R7" s="82">
         <f>'[4]Project Summary'!$D$13</f>
-        <v>35.67853306666666</v>
+        <v>35.697580685714279</v>
       </c>
       <c r="S7" s="82">
         <f>'[4]Project Summary'!$E$13</f>
@@ -19356,7 +19367,7 @@
         <v>5</v>
       </c>
       <c r="U7" s="69">
-        <f>'[4]Project Summary'!$F$20</f>
+        <f ca="1">'[4]Project Summary'!$F$20</f>
         <v>1</v>
       </c>
       <c r="V7" s="69">
@@ -19383,36 +19394,36 @@
         <v>56</v>
       </c>
       <c r="N8" s="102">
-        <f>'[5]Project Summary'!$D$7</f>
-        <v>0.2628301904761905</v>
+        <f ca="1">'[5]Project Summary'!$D$7</f>
+        <v>0</v>
       </c>
       <c r="O8" s="102">
         <f>'[5]Project Summary'!$E$7</f>
-        <v>3.1068084714285713</v>
+        <v>3.8064526714285707</v>
       </c>
       <c r="P8" s="105">
         <f>'[5]Project Summary'!$F$7</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="82">
         <f>'[5]Project Summary'!$C$13</f>
-        <v>29.2764867</v>
+        <v>34.304362699999999</v>
       </c>
       <c r="R8" s="82">
         <f>'[5]Project Summary'!$D$13</f>
-        <v>28.113926766666662</v>
+        <v>28.990686871428569</v>
       </c>
       <c r="S8" s="82">
         <f>'[5]Project Summary'!$E$13</f>
-        <v>2.9578329428571428</v>
+        <v>6.2245148047619034</v>
       </c>
       <c r="T8" s="69">
         <f>'[5]Project Summary'!$D$20</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="U8" s="69">
-        <f>'[5]Project Summary'!$F$20</f>
-        <v>6</v>
+        <f ca="1">'[5]Project Summary'!$F$20</f>
+        <v>5</v>
       </c>
       <c r="V8" s="69">
         <f>'[5]Project Summary'!$Q$3</f>
@@ -19490,8 +19501,8 @@
         <v>25</v>
       </c>
       <c r="N10" s="102">
-        <f>'[7]Project Summary'!$D$7</f>
-        <v>7.1428571428571438E-2</v>
+        <f ca="1">'[7]Project Summary'!$D$7</f>
+        <v>0</v>
       </c>
       <c r="O10" s="103">
         <f>'[7]Project Summary'!$E$7</f>
@@ -19499,11 +19510,11 @@
       </c>
       <c r="P10" s="106">
         <f>'[7]Project Summary'!$F$7</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="82">
         <f>'[7]Project Summary'!$C$13</f>
-        <v>20.2332444</v>
+        <v>24.316816500000002</v>
       </c>
       <c r="R10" s="82">
         <f>'[7]Project Summary'!$D$13</f>
@@ -19511,15 +19522,15 @@
       </c>
       <c r="S10" s="82">
         <f>'[7]Project Summary'!$E$13</f>
-        <v>1.8083477666666665</v>
+        <v>4.8549033190476196</v>
       </c>
       <c r="T10" s="69">
         <f>'[7]Project Summary'!$D$20</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U10" s="69">
-        <f>'[7]Project Summary'!$F$20</f>
-        <v>2</v>
+        <f ca="1">'[7]Project Summary'!$F$20</f>
+        <v>1</v>
       </c>
       <c r="V10" s="69">
         <f>'[7]Project Summary'!$Q$3</f>
@@ -19541,39 +19552,39 @@
       </c>
       <c r="M11" s="117">
         <f>SUM(M4:M10)</f>
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N11" s="118">
-        <f t="shared" ref="N11:W11" si="0">SUM(N4:N10)</f>
-        <v>0.57235400000000003</v>
+        <f t="shared" ref="N11:W11" ca="1" si="0">SUM(N4:N10)</f>
+        <v>0</v>
       </c>
       <c r="O11" s="118">
         <f>SUM(O4:O10)</f>
-        <v>12.538933042857142</v>
+        <v>13.805686766666668</v>
       </c>
       <c r="P11" s="119">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q11" s="120">
         <f t="shared" si="0"/>
-        <v>525.32953553000004</v>
+        <v>534.44098363000001</v>
       </c>
       <c r="R11" s="120">
         <f t="shared" si="0"/>
-        <v>518.09850223809519</v>
+        <v>519.35189567619045</v>
       </c>
       <c r="S11" s="120">
         <f t="shared" si="0"/>
-        <v>13.569449115714285</v>
+        <v>19.822732958571429</v>
       </c>
       <c r="T11" s="121">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="U11" s="121">
-        <f t="shared" si="0"/>
-        <v>22</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
       </c>
       <c r="V11" s="121">
         <f t="shared" si="0"/>
@@ -19701,11 +19712,11 @@
       </c>
       <c r="U20" s="64">
         <f>N43</f>
-        <v>5.9421200047619047</v>
+        <v>6.6289399190476193</v>
       </c>
       <c r="V20" s="88">
         <f>O43</f>
-        <v>0.34730958929797462</v>
+        <v>0.38745336663015251</v>
       </c>
       <c r="W20" s="64">
         <f>P43</f>
@@ -19727,11 +19738,11 @@
       </c>
       <c r="N21" s="18">
         <f>'[2]Project Summary'!$J$13</f>
-        <v>2.4831453238095236</v>
+        <v>2.5260024666666663</v>
       </c>
       <c r="O21" s="19">
         <f t="shared" si="1"/>
-        <v>0.41448565895669942</v>
+        <v>0.42163935669956537</v>
       </c>
       <c r="P21" s="18">
         <f>'[2]Project Summary'!$L$13</f>
@@ -19739,7 +19750,7 @@
       </c>
       <c r="Q21" s="153">
         <f t="shared" ref="Q21:Q27" si="2">M21-N21</f>
-        <v>3.5077623714285719</v>
+        <v>3.4649052285714292</v>
       </c>
       <c r="S21" s="65" t="s">
         <v>43</v>
@@ -19750,11 +19761,11 @@
       </c>
       <c r="U21" s="64">
         <f>R43</f>
-        <v>0.5549061904761905</v>
+        <v>0.62403561904761906</v>
       </c>
       <c r="V21" s="88">
         <f>S43</f>
-        <v>0.3831657997550435</v>
+        <v>0.43090005329157366</v>
       </c>
       <c r="W21" s="64">
         <f>T43</f>
@@ -19776,11 +19787,11 @@
       </c>
       <c r="N22" s="18">
         <f>'[3]Project Summary'!$J$13</f>
-        <v>2.2196234523809526</v>
+        <v>2.3628282142857149</v>
       </c>
       <c r="O22" s="19">
         <f t="shared" si="1"/>
-        <v>0.29850201653840408</v>
+        <v>0.31776064806918003</v>
       </c>
       <c r="P22" s="18">
         <f>'[3]Project Summary'!$L$13</f>
@@ -19788,7 +19799,7 @@
       </c>
       <c r="Q22" s="153">
         <f t="shared" si="2"/>
-        <v>5.216250777619047</v>
+        <v>5.0730460157142847</v>
       </c>
       <c r="S22" s="65" t="s">
         <v>45</v>
@@ -19799,11 +19810,11 @@
       </c>
       <c r="U22" s="64">
         <f>V43</f>
-        <v>0.82428523809523813</v>
+        <v>0.78628523809523809</v>
       </c>
       <c r="V22" s="88">
         <f>W43</f>
-        <v>0.39629097985347983</v>
+        <v>0.37802174908424907</v>
       </c>
       <c r="W22" s="64">
         <f>X43</f>
@@ -19877,11 +19888,11 @@
       </c>
       <c r="N24" s="18">
         <f>'[5]Project Summary'!$J$13</f>
-        <v>2.701121138095238</v>
+        <v>3.8064526714285716</v>
       </c>
       <c r="O24" s="19">
         <f>N24/M24</f>
-        <v>0.24497300153963639</v>
+        <v>0.3452189252037709</v>
       </c>
       <c r="P24" s="18">
         <f>'[5]Project Summary'!$L$13</f>
@@ -19903,11 +19914,11 @@
       </c>
       <c r="U24" s="64">
         <f>AD43</f>
-        <v>0.24822390476190476</v>
+        <v>0.55087066666666673</v>
       </c>
       <c r="V24" s="88">
         <f>AE43</f>
-        <v>2.6893164112882419E-2</v>
+        <v>5.9682629107981222E-2</v>
       </c>
       <c r="W24" s="64">
         <f>AF43</f>
@@ -19952,11 +19963,11 @@
       </c>
       <c r="U25" s="64">
         <f>AH43</f>
-        <v>1.9275055238095238</v>
+        <v>2.1603028571428569</v>
       </c>
       <c r="V25" s="88">
         <f>AI43</f>
-        <v>0.22864834208891149</v>
+        <v>0.25626368412133532</v>
       </c>
       <c r="W25" s="64">
         <f>AJ43</f>
@@ -20004,11 +20015,11 @@
       </c>
       <c r="N27" s="18">
         <f>SUM(N20:N26)</f>
-        <v>11.544434599999999</v>
+        <v>12.835828038095237</v>
       </c>
       <c r="O27" s="19">
         <f>N27/M27</f>
-        <v>0.28696158824330709</v>
+        <v>0.31906193138551642</v>
       </c>
       <c r="P27" s="18">
         <f>SUM(P20:P26)</f>
@@ -20016,7 +20027,7 @@
       </c>
       <c r="Q27" s="153">
         <f t="shared" si="2"/>
-        <v>28.685460525238089</v>
+        <v>27.394067087142851</v>
       </c>
       <c r="AF27" s="1"/>
     </row>
@@ -20085,8 +20096,8 @@
       <c r="AA34" s="231"/>
       <c r="AB34" s="235"/>
       <c r="AC34" s="230" t="str">
-        <f>CONCATENATE("Expected Registrations in August ",$D$3,"'",$E$3," ")</f>
-        <v xml:space="preserve">Expected Registrations in August '₹ 0.57  |  ₹ 12.54 </v>
+        <f ca="1">CONCATENATE("Expected Registrations in August ",$D$3,"'",$E$3," ")</f>
+        <v xml:space="preserve">Expected Registrations in August '₹ 0  |  ₹ 13.81 </v>
       </c>
       <c r="AD34" s="231"/>
       <c r="AE34" s="231"/>
@@ -20293,11 +20304,11 @@
       </c>
       <c r="N37" s="63">
         <f>'[2]Project Summary'!$J$7</f>
-        <v>2.4831453238095236</v>
+        <v>2.5260024666666663</v>
       </c>
       <c r="O37" s="88">
         <f t="shared" si="4"/>
-        <v>0.41714651821240034</v>
+        <v>0.42434614030135703</v>
       </c>
       <c r="P37" s="146">
         <f>'[2]Project Summary'!$L$7</f>
@@ -20417,11 +20428,11 @@
       </c>
       <c r="R38" s="63">
         <f>'[3]Project Summary'!$J$8</f>
-        <v>0.22850133333333336</v>
+        <v>0.37170609523809517</v>
       </c>
       <c r="S38" s="88">
         <f t="shared" si="5"/>
-        <v>1.1425066666666668</v>
+        <v>1.8585304761904757</v>
       </c>
       <c r="T38" s="124">
         <f>'[3]Project Summary'!$L$8</f>
@@ -20433,11 +20444,11 @@
       </c>
       <c r="V38" s="63">
         <f>'[3]Project Summary'!$J$9</f>
-        <v>1.4189999999999999E-2</v>
+        <v>0.1857138095238095</v>
       </c>
       <c r="W38" s="88">
         <f t="shared" si="6"/>
-        <v>1.4189999999999999E-2</v>
+        <v>0.1857138095238095</v>
       </c>
       <c r="X38" s="146">
         <f>'[3]Project Summary'!$L$9</f>
@@ -20537,11 +20548,11 @@
       </c>
       <c r="V39" s="63">
         <f>'[4]Project Summary'!$J$9</f>
-        <v>0.23206438095238097</v>
+        <v>0.251112</v>
       </c>
       <c r="W39" s="88">
         <f t="shared" si="6"/>
-        <v>0.33152054421768712</v>
+        <v>0.35873142857142859</v>
       </c>
       <c r="X39" s="146">
         <f>'[4]Project Summary'!$L$9</f>
@@ -20609,11 +20620,11 @@
       </c>
       <c r="N40" s="63">
         <f>'[5]Project Summary'!$J$7</f>
-        <v>0.81702142380952358</v>
+        <v>1.4609841952380953</v>
       </c>
       <c r="O40" s="88">
         <f t="shared" si="4"/>
-        <v>0.33888493760637517</v>
+        <v>0.60598843973837913</v>
       </c>
       <c r="P40" s="146">
         <f>'[5]Project Summary'!$L$7</f>
@@ -20625,11 +20636,11 @@
       </c>
       <c r="R40" s="63">
         <f>'[5]Project Summary'!$J$8</f>
-        <v>0.27878580952380949</v>
+        <v>0.20471047619047619</v>
       </c>
       <c r="S40" s="88">
         <f t="shared" si="5"/>
-        <v>0.53612655677655674</v>
+        <v>0.39367399267399267</v>
       </c>
       <c r="T40" s="124">
         <f>'[5]Project Summary'!$L$8</f>
@@ -20641,11 +20652,11 @@
       </c>
       <c r="V40" s="63">
         <f>'[5]Project Summary'!$J$9</f>
-        <v>0.22857142857142854</v>
+        <v>0</v>
       </c>
       <c r="W40" s="88">
         <f t="shared" si="6"/>
-        <v>1.2698412698412698</v>
+        <v>0</v>
       </c>
       <c r="X40" s="146">
         <f>'[5]Project Summary'!$L$9</f>
@@ -20673,11 +20684,11 @@
       </c>
       <c r="AD40" s="63">
         <f>'[5]Project Summary'!$J$11</f>
-        <v>0</v>
+        <v>0.30264676190476192</v>
       </c>
       <c r="AE40" s="88">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>0.14982512965582273</v>
       </c>
       <c r="AF40" s="146">
         <f>'[5]Project Summary'!$L$11</f>
@@ -20689,11 +20700,11 @@
       </c>
       <c r="AH40" s="63">
         <f>'[5]Project Summary'!$J$12</f>
-        <v>0.58587628571428574</v>
+        <v>0.81867361904761904</v>
       </c>
       <c r="AI40" s="88">
         <f t="shared" si="7"/>
-        <v>0.13437529488859765</v>
+        <v>0.18776917868064655</v>
       </c>
       <c r="AJ40" s="124">
         <f>'[5]Project Summary'!$L$12</f>
@@ -20921,11 +20932,11 @@
       </c>
       <c r="N43" s="125">
         <f>SUM(N36:N42)</f>
-        <v>5.9421200047619047</v>
+        <v>6.6289399190476193</v>
       </c>
       <c r="O43" s="126">
         <f>N43/M43</f>
-        <v>0.34730958929797462</v>
+        <v>0.38745336663015251</v>
       </c>
       <c r="P43" s="147">
         <f>SUM(P36:P42)</f>
@@ -20937,11 +20948,11 @@
       </c>
       <c r="R43" s="125">
         <f>SUM(R36:R42)</f>
-        <v>0.5549061904761905</v>
+        <v>0.62403561904761906</v>
       </c>
       <c r="S43" s="126">
         <f>R43/Q43</f>
-        <v>0.3831657997550435</v>
+        <v>0.43090005329157366</v>
       </c>
       <c r="T43" s="127">
         <f>SUM(T36:T42)</f>
@@ -20953,11 +20964,11 @@
       </c>
       <c r="V43" s="125">
         <f>SUM(V36:V42)</f>
-        <v>0.82428523809523813</v>
+        <v>0.78628523809523809</v>
       </c>
       <c r="W43" s="126">
         <f>V43/U43</f>
-        <v>0.39629097985347983</v>
+        <v>0.37802174908424907</v>
       </c>
       <c r="X43" s="147">
         <f>SUM(X36:X42)</f>
@@ -20985,11 +20996,11 @@
       </c>
       <c r="AD43" s="125">
         <f>SUM(AD36:AD42)</f>
-        <v>0.24822390476190476</v>
+        <v>0.55087066666666673</v>
       </c>
       <c r="AE43" s="126">
         <f>AD43/AC43</f>
-        <v>2.6893164112882419E-2</v>
+        <v>5.9682629107981222E-2</v>
       </c>
       <c r="AF43" s="147">
         <f>SUM(AF36:AF42)</f>
@@ -21001,11 +21012,11 @@
       </c>
       <c r="AH43" s="125">
         <f>SUM(AH36:AH42)</f>
-        <v>1.9275055238095238</v>
+        <v>2.1603028571428569</v>
       </c>
       <c r="AI43" s="126">
         <f>AH43/AG43</f>
-        <v>0.22864834208891149</v>
+        <v>0.25626368412133532</v>
       </c>
       <c r="AJ43" s="127">
         <f>SUM(AJ36:AJ42)</f>
@@ -21051,7 +21062,7 @@
       </c>
       <c r="R45" s="112">
         <f>N27-R43</f>
-        <v>10.989528409523809</v>
+        <v>12.211792419047617</v>
       </c>
       <c r="S45" s="113"/>
       <c r="T45" s="112"/>
@@ -21200,7 +21211,7 @@
       </c>
       <c r="X53" s="169">
         <f>'[2]Project Summary'!$L$18</f>
-        <v>3.2648272523809525</v>
+        <v>3.2219701095238098</v>
       </c>
       <c r="Y53" s="169">
         <f>'[3]Project Summary'!$L$18</f>
@@ -21212,18 +21223,18 @@
       </c>
       <c r="AA53" s="169">
         <f>'[5]Project Summary'!$L$18</f>
-        <v>1.8667736714285712</v>
+        <v>4.1346330333333334</v>
       </c>
       <c r="AB53" s="169">
         <v>0.23</v>
       </c>
       <c r="AC53" s="169">
         <f>'[7]Project Summary'!$L$18</f>
-        <v>1.783109619047619</v>
+        <v>4.8191245476190474</v>
       </c>
       <c r="AD53" s="169">
         <f>SUM(W53:AC53)</f>
-        <v>11.838813595238097</v>
+        <v>17.099830742857144</v>
       </c>
     </row>
     <row r="54" spans="12:30" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -21256,7 +21267,7 @@
       </c>
       <c r="Y54" s="169">
         <f>'[3]Project Summary'!$L$19</f>
-        <v>1.7096528571428567E-2</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="Z54" s="169">
         <f>'[4]Project Summary'!$L$19</f>
@@ -21264,7 +21275,7 @@
       </c>
       <c r="AA54" s="169">
         <f>'[5]Project Summary'!$L$19</f>
-        <v>0.30473239047619044</v>
+        <v>0.38415322380952377</v>
       </c>
       <c r="AB54" s="169"/>
       <c r="AC54" s="169">
@@ -21273,7 +21284,7 @@
       </c>
       <c r="AD54" s="169">
         <f>SUM(W54:AC54)</f>
-        <v>0.36004321904761899</v>
+        <v>0.42236762380952375</v>
       </c>
     </row>
     <row r="55" spans="12:30" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -21319,11 +21330,11 @@
       <c r="AB55" s="169"/>
       <c r="AC55" s="169">
         <f>'[7]Project Summary'!$L$20</f>
-        <v>2.5238147619047597E-2</v>
+        <v>3.5778771428571408E-2</v>
       </c>
       <c r="AD55" s="169">
         <f>SUM(W55:AC55)</f>
-        <v>0.1226975333333333</v>
+        <v>0.13323815714285711</v>
       </c>
     </row>
     <row r="56" spans="12:30" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -21367,7 +21378,7 @@
       </c>
       <c r="AA56" s="169">
         <f>'[5]Project Summary'!$L$21</f>
-        <v>0.69585068095238101</v>
+        <v>0.79152638095238093</v>
       </c>
       <c r="AB56" s="169"/>
       <c r="AC56" s="169">
@@ -21376,7 +21387,7 @@
       </c>
       <c r="AD56" s="169">
         <f>SUM(W56:AC56)</f>
-        <v>1.141548872857143</v>
+        <v>1.2372245728571429</v>
       </c>
     </row>
     <row r="57" spans="12:30" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -21420,7 +21431,7 @@
       </c>
       <c r="AA57" s="169">
         <f>'[5]Project Summary'!$L$22</f>
-        <v>9.0476200000000007E-2</v>
+        <v>0.91420216666666665</v>
       </c>
       <c r="AB57" s="169"/>
       <c r="AC57" s="169">
@@ -21429,7 +21440,7 @@
       </c>
       <c r="AD57" s="169">
         <f>SUM(W57:AC57)</f>
-        <v>0.10749029523809524</v>
+        <v>0.93121626190476192</v>
       </c>
     </row>
     <row r="58" spans="12:30" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -21458,11 +21469,11 @@
       </c>
       <c r="X58" s="167">
         <f t="shared" si="11"/>
-        <v>3.3030415523809524</v>
+        <v>3.2601844095238097</v>
       </c>
       <c r="Y58" s="167">
         <f t="shared" si="11"/>
-        <v>1.5123963585714286</v>
+        <v>1.4952999300000001</v>
       </c>
       <c r="Z58" s="167">
         <f t="shared" si="11"/>
@@ -21470,7 +21481,7 @@
       </c>
       <c r="AA58" s="167">
         <f t="shared" si="11"/>
-        <v>2.9578329428571428</v>
+        <v>6.2245148047619043</v>
       </c>
       <c r="AB58" s="167">
         <f t="shared" si="11"/>
@@ -21478,11 +21489,11 @@
       </c>
       <c r="AC58" s="167">
         <f t="shared" si="11"/>
-        <v>1.8083477666666665</v>
+        <v>4.8549033190476187</v>
       </c>
       <c r="AD58" s="167">
         <f t="shared" si="11"/>
-        <v>13.570593515714288</v>
+        <v>19.82387735857143</v>
       </c>
     </row>
     <row r="59" spans="12:30" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -21539,13 +21550,6 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="16">
-    <mergeCell ref="S18:V18"/>
-    <mergeCell ref="M34:P34"/>
-    <mergeCell ref="AG34:AJ34"/>
-    <mergeCell ref="AC34:AF34"/>
-    <mergeCell ref="Y34:AB34"/>
-    <mergeCell ref="U34:X34"/>
-    <mergeCell ref="Q34:T34"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="L18:O18"/>
     <mergeCell ref="L52:Q52"/>
@@ -21555,6 +21559,13 @@
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="G7:I7"/>
+    <mergeCell ref="S18:V18"/>
+    <mergeCell ref="M34:P34"/>
+    <mergeCell ref="AG34:AJ34"/>
+    <mergeCell ref="AC34:AF34"/>
+    <mergeCell ref="Y34:AB34"/>
+    <mergeCell ref="U34:X34"/>
+    <mergeCell ref="Q34:T34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -21607,20 +21618,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:36" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="252" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="252"/>
-      <c r="D1" s="252"/>
-      <c r="E1" s="252"/>
-      <c r="F1" s="252"/>
+      <c r="B1" s="255" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="255"/>
+      <c r="D1" s="255"/>
+      <c r="E1" s="255"/>
+      <c r="F1" s="255"/>
       <c r="H1" s="37" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="35"/>
       <c r="J1" s="36">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="Q1" s="233" t="s">
         <v>77</v>
@@ -21630,19 +21641,19 @@
       <c r="T1" s="233"/>
     </row>
     <row r="2" spans="2:36" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="253" t="s">
+      <c r="B2" s="256" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="253"/>
-      <c r="D2" s="253"/>
-      <c r="E2" s="253"/>
-      <c r="F2" s="253"/>
+      <c r="C2" s="256"/>
+      <c r="D2" s="256"/>
+      <c r="E2" s="256"/>
+      <c r="F2" s="256"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="253" t="s">
+      <c r="H2" s="256" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="253"/>
-      <c r="J2" s="253"/>
+      <c r="I2" s="256"/>
+      <c r="J2" s="256"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
@@ -21662,12 +21673,12 @@
         <f>$S$9</f>
         <v>0</v>
       </c>
-      <c r="H3" s="254" t="str">
+      <c r="H3" s="257" t="str">
         <f>CONCATENATE($Z$9, " / ", $Y$9)</f>
         <v>9 / 17</v>
       </c>
-      <c r="I3" s="255"/>
-      <c r="J3" s="256"/>
+      <c r="I3" s="258"/>
+      <c r="J3" s="259"/>
       <c r="L3" s="5">
         <v>8</v>
       </c>
@@ -21808,12 +21819,12 @@
         <f>$W$19</f>
         <v>6.6640613999999996</v>
       </c>
-      <c r="H6" s="257" t="str">
+      <c r="H6" s="252" t="str">
         <f>CONCATENATE($U$9," / ",AA9)</f>
         <v>17 / 20</v>
       </c>
-      <c r="I6" s="258"/>
-      <c r="J6" s="259"/>
+      <c r="I6" s="253"/>
+      <c r="J6" s="254"/>
       <c r="L6" s="10"/>
       <c r="Q6" s="11" t="s">
         <v>86</v>
@@ -22582,17 +22593,17 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="11">
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="Q12:T12"/>
-    <mergeCell ref="V12:AA12"/>
-    <mergeCell ref="Q23:T23"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="Q1:T1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="H3:J3"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="Q12:T12"/>
+    <mergeCell ref="V12:AA12"/>
+    <mergeCell ref="Q23:T23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -22651,12 +22662,10 @@
       </c>
       <c r="I1" s="98">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="K1" s="170"/>
-      <c r="L1" s="110" t="s">
-        <v>153</v>
-      </c>
+      <c r="L1" s="110"/>
       <c r="M1" s="110"/>
       <c r="N1" s="110"/>
       <c r="O1" s="110"/>
@@ -22687,21 +22696,21 @@
     <row r="3" spans="2:32" ht="134.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="237" t="str">
         <f>CONCATENATE("₹ ",ROUND($N$27,2)," / ",ROUND($M$27,2)," (",ROUND($O$27,3)*100,"%)")</f>
-        <v>₹ 10.99 / 38.72 (28.4%)</v>
+        <v>₹ 12.21 / 38.72 (31.5%)</v>
       </c>
       <c r="C3" s="238"/>
       <c r="D3" s="239"/>
       <c r="F3" s="161" t="str">
         <f>CONCATENATE("₹ ", ROUND($U$21,2), "  /  ", "₹ ", ROUND($T$21,2))</f>
-        <v>₹ 1.35  /  ₹ 2.01</v>
+        <v>₹ 1.42  /  ₹ 2.01</v>
       </c>
       <c r="G3" s="160" t="str">
         <f>CONCATENATE("₹ ", ROUND($U$22,2), "  /  ", "₹ ", ROUND($T$22,2))</f>
-        <v>₹ 0.98  /  ₹ 2.08</v>
+        <v>₹ 0.95  /  ₹ 2.08</v>
       </c>
       <c r="I3" s="85" t="str">
-        <f>CONCATENATE("₹ ",ROUND($N$11,2), "  |  ", "₹ ",ROUND($O$11,2))</f>
-        <v>₹ 0.57  |  ₹ 13.5</v>
+        <f ca="1">CONCATENATE("₹ ",ROUND($N$11,2), "  |  ", "₹ ",ROUND($O$11,2))</f>
+        <v>₹ 0  |  ₹ 14.76</v>
       </c>
       <c r="L3" s="114" t="s">
         <v>5</v>
@@ -22796,7 +22805,7 @@
       </c>
       <c r="U4" s="69">
         <f>'[1]Project Summary'!$F$21</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V4" s="69">
         <f>'[1]Project Summary'!$Q$3</f>
@@ -22829,7 +22838,7 @@
       </c>
       <c r="O5" s="102">
         <f>'[2]Project Summary'!$E$7</f>
-        <v>2.4831453238095245</v>
+        <v>2.5260024666666676</v>
       </c>
       <c r="P5" s="105">
         <f>'[2]Project Summary'!$F$7</f>
@@ -22841,11 +22850,11 @@
       </c>
       <c r="R5" s="82">
         <f>'[2]Project Summary'!$D$13</f>
-        <v>100.53227582380951</v>
+        <v>100.57513296666666</v>
       </c>
       <c r="S5" s="82">
         <f>'[2]Project Summary'!$E$13</f>
-        <v>3.3030415523809524</v>
+        <v>3.2601844095238097</v>
       </c>
       <c r="T5" s="69">
         <f>'[2]Project Summary'!$D$20</f>
@@ -22875,38 +22884,38 @@
       <c r="C6" s="8"/>
       <c r="D6" s="84">
         <f>$S$11-AC54-AC55</f>
-        <v>13.025761963333334</v>
+        <v>19.206180777619046</v>
       </c>
       <c r="F6" s="154" t="str">
-        <f>CONCATENATE($U$11, "      |    ", $T$11)</f>
-        <v>28      |    57</v>
+        <f ca="1">CONCATENATE($U$11, "      |    ", $T$11)</f>
+        <v>26      |    52</v>
       </c>
       <c r="G6" s="156" t="str">
         <f>CONCATENATE($P$11," / ",V11)</f>
-        <v>3 / 15</v>
+        <v>9 / 15</v>
       </c>
       <c r="I6" s="84">
         <f>$S$11</f>
-        <v>16.284649915714287</v>
+        <v>22.537933758571427</v>
       </c>
       <c r="L6" s="109" t="s">
         <v>149</v>
       </c>
       <c r="M6" s="69">
         <f>'[3]Project Summary'!$B$7</f>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N6" s="102">
-        <f>'[3]Project Summary'!$D$7</f>
+        <f ca="1">'[3]Project Summary'!$D$7</f>
         <v>0</v>
       </c>
       <c r="O6" s="102">
         <f>'[3]Project Summary'!$E$7</f>
-        <v>2.2269107523809528</v>
+        <v>2.7321155142857152</v>
       </c>
       <c r="P6" s="105">
         <f>'[3]Project Summary'!$F$7</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="82">
         <f>'[3]Project Summary'!$C$13</f>
@@ -22914,19 +22923,19 @@
       </c>
       <c r="R6" s="82">
         <f>'[3]Project Summary'!$D$13</f>
-        <v>48.900917852380957</v>
+        <v>49.215646423809524</v>
       </c>
       <c r="S6" s="82">
         <f>'[3]Project Summary'!$E$13</f>
-        <v>1.5123963585714286</v>
+        <v>1.4952999300000001</v>
       </c>
       <c r="T6" s="69">
         <f>'[3]Project Summary'!$D$20</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U6" s="69">
-        <f>'[3]Project Summary'!$F$20</f>
-        <v>10</v>
+        <f ca="1">'[3]Project Summary'!$F$20</f>
+        <v>9</v>
       </c>
       <c r="V6" s="69">
         <f>'[3]Project Summary'!$Q$3</f>
@@ -22966,12 +22975,12 @@
         <v>54</v>
       </c>
       <c r="N7" s="102">
-        <f>'[4]Project Summary'!$D$7</f>
-        <v>0.23809523809523811</v>
+        <f ca="1">'[4]Project Summary'!$D$7</f>
+        <v>0</v>
       </c>
       <c r="O7" s="102">
         <f>'[4]Project Summary'!$E$7</f>
-        <v>2.1198986666666664</v>
+        <v>2.1389462857142854</v>
       </c>
       <c r="P7" s="105">
         <f>'[4]Project Summary'!$F$7</f>
@@ -22983,7 +22992,7 @@
       </c>
       <c r="R7" s="82">
         <f>'[4]Project Summary'!$D$13</f>
-        <v>35.67853306666666</v>
+        <v>35.697580685714279</v>
       </c>
       <c r="S7" s="82">
         <f>'[4]Project Summary'!$E$13</f>
@@ -22994,7 +23003,7 @@
         <v>5</v>
       </c>
       <c r="U7" s="69">
-        <f>'[4]Project Summary'!$F$20</f>
+        <f ca="1">'[4]Project Summary'!$F$20</f>
         <v>1</v>
       </c>
       <c r="V7" s="69">
@@ -23020,36 +23029,36 @@
         <v>56</v>
       </c>
       <c r="N8" s="102">
-        <f>'[5]Project Summary'!$D$7</f>
-        <v>0.2628301904761905</v>
+        <f ca="1">'[5]Project Summary'!$D$7</f>
+        <v>0</v>
       </c>
       <c r="O8" s="102">
         <f>'[5]Project Summary'!$E$7</f>
-        <v>3.1068084714285713</v>
+        <v>3.8064526714285707</v>
       </c>
       <c r="P8" s="105">
         <f>'[5]Project Summary'!$F$7</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="82">
         <f>'[5]Project Summary'!$C$13</f>
-        <v>29.2764867</v>
+        <v>34.304362699999999</v>
       </c>
       <c r="R8" s="82">
         <f>'[5]Project Summary'!$D$13</f>
-        <v>28.113926766666662</v>
+        <v>28.990686871428569</v>
       </c>
       <c r="S8" s="82">
         <f>'[5]Project Summary'!$E$13</f>
-        <v>2.9578329428571428</v>
+        <v>6.2245148047619034</v>
       </c>
       <c r="T8" s="69">
         <f>'[5]Project Summary'!$D$20</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="U8" s="69">
-        <f>'[5]Project Summary'!$F$20</f>
-        <v>6</v>
+        <f ca="1">'[5]Project Summary'!$F$20</f>
+        <v>5</v>
       </c>
       <c r="V8" s="69">
         <f>'[5]Project Summary'!$Q$3</f>
@@ -23073,7 +23082,7 @@
         <v>18</v>
       </c>
       <c r="N9" s="102">
-        <f>'[6]Project Summary'!$D$7</f>
+        <f ca="1">'[6]Project Summary'!$D$7</f>
         <v>0</v>
       </c>
       <c r="O9" s="103">
@@ -23101,7 +23110,7 @@
         <v>15</v>
       </c>
       <c r="U9" s="69">
-        <f>'[6]Project Summary'!$F$20</f>
+        <f ca="1">'[6]Project Summary'!$F$20</f>
         <v>7</v>
       </c>
       <c r="V9" s="69">
@@ -23125,8 +23134,8 @@
         <v>25</v>
       </c>
       <c r="N10" s="102">
-        <f>'[7]Project Summary'!$D$7</f>
-        <v>7.1428571428571438E-2</v>
+        <f ca="1">'[7]Project Summary'!$D$7</f>
+        <v>0</v>
       </c>
       <c r="O10" s="103">
         <f>'[7]Project Summary'!$E$7</f>
@@ -23134,11 +23143,11 @@
       </c>
       <c r="P10" s="106">
         <f>'[7]Project Summary'!$F$7</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="82">
         <f>'[7]Project Summary'!$C$13</f>
-        <v>20.2332444</v>
+        <v>24.316816500000002</v>
       </c>
       <c r="R10" s="82">
         <f>'[7]Project Summary'!$D$13</f>
@@ -23146,15 +23155,15 @@
       </c>
       <c r="S10" s="82">
         <f>'[7]Project Summary'!$E$13</f>
-        <v>1.8083477666666665</v>
+        <v>4.8549033190476196</v>
       </c>
       <c r="T10" s="69">
         <f>'[7]Project Summary'!$D$20</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U10" s="69">
-        <f>'[7]Project Summary'!$F$20</f>
-        <v>2</v>
+        <f ca="1">'[7]Project Summary'!$F$20</f>
+        <v>1</v>
       </c>
       <c r="V10" s="69">
         <f>'[7]Project Summary'!$Q$3</f>
@@ -23174,39 +23183,39 @@
       </c>
       <c r="M11" s="117">
         <f t="shared" ref="M11:W11" si="0">SUM(M4:M10)</f>
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N11" s="118">
-        <f t="shared" si="0"/>
-        <v>0.57235400000000003</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
       <c r="O11" s="118">
         <f t="shared" si="0"/>
-        <v>13.496240142857143</v>
+        <v>14.762993866666665</v>
       </c>
       <c r="P11" s="119">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q11" s="120">
         <f t="shared" si="0"/>
-        <v>451.38305863000005</v>
+        <v>460.49450673000007</v>
       </c>
       <c r="R11" s="120">
         <f t="shared" si="0"/>
-        <v>442.28441093809522</v>
+        <v>443.53780437619048</v>
       </c>
       <c r="S11" s="120">
         <f t="shared" si="0"/>
-        <v>16.284649915714287</v>
+        <v>22.537933758571427</v>
       </c>
       <c r="T11" s="121">
         <f t="shared" si="0"/>
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="U11" s="121">
-        <f t="shared" si="0"/>
-        <v>28</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
       </c>
       <c r="V11" s="121">
         <f t="shared" si="0"/>
@@ -23335,11 +23344,11 @@
       </c>
       <c r="U20" s="64">
         <f>N43</f>
-        <v>5.9421200047619047</v>
+        <v>6.6289399190476193</v>
       </c>
       <c r="V20" s="88">
         <f>O43</f>
-        <v>0.35204216837542379</v>
+        <v>0.39273296083919096</v>
       </c>
       <c r="W20" s="64">
         <f>P43</f>
@@ -23361,11 +23370,11 @@
       </c>
       <c r="N21" s="18">
         <f>'[2]Project Summary'!$J$13-R37</f>
-        <v>2.4831453238095236</v>
+        <v>2.5260024666666663</v>
       </c>
       <c r="O21" s="19">
         <f t="shared" si="1"/>
-        <v>0.41714651821240034</v>
+        <v>0.42434614030135703</v>
       </c>
       <c r="P21" s="18">
         <f>'[2]Project Summary'!$L$13-T37</f>
@@ -23373,7 +23382,7 @@
       </c>
       <c r="Q21" s="18">
         <f t="shared" si="2"/>
-        <v>0.66685467619047634</v>
+        <v>0.62399753333333363</v>
       </c>
       <c r="S21" s="65" t="s">
         <v>119</v>
@@ -23384,18 +23393,18 @@
       </c>
       <c r="U21" s="64">
         <f>R43</f>
-        <v>1.3519880904761905</v>
+        <v>1.4211175190476191</v>
       </c>
       <c r="V21" s="88">
         <f>S43</f>
-        <v>0.67106477250489904</v>
+        <v>0.70537744477210818</v>
       </c>
       <c r="W21" s="64">
         <f>T43</f>
         <v>1.41</v>
       </c>
       <c r="X21" s="63">
-        <f t="shared" ref="X21:X25" si="3">T21-W21</f>
+        <f t="shared" ref="X20:X25" si="3">T21-W21</f>
         <v>0.60469090000000025</v>
       </c>
       <c r="AF21" s="1"/>
@@ -23410,11 +23419,11 @@
       </c>
       <c r="N22" s="18">
         <f>'[3]Project Summary'!$J$13-R38</f>
-        <v>1.9911221190476192</v>
+        <v>1.9911221190476196</v>
       </c>
       <c r="O22" s="19">
         <f t="shared" si="1"/>
-        <v>0.27517367712009266</v>
+        <v>0.27517367712009277</v>
       </c>
       <c r="P22" s="18">
         <f>'[3]Project Summary'!$L$13-T38</f>
@@ -23422,7 +23431,7 @@
       </c>
       <c r="Q22" s="18">
         <f t="shared" si="2"/>
-        <v>4.8388778809523814</v>
+        <v>4.8388778809523805</v>
       </c>
       <c r="S22" s="65" t="s">
         <v>120</v>
@@ -23433,11 +23442,11 @@
       </c>
       <c r="U22" s="64">
         <f>V43</f>
-        <v>0.98451043809523808</v>
+        <v>0.94651043809523805</v>
       </c>
       <c r="V22" s="88">
         <f>W43</f>
-        <v>0.47332232600732599</v>
+        <v>0.45505309523809517</v>
       </c>
       <c r="W22" s="64">
         <f>X43</f>
@@ -23511,11 +23520,11 @@
       </c>
       <c r="N24" s="18">
         <f>'[5]Project Summary'!$J$13-R40</f>
-        <v>2.4223353285714286</v>
+        <v>3.6017421952380952</v>
       </c>
       <c r="O24" s="19">
         <f t="shared" si="1"/>
-        <v>0.23056247643916561</v>
+        <v>0.34282066162956709</v>
       </c>
       <c r="P24" s="18">
         <f>'[5]Project Summary'!$L$13-T40</f>
@@ -23523,7 +23532,7 @@
       </c>
       <c r="Q24" s="18">
         <f t="shared" si="2"/>
-        <v>6.8976646714285721</v>
+        <v>5.7182578047619046</v>
       </c>
       <c r="S24" s="65" t="str">
         <f>CONCATENATE("Expected New Monthly
@@ -23537,11 +23546,11 @@
       </c>
       <c r="U24" s="64">
         <f>AD43</f>
-        <v>0.24822390476190476</v>
+        <v>0.55087066666666673</v>
       </c>
       <c r="V24" s="88">
         <f>AE43</f>
-        <v>2.6893164112882419E-2</v>
+        <v>5.9682629107981222E-2</v>
       </c>
       <c r="W24" s="64">
         <f>AF43</f>
@@ -23586,11 +23595,11 @@
       </c>
       <c r="U25" s="64">
         <f>AH43</f>
-        <v>1.9275055238095238</v>
+        <v>2.1603028571428569</v>
       </c>
       <c r="V25" s="88">
         <f>AI43</f>
-        <v>0.2241285492801772</v>
+        <v>0.25119800664451825</v>
       </c>
       <c r="W25" s="64">
         <f>AJ43</f>
@@ -23638,11 +23647,11 @@
       </c>
       <c r="N27" s="18">
         <f>SUM(N20:N26)</f>
-        <v>10.989528409523809</v>
+        <v>12.211792419047619</v>
       </c>
       <c r="O27" s="19">
         <f>N27/M27</f>
-        <v>0.28380814508343938</v>
+        <v>0.31537351062219876</v>
       </c>
       <c r="P27" s="18">
         <f>SUM(P20:P26)</f>
@@ -23650,7 +23659,7 @@
       </c>
       <c r="Q27" s="18">
         <f t="shared" si="2"/>
-        <v>21.520471590476191</v>
+        <v>20.298207580952379</v>
       </c>
       <c r="AF27" s="1"/>
     </row>
@@ -23718,8 +23727,8 @@
       <c r="AA34" s="231"/>
       <c r="AB34" s="235"/>
       <c r="AC34" s="230" t="str">
-        <f>CONCATENATE("Expected Registrations in August ",$D$3,"'",$I$3," ")</f>
-        <v xml:space="preserve">Expected Registrations in August '₹ 0.57  |  ₹ 13.5 </v>
+        <f ca="1">CONCATENATE("Expected Registrations in August ",$D$3,"'",$I$3," ")</f>
+        <v xml:space="preserve">Expected Registrations in August '₹ 0  |  ₹ 14.76 </v>
       </c>
       <c r="AD34" s="231"/>
       <c r="AE34" s="231"/>
@@ -23926,11 +23935,11 @@
       </c>
       <c r="N37" s="63">
         <f>'[2]Project Summary'!$J$7</f>
-        <v>2.4831453238095236</v>
+        <v>2.5260024666666663</v>
       </c>
       <c r="O37" s="88">
         <f t="shared" si="4"/>
-        <v>0.41714651821240034</v>
+        <v>0.42434614030135703</v>
       </c>
       <c r="P37" s="146">
         <f>'[2]Project Summary'!$L$7</f>
@@ -24050,11 +24059,11 @@
       </c>
       <c r="R38" s="63">
         <f>'[3]Project Summary'!$J$8</f>
-        <v>0.22850133333333336</v>
+        <v>0.37170609523809517</v>
       </c>
       <c r="S38" s="88">
         <f t="shared" si="5"/>
-        <v>1.1425066666666668</v>
+        <v>1.8585304761904757</v>
       </c>
       <c r="T38" s="124">
         <f>'[3]Project Summary'!$L$8</f>
@@ -24066,11 +24075,11 @@
       </c>
       <c r="V38" s="63">
         <f>'[3]Project Summary'!$J$9</f>
-        <v>1.4189999999999999E-2</v>
+        <v>0.1857138095238095</v>
       </c>
       <c r="W38" s="88">
         <f t="shared" si="6"/>
-        <v>1.4189999999999999E-2</v>
+        <v>0.1857138095238095</v>
       </c>
       <c r="X38" s="146">
         <f>'[3]Project Summary'!$L$9</f>
@@ -24170,11 +24179,11 @@
       </c>
       <c r="V39" s="63">
         <f>'[4]Project Summary'!$J$9</f>
-        <v>0.23206438095238097</v>
+        <v>0.251112</v>
       </c>
       <c r="W39" s="88">
         <f t="shared" si="6"/>
-        <v>0.33152054421768712</v>
+        <v>0.35873142857142859</v>
       </c>
       <c r="X39" s="146">
         <f>'[4]Project Summary'!$L$9</f>
@@ -24242,11 +24251,11 @@
       </c>
       <c r="N40" s="63">
         <f>'[5]Project Summary'!$J$7</f>
-        <v>0.81702142380952358</v>
+        <v>1.4609841952380953</v>
       </c>
       <c r="O40" s="88">
         <f t="shared" si="4"/>
-        <v>0.33888493760637517</v>
+        <v>0.60598843973837913</v>
       </c>
       <c r="P40" s="146">
         <f>'[5]Project Summary'!$L$7</f>
@@ -24258,11 +24267,11 @@
       </c>
       <c r="R40" s="63">
         <f>'[5]Project Summary'!$J$8</f>
-        <v>0.27878580952380949</v>
+        <v>0.20471047619047619</v>
       </c>
       <c r="S40" s="88">
         <f t="shared" si="5"/>
-        <v>0.53612655677655674</v>
+        <v>0.39367399267399267</v>
       </c>
       <c r="T40" s="124">
         <f>'[5]Project Summary'!$L$8</f>
@@ -24274,11 +24283,11 @@
       </c>
       <c r="V40" s="63">
         <f>'[5]Project Summary'!$J$9</f>
-        <v>0.22857142857142854</v>
+        <v>0</v>
       </c>
       <c r="W40" s="88">
         <f t="shared" si="6"/>
-        <v>1.2698412698412698</v>
+        <v>0</v>
       </c>
       <c r="X40" s="146">
         <f>'[5]Project Summary'!$L$9</f>
@@ -24306,11 +24315,11 @@
       </c>
       <c r="AD40" s="63">
         <f>'[5]Project Summary'!$J$11</f>
-        <v>0</v>
+        <v>0.30264676190476192</v>
       </c>
       <c r="AE40" s="88">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.14982512965582273</v>
       </c>
       <c r="AF40" s="146">
         <f>'[5]Project Summary'!$L$11</f>
@@ -24322,11 +24331,11 @@
       </c>
       <c r="AH40" s="63">
         <f>'[5]Project Summary'!$J$12</f>
-        <v>0.58587628571428574</v>
+        <v>0.81867361904761904</v>
       </c>
       <c r="AI40" s="88">
         <f t="shared" si="9"/>
-        <v>0.13437529488859765</v>
+        <v>0.18776917868064655</v>
       </c>
       <c r="AJ40" s="186">
         <f>'[5]Project Summary'!$L$12</f>
@@ -24554,11 +24563,11 @@
       </c>
       <c r="N43" s="192">
         <f>SUM(N36:N42)</f>
-        <v>5.9421200047619047</v>
+        <v>6.6289399190476193</v>
       </c>
       <c r="O43" s="193">
         <f t="shared" si="4"/>
-        <v>0.35204216837542379</v>
+        <v>0.39273296083919096</v>
       </c>
       <c r="P43" s="194">
         <f>SUM(P36:P42)</f>
@@ -24570,11 +24579,11 @@
       </c>
       <c r="R43" s="192">
         <f>SUM(R36:R42)</f>
-        <v>1.3519880904761905</v>
+        <v>1.4211175190476191</v>
       </c>
       <c r="S43" s="193">
         <f t="shared" si="5"/>
-        <v>0.67106477250489904</v>
+        <v>0.70537744477210818</v>
       </c>
       <c r="T43" s="195">
         <f>SUM(T36:T42)</f>
@@ -24586,11 +24595,11 @@
       </c>
       <c r="V43" s="192">
         <f>SUM(V36:V42)</f>
-        <v>0.98451043809523808</v>
+        <v>0.94651043809523805</v>
       </c>
       <c r="W43" s="193">
         <f t="shared" si="6"/>
-        <v>0.47332232600732599</v>
+        <v>0.45505309523809517</v>
       </c>
       <c r="X43" s="194">
         <f>SUM(X36:X42)</f>
@@ -24618,11 +24627,11 @@
       </c>
       <c r="AD43" s="192">
         <f>SUM(AD36:AD42)</f>
-        <v>0.24822390476190476</v>
+        <v>0.55087066666666673</v>
       </c>
       <c r="AE43" s="193">
         <f t="shared" si="8"/>
-        <v>2.6893164112882419E-2</v>
+        <v>5.9682629107981222E-2</v>
       </c>
       <c r="AF43" s="194">
         <f>SUM(AF36:AF42)</f>
@@ -24634,11 +24643,11 @@
       </c>
       <c r="AH43" s="192">
         <f>SUM(AH36:AH42)</f>
-        <v>1.9275055238095238</v>
+        <v>2.1603028571428569</v>
       </c>
       <c r="AI43" s="193">
         <f t="shared" si="9"/>
-        <v>0.2241285492801772</v>
+        <v>0.25119800664451825</v>
       </c>
       <c r="AJ43" s="197">
         <f>SUM(AJ36:AJ42)</f>
@@ -24687,7 +24696,7 @@
       </c>
       <c r="R45" s="112">
         <f>N27-R43</f>
-        <v>9.6375403190476181</v>
+        <v>10.790674899999999</v>
       </c>
       <c r="S45" s="158"/>
       <c r="T45" s="112"/>
@@ -24842,7 +24851,7 @@
       </c>
       <c r="W53" s="169">
         <f>'[2]Project Summary'!$L$18</f>
-        <v>3.2648272523809525</v>
+        <v>3.2219701095238098</v>
       </c>
       <c r="X53" s="169">
         <f>'[3]Project Summary'!$L$18</f>
@@ -24854,7 +24863,7 @@
       </c>
       <c r="Z53" s="169">
         <f>'[5]Project Summary'!$L$18</f>
-        <v>1.8667736714285712</v>
+        <v>4.1346330333333334</v>
       </c>
       <c r="AA53" s="169">
         <f>'[6]Project Summary'!$L$18</f>
@@ -24862,11 +24871,11 @@
       </c>
       <c r="AB53" s="169">
         <f>'[7]Project Summary'!$L$18</f>
-        <v>1.783109619047619</v>
+        <v>4.8191245476190474</v>
       </c>
       <c r="AC53" s="169">
         <f>SUM(V53:AB53)</f>
-        <v>11.776722695238096</v>
+        <v>17.037739842857142</v>
       </c>
     </row>
     <row r="54" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -24902,7 +24911,7 @@
       </c>
       <c r="X54" s="169">
         <f>'[3]Project Summary'!$L$19</f>
-        <v>1.7096528571428567E-2</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="Y54" s="169">
         <f>'[4]Project Summary'!$L$19</f>
@@ -24910,7 +24919,7 @@
       </c>
       <c r="Z54" s="169">
         <f>'[5]Project Summary'!$L$19</f>
-        <v>0.30473239047619044</v>
+        <v>0.38415322380952377</v>
       </c>
       <c r="AA54" s="169">
         <f>'[6]Project Summary'!$L$19</f>
@@ -24922,7 +24931,7 @@
       </c>
       <c r="AC54" s="169">
         <f>SUM(V54:AB54)</f>
-        <v>3.1361904190476189</v>
+        <v>3.198514823809524</v>
       </c>
     </row>
     <row r="55" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -24974,11 +24983,11 @@
       </c>
       <c r="AB55" s="169">
         <f>'[7]Project Summary'!$L$20</f>
-        <v>2.5238147619047597E-2</v>
+        <v>3.5778771428571408E-2</v>
       </c>
       <c r="AC55" s="169">
         <f>SUM(V55:AB55)</f>
-        <v>0.1226975333333333</v>
+        <v>0.13323815714285711</v>
       </c>
     </row>
     <row r="56" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -25025,7 +25034,7 @@
       </c>
       <c r="Z56" s="169">
         <f>'[5]Project Summary'!$L$21</f>
-        <v>0.69585068095238101</v>
+        <v>0.79152638095238093</v>
       </c>
       <c r="AA56" s="169">
         <f>'[6]Project Summary'!$L$21</f>
@@ -25037,7 +25046,7 @@
       </c>
       <c r="AC56" s="169">
         <f>SUM(V56:AB56)</f>
-        <v>1.141548872857143</v>
+        <v>1.2372245728571429</v>
       </c>
     </row>
     <row r="57" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -25084,7 +25093,7 @@
       </c>
       <c r="Z57" s="169">
         <f>'[5]Project Summary'!$L$22</f>
-        <v>9.0476200000000007E-2</v>
+        <v>0.91420216666666665</v>
       </c>
       <c r="AA57" s="169">
         <f>'[6]Project Summary'!$L$22</f>
@@ -25096,7 +25105,7 @@
       </c>
       <c r="AC57" s="169">
         <f>SUM(V57:AB57)</f>
-        <v>0.10749029523809524</v>
+        <v>0.93121626190476192</v>
       </c>
     </row>
     <row r="58" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -25128,11 +25137,11 @@
       </c>
       <c r="W58" s="167">
         <f t="shared" si="11"/>
-        <v>3.3030415523809524</v>
+        <v>3.2601844095238097</v>
       </c>
       <c r="X58" s="167">
         <f t="shared" si="11"/>
-        <v>1.5123963585714286</v>
+        <v>1.4952999300000001</v>
       </c>
       <c r="Y58" s="167">
         <f t="shared" si="11"/>
@@ -25140,7 +25149,7 @@
       </c>
       <c r="Z58" s="167">
         <f t="shared" si="11"/>
-        <v>2.9578329428571428</v>
+        <v>6.2245148047619043</v>
       </c>
       <c r="AA58" s="167">
         <f t="shared" si="11"/>
@@ -25148,11 +25157,11 @@
       </c>
       <c r="AB58" s="167">
         <f t="shared" si="11"/>
-        <v>1.8083477666666665</v>
+        <v>4.8549033190476187</v>
       </c>
       <c r="AC58" s="167">
         <f t="shared" si="11"/>
-        <v>16.284649815714285</v>
+        <v>22.537933658571429</v>
       </c>
     </row>
     <row r="59" spans="12:29" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -25529,7 +25538,7 @@
       </c>
       <c r="Q2" s="219">
         <f>Overall_Draft!U4</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2" s="219">
         <f>Overall_Draft!V4</f>
@@ -25652,11 +25661,11 @@
       </c>
       <c r="AX2" s="205">
         <f>Overall!U20</f>
-        <v>5.9421200047619047</v>
+        <v>6.6289399190476193</v>
       </c>
       <c r="AY2" s="206">
         <f>Overall!V20</f>
-        <v>0.34730958929797462</v>
+        <v>0.38745336663015251</v>
       </c>
       <c r="AZ2" s="205">
         <f>Overall!W20</f>
@@ -25679,11 +25688,11 @@
       </c>
       <c r="D3" s="221">
         <f>Overall_Draft!N21</f>
-        <v>2.4831453238095236</v>
+        <v>2.5260024666666663</v>
       </c>
       <c r="E3" s="222">
         <f t="shared" si="0"/>
-        <v>0.41714651821240034</v>
+        <v>0.42434614030135703</v>
       </c>
       <c r="F3" s="221">
         <f>Overall_Draft!P21</f>
@@ -25691,7 +25700,7 @@
       </c>
       <c r="G3" s="221">
         <f>Overall_Draft!Q21</f>
-        <v>0.66685467619047634</v>
+        <v>0.62399753333333363</v>
       </c>
       <c r="H3" s="123" t="str">
         <f>Overall_Draft!L5</f>
@@ -25707,7 +25716,7 @@
       </c>
       <c r="K3" s="209">
         <f>Overall_Draft!O5</f>
-        <v>2.4831453238095245</v>
+        <v>2.5260024666666676</v>
       </c>
       <c r="L3" s="123">
         <f>Overall_Draft!P5</f>
@@ -25719,11 +25728,11 @@
       </c>
       <c r="N3" s="209">
         <f>Overall_Draft!R5</f>
-        <v>100.53227582380951</v>
+        <v>100.57513296666666</v>
       </c>
       <c r="O3" s="209">
         <f>Overall_Draft!S5</f>
-        <v>3.3030415523809524</v>
+        <v>3.2601844095238097</v>
       </c>
       <c r="P3" s="123">
         <f>Overall_Draft!T5</f>
@@ -25753,11 +25762,11 @@
       </c>
       <c r="W3" s="209">
         <f>Overall_Draft!N37</f>
-        <v>2.4831453238095236</v>
+        <v>2.5260024666666663</v>
       </c>
       <c r="X3" s="210">
         <f>Overall_Draft!O37</f>
-        <v>0.41714651821240034</v>
+        <v>0.42434614030135703</v>
       </c>
       <c r="Y3" s="209">
         <f>Overall_Draft!P37</f>
@@ -25854,11 +25863,11 @@
       </c>
       <c r="AX3" s="209">
         <f>Overall!U21</f>
-        <v>0.5549061904761905</v>
+        <v>0.62403561904761906</v>
       </c>
       <c r="AY3" s="210">
         <f>Overall!V21</f>
-        <v>0.3831657997550435</v>
+        <v>0.43090005329157366</v>
       </c>
       <c r="AZ3" s="209">
         <f>Overall!W21</f>
@@ -25881,11 +25890,11 @@
       </c>
       <c r="D4" s="221">
         <f>Overall_Draft!N22</f>
-        <v>1.9911221190476192</v>
+        <v>1.9911221190476196</v>
       </c>
       <c r="E4" s="222">
         <f t="shared" si="0"/>
-        <v>0.27517367712009266</v>
+        <v>0.27517367712009277</v>
       </c>
       <c r="F4" s="221">
         <f>Overall_Draft!P22</f>
@@ -25893,7 +25902,7 @@
       </c>
       <c r="G4" s="221">
         <f>Overall_Draft!Q22</f>
-        <v>4.8388778809523814</v>
+        <v>4.8388778809523805</v>
       </c>
       <c r="H4" s="123" t="str">
         <f>Overall_Draft!L6</f>
@@ -25901,19 +25910,19 @@
       </c>
       <c r="I4" s="123">
         <f>Overall_Draft!M6</f>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J4" s="209">
-        <f>Overall_Draft!N6</f>
+        <f ca="1">Overall_Draft!N6</f>
         <v>0</v>
       </c>
       <c r="K4" s="209">
         <f>Overall_Draft!O6</f>
-        <v>2.2269107523809528</v>
+        <v>2.7321155142857152</v>
       </c>
       <c r="L4" s="123">
         <f>Overall_Draft!P6</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="209">
         <f>Overall_Draft!Q6</f>
@@ -25921,19 +25930,19 @@
       </c>
       <c r="N4" s="209">
         <f>Overall_Draft!R6</f>
-        <v>48.900917852380957</v>
+        <v>49.215646423809524</v>
       </c>
       <c r="O4" s="209">
         <f>Overall_Draft!S6</f>
-        <v>1.5123963585714286</v>
+        <v>1.4952999300000001</v>
       </c>
       <c r="P4" s="123">
         <f>Overall_Draft!T6</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q4" s="123">
-        <f>Overall_Draft!U6</f>
-        <v>10</v>
+        <f ca="1">Overall_Draft!U6</f>
+        <v>9</v>
       </c>
       <c r="R4" s="123">
         <f>Overall_Draft!V6</f>
@@ -25971,11 +25980,11 @@
       </c>
       <c r="AA4" s="209">
         <f>Overall_Draft!R38</f>
-        <v>0.22850133333333336</v>
+        <v>0.37170609523809517</v>
       </c>
       <c r="AB4" s="210">
         <f>Overall_Draft!S38</f>
-        <v>1.1425066666666668</v>
+        <v>1.8585304761904757</v>
       </c>
       <c r="AC4" s="209">
         <f>Overall_Draft!T38</f>
@@ -25987,11 +25996,11 @@
       </c>
       <c r="AE4" s="209">
         <f>Overall_Draft!V38</f>
-        <v>1.4189999999999999E-2</v>
+        <v>0.1857138095238095</v>
       </c>
       <c r="AF4" s="210">
         <f>Overall_Draft!W38</f>
-        <v>1.4189999999999999E-2</v>
+        <v>0.1857138095238095</v>
       </c>
       <c r="AG4" s="209">
         <f>Overall_Draft!X38</f>
@@ -26056,11 +26065,11 @@
       </c>
       <c r="AX4" s="209">
         <f>Overall!U22</f>
-        <v>0.82428523809523813</v>
+        <v>0.78628523809523809</v>
       </c>
       <c r="AY4" s="210">
         <f>Overall!V22</f>
-        <v>0.39629097985347983</v>
+        <v>0.37802174908424907</v>
       </c>
       <c r="AZ4" s="209">
         <f>Overall!W22</f>
@@ -26106,12 +26115,12 @@
         <v>54</v>
       </c>
       <c r="J5" s="209">
-        <f>Overall_Draft!N7</f>
-        <v>0.23809523809523811</v>
+        <f ca="1">Overall_Draft!N7</f>
+        <v>0</v>
       </c>
       <c r="K5" s="209">
         <f>Overall_Draft!O7</f>
-        <v>2.1198986666666664</v>
+        <v>2.1389462857142854</v>
       </c>
       <c r="L5" s="123">
         <f>Overall_Draft!P7</f>
@@ -26123,7 +26132,7 @@
       </c>
       <c r="N5" s="209">
         <f>Overall_Draft!R7</f>
-        <v>35.67853306666666</v>
+        <v>35.697580685714279</v>
       </c>
       <c r="O5" s="209">
         <f>Overall_Draft!S7</f>
@@ -26134,7 +26143,7 @@
         <v>5</v>
       </c>
       <c r="Q5" s="123">
-        <f>Overall_Draft!U7</f>
+        <f ca="1">Overall_Draft!U7</f>
         <v>1</v>
       </c>
       <c r="R5" s="123">
@@ -26189,11 +26198,11 @@
       </c>
       <c r="AE5" s="209">
         <f>Overall_Draft!V39</f>
-        <v>0.23206438095238097</v>
+        <v>0.251112</v>
       </c>
       <c r="AF5" s="210">
         <f>Overall_Draft!W39</f>
-        <v>0.33152054421768712</v>
+        <v>0.35873142857142859</v>
       </c>
       <c r="AG5" s="209">
         <f>Overall_Draft!X39</f>
@@ -26285,11 +26294,11 @@
       </c>
       <c r="D6" s="221">
         <f>Overall_Draft!N24</f>
-        <v>2.4223353285714286</v>
+        <v>3.6017421952380952</v>
       </c>
       <c r="E6" s="222">
         <f t="shared" si="0"/>
-        <v>0.23056247643916561</v>
+        <v>0.34282066162956709</v>
       </c>
       <c r="F6" s="221">
         <f>Overall_Draft!P24</f>
@@ -26297,7 +26306,7 @@
       </c>
       <c r="G6" s="221">
         <f>Overall_Draft!Q24</f>
-        <v>6.8976646714285721</v>
+        <v>5.7182578047619046</v>
       </c>
       <c r="H6" s="123" t="str">
         <f>Overall_Draft!L8</f>
@@ -26308,36 +26317,36 @@
         <v>56</v>
       </c>
       <c r="J6" s="209">
-        <f>Overall_Draft!N8</f>
-        <v>0.2628301904761905</v>
+        <f ca="1">Overall_Draft!N8</f>
+        <v>0</v>
       </c>
       <c r="K6" s="209">
         <f>Overall_Draft!O8</f>
-        <v>3.1068084714285713</v>
+        <v>3.8064526714285707</v>
       </c>
       <c r="L6" s="123">
         <f>Overall_Draft!P8</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M6" s="209">
         <f>Overall_Draft!Q8</f>
-        <v>29.2764867</v>
+        <v>34.304362699999999</v>
       </c>
       <c r="N6" s="209">
         <f>Overall_Draft!R8</f>
-        <v>28.113926766666662</v>
+        <v>28.990686871428569</v>
       </c>
       <c r="O6" s="209">
         <f>Overall_Draft!S8</f>
-        <v>2.9578329428571428</v>
+        <v>6.2245148047619034</v>
       </c>
       <c r="P6" s="123">
         <f>Overall_Draft!T8</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q6" s="123">
-        <f>Overall_Draft!U8</f>
-        <v>6</v>
+        <f ca="1">Overall_Draft!U8</f>
+        <v>5</v>
       </c>
       <c r="R6" s="123">
         <f>Overall_Draft!V8</f>
@@ -26359,11 +26368,11 @@
       </c>
       <c r="W6" s="209">
         <f>Overall_Draft!N40</f>
-        <v>0.81702142380952358</v>
+        <v>1.4609841952380953</v>
       </c>
       <c r="X6" s="210">
         <f>Overall_Draft!O40</f>
-        <v>0.33888493760637517</v>
+        <v>0.60598843973837913</v>
       </c>
       <c r="Y6" s="209">
         <f>Overall_Draft!P40</f>
@@ -26375,11 +26384,11 @@
       </c>
       <c r="AA6" s="209">
         <f>Overall_Draft!R40</f>
-        <v>0.27878580952380949</v>
+        <v>0.20471047619047619</v>
       </c>
       <c r="AB6" s="210">
         <f>Overall_Draft!S40</f>
-        <v>0.53612655677655674</v>
+        <v>0.39367399267399267</v>
       </c>
       <c r="AC6" s="209">
         <f>Overall_Draft!T40</f>
@@ -26391,11 +26400,11 @@
       </c>
       <c r="AE6" s="209">
         <f>Overall_Draft!V40</f>
-        <v>0.22857142857142854</v>
+        <v>0</v>
       </c>
       <c r="AF6" s="210">
         <f>Overall_Draft!W40</f>
-        <v>1.2698412698412698</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="209">
         <f>Overall_Draft!X40</f>
@@ -26423,11 +26432,11 @@
       </c>
       <c r="AM6" s="209">
         <f>Overall_Draft!AD40</f>
-        <v>0</v>
+        <v>0.30264676190476192</v>
       </c>
       <c r="AN6" s="210">
         <f>Overall_Draft!AE40</f>
-        <v>0</v>
+        <v>0.14982512965582273</v>
       </c>
       <c r="AO6" s="209">
         <f>Overall_Draft!AF40</f>
@@ -26439,11 +26448,11 @@
       </c>
       <c r="AQ6" s="209">
         <f>Overall_Draft!AH40</f>
-        <v>0.58587628571428574</v>
+        <v>0.81867361904761904</v>
       </c>
       <c r="AR6" s="210">
         <f>Overall_Draft!AI40</f>
-        <v>0.13437529488859765</v>
+        <v>0.18776917868064655</v>
       </c>
       <c r="AS6" s="211">
         <f>Overall_Draft!AJ40</f>
@@ -26460,11 +26469,11 @@
       </c>
       <c r="AX6" s="209">
         <f>Overall!U24</f>
-        <v>0.24822390476190476</v>
+        <v>0.55087066666666673</v>
       </c>
       <c r="AY6" s="210">
         <f>Overall!V24</f>
-        <v>2.6893164112882419E-2</v>
+        <v>5.9682629107981222E-2</v>
       </c>
       <c r="AZ6" s="209">
         <f>Overall!W24</f>
@@ -26510,7 +26519,7 @@
         <v>18</v>
       </c>
       <c r="J7" s="209">
-        <f>Overall_Draft!N9</f>
+        <f ca="1">Overall_Draft!N9</f>
         <v>0</v>
       </c>
       <c r="K7" s="209">
@@ -26538,7 +26547,7 @@
         <v>15</v>
       </c>
       <c r="Q7" s="123">
-        <f>Overall_Draft!U9</f>
+        <f ca="1">Overall_Draft!U9</f>
         <v>7</v>
       </c>
       <c r="R7" s="123">
@@ -26662,11 +26671,11 @@
       </c>
       <c r="AX7" s="213">
         <f>Overall!U25</f>
-        <v>1.9275055238095238</v>
+        <v>2.1603028571428569</v>
       </c>
       <c r="AY7" s="214">
         <f>Overall!V25</f>
-        <v>0.22864834208891149</v>
+        <v>0.25626368412133532</v>
       </c>
       <c r="AZ7" s="213">
         <f>Overall!W25</f>
@@ -26712,8 +26721,8 @@
         <v>25</v>
       </c>
       <c r="J8" s="209">
-        <f>Overall_Draft!N10</f>
-        <v>7.1428571428571438E-2</v>
+        <f ca="1">Overall_Draft!N10</f>
+        <v>0</v>
       </c>
       <c r="K8" s="209">
         <f>Overall_Draft!O10</f>
@@ -26721,11 +26730,11 @@
       </c>
       <c r="L8" s="123">
         <f>Overall_Draft!P10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="209">
         <f>Overall_Draft!Q10</f>
-        <v>20.2332444</v>
+        <v>24.316816500000002</v>
       </c>
       <c r="N8" s="209">
         <f>Overall_Draft!R10</f>
@@ -26733,15 +26742,15 @@
       </c>
       <c r="O8" s="209">
         <f>Overall_Draft!S10</f>
-        <v>1.8083477666666665</v>
+        <v>4.8549033190476196</v>
       </c>
       <c r="P8" s="123">
         <f>Overall_Draft!T10</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="123">
-        <f>Overall_Draft!U10</f>
-        <v>2</v>
+        <f ca="1">Overall_Draft!U10</f>
+        <v>1</v>
       </c>
       <c r="R8" s="123">
         <f>Overall_Draft!V10</f>
@@ -26865,11 +26874,11 @@
       </c>
       <c r="D9" s="224">
         <f>Overall_Draft!N27</f>
-        <v>10.989528409523809</v>
+        <v>12.211792419047619</v>
       </c>
       <c r="E9" s="225">
         <f t="shared" si="0"/>
-        <v>0.28380814508343938</v>
+        <v>0.31537351062219876</v>
       </c>
       <c r="F9" s="224">
         <f>Overall_Draft!P27</f>
@@ -26877,7 +26886,7 @@
       </c>
       <c r="G9" s="224">
         <f>Overall_Draft!Q27</f>
-        <v>21.520471590476191</v>
+        <v>20.298207580952379</v>
       </c>
       <c r="H9" s="226" t="str">
         <f>Overall_Draft!L11</f>
@@ -26885,39 +26894,39 @@
       </c>
       <c r="I9" s="226">
         <f>Overall_Draft!M11</f>
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J9" s="213">
-        <f>Overall_Draft!N11</f>
-        <v>0.57235400000000003</v>
+        <f ca="1">Overall_Draft!N11</f>
+        <v>0</v>
       </c>
       <c r="K9" s="213">
         <f>Overall_Draft!O11</f>
-        <v>13.496240142857143</v>
+        <v>14.762993866666665</v>
       </c>
       <c r="L9" s="226">
         <f>Overall_Draft!P11</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M9" s="213">
         <f>Overall_Draft!Q11</f>
-        <v>451.38305863000005</v>
+        <v>460.49450673000007</v>
       </c>
       <c r="N9" s="213">
         <f>Overall_Draft!R11</f>
-        <v>442.28441093809522</v>
+        <v>443.53780437619048</v>
       </c>
       <c r="O9" s="213">
         <f>Overall_Draft!S11</f>
-        <v>16.284649915714287</v>
+        <v>22.537933758571427</v>
       </c>
       <c r="P9" s="226">
         <f>Overall_Draft!T11</f>
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="Q9" s="226">
-        <f>Overall_Draft!U11</f>
-        <v>28</v>
+        <f ca="1">Overall_Draft!U11</f>
+        <v>26</v>
       </c>
       <c r="R9" s="226">
         <f>Overall_Draft!V11</f>
@@ -26938,11 +26947,11 @@
       </c>
       <c r="W9" s="213">
         <f>Overall_Draft!N43</f>
-        <v>5.9421200047619047</v>
+        <v>6.6289399190476193</v>
       </c>
       <c r="X9" s="214">
         <f>Overall_Draft!O43</f>
-        <v>0.35204216837542379</v>
+        <v>0.39273296083919096</v>
       </c>
       <c r="Y9" s="213">
         <f>Overall_Draft!P43</f>
@@ -26954,11 +26963,11 @@
       </c>
       <c r="AA9" s="213">
         <f>Overall_Draft!R43</f>
-        <v>1.3519880904761905</v>
+        <v>1.4211175190476191</v>
       </c>
       <c r="AB9" s="214">
         <f>Overall_Draft!S43</f>
-        <v>0.67106477250489904</v>
+        <v>0.70537744477210818</v>
       </c>
       <c r="AC9" s="213">
         <f>Overall_Draft!T43</f>
@@ -26970,11 +26979,11 @@
       </c>
       <c r="AE9" s="213">
         <f>Overall_Draft!V43</f>
-        <v>0.98451043809523808</v>
+        <v>0.94651043809523805</v>
       </c>
       <c r="AF9" s="214">
         <f>Overall_Draft!W43</f>
-        <v>0.47332232600732599</v>
+        <v>0.45505309523809517</v>
       </c>
       <c r="AG9" s="213">
         <f>Overall_Draft!X43</f>
@@ -27002,11 +27011,11 @@
       </c>
       <c r="AM9" s="213">
         <f>Overall_Draft!AD43</f>
-        <v>0.24822390476190476</v>
+        <v>0.55087066666666673</v>
       </c>
       <c r="AN9" s="214">
         <f>Overall_Draft!AE43</f>
-        <v>2.6893164112882419E-2</v>
+        <v>5.9682629107981222E-2</v>
       </c>
       <c r="AO9" s="213">
         <f>Overall_Draft!AF43</f>
@@ -27018,11 +27027,11 @@
       </c>
       <c r="AQ9" s="213">
         <f>Overall_Draft!AH43</f>
-        <v>1.9275055238095238</v>
+        <v>2.1603028571428569</v>
       </c>
       <c r="AR9" s="214">
         <f>Overall_Draft!AI43</f>
-        <v>0.2241285492801772</v>
+        <v>0.25119800664451825</v>
       </c>
       <c r="AS9" s="215">
         <f>Overall_Draft!AJ43</f>
@@ -27038,39 +27047,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="720fc211-b8f9-4216-8e59-f92e385e0bb9">
-      <UserInfo>
-        <DisplayName>Ankit Jain</DisplayName>
-        <AccountId>34</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Poonam</DisplayName>
-        <AccountId>10</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Rishabh Goyal</DisplayName>
-        <AccountId>15</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F060A9DEC12A74CAEC81197F47A267F" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9541e711a3f8d554dd3b47338dc6045a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1c221b64-27b2-4021-9af7-79dcbf083a1e" xmlns:ns3="720fc211-b8f9-4216-8e59-f92e385e0bb9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="098a64c75b1331547a23e680aa36f5f3" ns2:_="" ns3:_="">
     <xsd:import namespace="1c221b64-27b2-4021-9af7-79dcbf083a1e"/>
@@ -27247,32 +27223,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{850BD086-9051-4567-AFD1-B7C8873D4F2D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="720fc211-b8f9-4216-8e59-f92e385e0bb9"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="1c221b64-27b2-4021-9af7-79dcbf083a1e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{037A7D67-D63F-48F5-85CA-5FAB13DF5982}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="720fc211-b8f9-4216-8e59-f92e385e0bb9">
+      <UserInfo>
+        <DisplayName>Ankit Jain</DisplayName>
+        <AccountId>34</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Poonam</DisplayName>
+        <AccountId>10</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Rishabh Goyal</DisplayName>
+        <AccountId>15</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD55F499-65CE-441F-9D64-BBB026E75EFE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27289,4 +27273,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{037A7D67-D63F-48F5-85CA-5FAB13DF5982}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{850BD086-9051-4567-AFD1-B7C8873D4F2D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="720fc211-b8f9-4216-8e59-f92e385e0bb9"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="1c221b64-27b2-4021-9af7-79dcbf083a1e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/Overall Collection Summary - May 2026.xlsx
+++ b/data/Overall Collection Summary - May 2026.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr updateLinks="always" codeName="ThisWorkbook" hidePivotFieldList="1"/>
+  <workbookPr updateLinks="always" codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://raghavgroup.sharepoint.com/sites/CRM/Shared Documents/General/LAKSHYA TRACKERS MONTHLY/LAKSHYA CRM TRACKER/LAKSHYA CRM Tracker - May'26/Overall Summary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9943" documentId="8_{AED7C0B6-5B33-4314-A282-567B12F8F8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1960BDF-DBEA-4975-949E-EA98429D7ABA}"/>
+  <xr:revisionPtr revIDLastSave="10070" documentId="8_{AED7C0B6-5B33-4314-A282-567B12F8F8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88A74241-ECAE-4A28-A60C-A236260AB503}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="917" activeTab="2" xr2:uid="{3D2F352B-9E05-401C-B527-666CFC22F994}"/>
+    <workbookView minimized="1" xWindow="2450" yWindow="2210" windowWidth="14400" windowHeight="7270" tabRatio="917" activeTab="2" xr2:uid="{3D2F352B-9E05-401C-B527-666CFC22F994}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="1" r:id="rId1"/>
     <sheet name="Overall - Testing" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="Overall_Draft" sheetId="8" r:id="rId3"/>
-    <sheet name="Reporting" sheetId="3" r:id="rId4"/>
+    <sheet name="Reporting" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId5"/>
@@ -2442,15 +2442,6 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2464,6 +2455,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3144,25 +3144,25 @@
                 <c:formatCode>_("₹"* #,##0.00_);_("₹"* \(#,##0.00\);_("₹"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>1.337979</c:v>
+                  <c:v>2.2578117</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5260024666666663</c:v>
+                  <c:v>2.889856623809524</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.3628282142857149</c:v>
+                  <c:v>4.3864693285714287</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8878342857142858</c:v>
+                  <c:v>4.5381641904761905</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.8064526714285716</c:v>
+                  <c:v>6.5512638047619038</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.91473139999999997</c:v>
+                  <c:v>3.5271965238095242</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3465,25 +3465,25 @@
                       <c:formatCode>0.00%</c:formatCode>
                       <c:ptCount val="7"/>
                       <c:pt idx="0">
-                        <c:v>0.38077896646428716</c:v>
+                        <c:v>0.64255657644624853</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0.42163935669956537</c:v>
+                        <c:v>0.48237375216222106</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.31776064806918003</c:v>
+                        <c:v>0.58990633688695793</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0.26765947829386499</c:v>
+                        <c:v>0.64342652786135135</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0.3452189252037709</c:v>
+                        <c:v>0.59415430707495942</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>0.18368100401606427</c:v>
+                        <c:v>0.70827239433926192</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -3512,7 +3512,7 @@
                           <c:extLst>
                             <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                              <c16:uniqueId val="{00000002-5B51-40AB-9028-F204091FB0C3}"/>
+                              <c16:uniqueId val="{00000002-7D55-4901-83A5-6118285604B0}"/>
                             </c:ext>
                           </c:extLst>
                         </c15:dLbl>
@@ -4246,22 +4246,22 @@
                 <c:formatCode>_("₹"* #,##0.00_);_("₹"* \(#,##0.00\);_("₹"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>6.6289399190476193</c:v>
+                  <c:v>9.3398698904761908</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.62403561904761906</c:v>
+                  <c:v>0.41932514285714284</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.78628523809523809</c:v>
+                  <c:v>1.1091579047619047</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.8716789761904766</c:v>
+                  <c:v>3.4387666428571433</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.55087066666666673</c:v>
+                  <c:v>2.8792148761904763</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.1603028571428569</c:v>
+                  <c:v>8.0735856190476198</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4427,22 +4427,22 @@
                       <c:formatCode>0.00%</c:formatCode>
                       <c:ptCount val="6"/>
                       <c:pt idx="0">
-                        <c:v>0.38745336663015251</c:v>
+                        <c:v>0.54590388163791081</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0.43090005329157366</c:v>
+                        <c:v>0.28954633499830984</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.37802174908424907</c:v>
+                        <c:v>0.53324899267399262</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0.71565110678046417</c:v>
+                        <c:v>0.85697502204272225</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>5.9682629107981222E-2</c:v>
+                        <c:v>0.31194093999896816</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0.25626368412133532</c:v>
+                        <c:v>0.95772071400327641</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -7053,25 +7053,25 @@
                 <c:formatCode>_("₹"* #,##0.00_);_("₹"* \(#,##0.00\);_("₹"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>1.337979</c:v>
+                  <c:v>2.2578117</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5260024666666663</c:v>
+                  <c:v>2.889856623809524</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.9911221190476196</c:v>
+                  <c:v>3.967144185714286</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8878342857142858</c:v>
+                  <c:v>4.5381641904761905</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.6017421952380952</c:v>
+                  <c:v>6.5512638047619038</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.8671123523809523</c:v>
+                  <c:v>3.5271965238095242</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7374,25 +7374,25 @@
                       <c:formatCode>0.00%</c:formatCode>
                       <c:ptCount val="7"/>
                       <c:pt idx="0">
-                        <c:v>0.38077896646428716</c:v>
+                        <c:v>0.64255657644624853</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0.42434614030135703</c:v>
+                        <c:v>0.48547043026292735</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.27517367712009277</c:v>
+                        <c:v>0.54826052244889367</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0.28808177322484135</c:v>
+                        <c:v>0.69251967562566041</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0.34282066162956709</c:v>
+                        <c:v>0.62356172938408871</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>0.18368100401606427</c:v>
+                        <c:v>0.70827239433926192</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -7421,7 +7421,7 @@
                           <c:extLst>
                             <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                              <c16:uniqueId val="{00000002-F287-4E1C-B845-1A467D1A64F1}"/>
+                              <c16:uniqueId val="{00000002-61A7-4FFE-85DE-2B6FE4D63A2C}"/>
                             </c:ext>
                           </c:extLst>
                         </c15:dLbl>
@@ -8023,8 +8023,8 @@
               <c:idx val="1"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="2.3232209487592238E-2"/>
-                  <c:y val="-2.9944114790954199E-2"/>
+                  <c:x val="3.9637825851218528E-2"/>
+                  <c:y val="-6.0169688443978322E-3"/>
                 </c:manualLayout>
               </c:layout>
               <c:dLblPos val="outEnd"/>
@@ -8060,6 +8060,28 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000000-82E5-4CB8-9EF5-0FA63CD8DF35}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="3.7281347830513241E-2"/>
+                  <c:y val="-2.0070004808899577E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-22A1-486E-AD56-4885FBB83F0D}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8179,22 +8201,22 @@
                 <c:formatCode>_("₹"* #,##0.00_);_("₹"* \(#,##0.00\);_("₹"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>6.6289399190476193</c:v>
+                  <c:v>9.3398698904761908</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.4211175190476191</c:v>
+                  <c:v>0.41932514285714284</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.94651043809523805</c:v>
+                  <c:v>1.2693831047619049</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.8716789761904766</c:v>
+                  <c:v>3.4387666428571433</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.55087066666666673</c:v>
+                  <c:v>2.8792148761904763</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.1603028571428569</c:v>
+                  <c:v>8.0735856190476198</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8361,22 +8383,22 @@
                       <c:formatCode>0.00%</c:formatCode>
                       <c:ptCount val="6"/>
                       <c:pt idx="0">
-                        <c:v>0.39273296083919096</c:v>
+                        <c:v>0.55334258580314866</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0.70537744477210818</c:v>
+                        <c:v>0.20813373548128042</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.45505309523809517</c:v>
+                        <c:v>0.61028033882783883</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0.71565110678046417</c:v>
+                        <c:v>0.85697502204272225</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>5.9682629107981222E-2</c:v>
+                        <c:v>0.31194093999896816</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0.25119800664451825</c:v>
+                        <c:v>0.93878902547065346</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -17358,13 +17380,17 @@
       <sheetName val="Working Sheet"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
       <sheetData sheetId="6">
+        <row r="3">
+          <cell r="Q3"/>
+          <cell r="R3"/>
+        </row>
         <row r="7">
           <cell r="B7">
             <v>189</v>
@@ -17373,7 +17399,7 @@
             <v>0</v>
           </cell>
           <cell r="E7">
-            <v>1.337979</v>
+            <v>2.3498838000000002</v>
           </cell>
           <cell r="F7">
             <v>0</v>
@@ -17382,33 +17408,42 @@
             <v>3.5137944000000001</v>
           </cell>
           <cell r="J7">
-            <v>1.337979</v>
+            <v>2.2578117</v>
           </cell>
           <cell r="L7">
             <v>2.19</v>
           </cell>
         </row>
         <row r="8">
+          <cell r="I8"/>
           <cell r="J8">
             <v>0</v>
           </cell>
+          <cell r="L8"/>
         </row>
         <row r="9">
+          <cell r="I9"/>
           <cell r="J9">
             <v>0</v>
           </cell>
+          <cell r="L9"/>
         </row>
         <row r="10">
+          <cell r="I10"/>
           <cell r="J10">
             <v>0</v>
           </cell>
+          <cell r="L10"/>
         </row>
         <row r="11">
+          <cell r="I11"/>
           <cell r="J11">
             <v>0</v>
           </cell>
+          <cell r="L11"/>
         </row>
         <row r="12">
+          <cell r="I12"/>
           <cell r="J12">
             <v>0</v>
           </cell>
@@ -17421,7 +17456,7 @@
             <v>3.5137944000000001</v>
           </cell>
           <cell r="J13">
-            <v>1.337979</v>
+            <v>2.2578117</v>
           </cell>
           <cell r="L13">
             <v>2.19</v>
@@ -17432,10 +17467,10 @@
             <v>208.36912079999999</v>
           </cell>
           <cell r="D14">
-            <v>206.96726649999999</v>
+            <v>208.8346166</v>
           </cell>
           <cell r="E14">
-            <v>2.2594641000000002</v>
+            <v>1.3896314000000001</v>
           </cell>
         </row>
         <row r="18">
@@ -17443,7 +17478,7 @@
             <v>0</v>
           </cell>
           <cell r="L18">
-            <v>2.2594639999999999</v>
+            <v>1.3896313</v>
           </cell>
         </row>
         <row r="19">
@@ -17467,7 +17502,7 @@
             <v>3</v>
           </cell>
           <cell r="F21">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="I21">
             <v>0</v>
@@ -17487,17 +17522,17 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -17528,12 +17563,12 @@
       <sheetName val="Working Sheet"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
       <sheetData sheetId="6">
         <row r="3">
           <cell r="Q3">
@@ -17551,7 +17586,7 @@
             <v>0</v>
           </cell>
           <cell r="E7">
-            <v>2.5260024666666676</v>
+            <v>2.8898566238095249</v>
           </cell>
           <cell r="F7">
             <v>0</v>
@@ -17560,7 +17595,7 @@
             <v>5.9526933952380956</v>
           </cell>
           <cell r="J7">
-            <v>2.5260024666666663</v>
+            <v>2.889856623809524</v>
           </cell>
           <cell r="L7">
             <v>3.15</v>
@@ -17573,42 +17608,51 @@
           <cell r="J8">
             <v>0</v>
           </cell>
+          <cell r="L8"/>
         </row>
         <row r="9">
+          <cell r="I9"/>
           <cell r="J9">
             <v>0</v>
           </cell>
+          <cell r="L9"/>
         </row>
         <row r="10">
+          <cell r="I10"/>
           <cell r="J10">
             <v>0</v>
           </cell>
+          <cell r="L10"/>
         </row>
         <row r="11">
+          <cell r="I11"/>
           <cell r="J11">
             <v>0</v>
           </cell>
+          <cell r="L11"/>
         </row>
         <row r="12">
+          <cell r="I12"/>
           <cell r="J12">
             <v>0</v>
           </cell>
+          <cell r="L12"/>
         </row>
         <row r="13">
           <cell r="C13">
             <v>103.07414780000001</v>
           </cell>
           <cell r="D13">
-            <v>100.57513296666666</v>
+            <v>100.93898712380951</v>
           </cell>
           <cell r="E13">
-            <v>3.2601844095238097</v>
+            <v>2.9382042238095241</v>
           </cell>
           <cell r="I13">
             <v>5.9909076952380955</v>
           </cell>
           <cell r="J13">
-            <v>2.5260024666666663</v>
+            <v>2.889856623809524</v>
           </cell>
           <cell r="L13">
             <v>3.15</v>
@@ -17616,7 +17660,7 @@
         </row>
         <row r="18">
           <cell r="L18">
-            <v>3.2219701095238098</v>
+            <v>2.8999899238095237</v>
           </cell>
         </row>
         <row r="19">
@@ -17646,14 +17690,14 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -17674,13 +17718,14 @@
       <sheetName val="Tracker"/>
       <sheetName val="Collection MTD - LTD"/>
       <sheetName val="Project Summary"/>
+      <sheetName val="Working Sheet"/>
       <sheetName val="2 May 26"/>
       <sheetName val="Payment Schedule "/>
       <sheetName val="Expected Reg"/>
       <sheetName val="Exp flooring from REG"/>
-      <sheetName val="Working Sheet"/>
       <sheetName val="Sheet1"/>
       <sheetName val="Slots"/>
+      <sheetName val="Gap Analysis"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -17700,22 +17745,22 @@
         </row>
         <row r="7">
           <cell r="B7">
-            <v>77</v>
+            <v>78</v>
           </cell>
           <cell r="D7">
             <v>0</v>
           </cell>
           <cell r="E7">
-            <v>2.7321155142857152</v>
+            <v>4.9375963761904789</v>
           </cell>
           <cell r="F7">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="I7">
             <v>1.6341805</v>
           </cell>
           <cell r="J7">
-            <v>0.1388807619047619</v>
+            <v>1.3832997714285715</v>
           </cell>
           <cell r="L7">
             <v>1.23</v>
@@ -17726,7 +17771,7 @@
             <v>0.2</v>
           </cell>
           <cell r="J8">
-            <v>0.37170609523809517</v>
+            <v>0.41932514285714284</v>
           </cell>
           <cell r="L8">
             <v>0.2</v>
@@ -17737,15 +17782,16 @@
             <v>1</v>
           </cell>
           <cell r="J9">
-            <v>0.1857138095238095</v>
+            <v>0.55112704761904763</v>
           </cell>
+          <cell r="L9"/>
         </row>
         <row r="10">
           <cell r="I10">
             <v>1.85169373</v>
           </cell>
           <cell r="J10">
-            <v>1.8522413571428575</v>
+            <v>1.8643365571428574</v>
           </cell>
           <cell r="L10">
             <v>1.85</v>
@@ -17756,7 +17802,7 @@
             <v>2.99</v>
           </cell>
           <cell r="J11">
-            <v>0</v>
+            <v>0.61960128571428563</v>
           </cell>
           <cell r="L11">
             <v>2.99</v>
@@ -17767,7 +17813,7 @@
             <v>0.76</v>
           </cell>
           <cell r="J12">
-            <v>0</v>
+            <v>9.9906571428571414E-2</v>
           </cell>
           <cell r="L12">
             <v>0.76</v>
@@ -17775,31 +17821,31 @@
         </row>
         <row r="13">
           <cell r="C13">
-            <v>49.654334429999999</v>
+            <v>52.623265600000003</v>
           </cell>
           <cell r="D13">
-            <v>49.215646423809524</v>
+            <v>51.599938876190471</v>
           </cell>
           <cell r="E13">
-            <v>1.4952999300000001</v>
+            <v>2.358388404761905</v>
           </cell>
           <cell r="I13">
             <v>7.4358742299999996</v>
           </cell>
           <cell r="J13">
-            <v>2.3628282142857149</v>
+            <v>4.3864693285714287</v>
           </cell>
           <cell r="L13">
             <v>7.03</v>
           </cell>
         </row>
         <row r="18">
-          <cell r="L18">
-            <v>1.495299738095238</v>
+          <cell r="M18">
+            <v>0.86600460952380953</v>
           </cell>
         </row>
         <row r="19">
-          <cell r="L19">
+          <cell r="M19">
             <v>9.9999999999999995E-8</v>
           </cell>
         </row>
@@ -17810,18 +17856,18 @@
           <cell r="F20">
             <v>9</v>
           </cell>
-          <cell r="L20">
+          <cell r="M20">
+            <v>3.5868595238095241E-2</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="M21">
             <v>0</v>
           </cell>
         </row>
-        <row r="21">
-          <cell r="L21">
-            <v>9.190476201474667E-8</v>
-          </cell>
-        </row>
         <row r="22">
-          <cell r="L22">
-            <v>0</v>
+          <cell r="M22">
+            <v>1.4565151000000001</v>
           </cell>
         </row>
       </sheetData>
@@ -17832,6 +17878,7 @@
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -17877,22 +17924,22 @@
         </row>
         <row r="7">
           <cell r="B7">
-            <v>54</v>
+            <v>56</v>
           </cell>
           <cell r="D7">
             <v>0</v>
           </cell>
           <cell r="E7">
-            <v>2.1389462857142854</v>
+            <v>4.8224563857142861</v>
           </cell>
           <cell r="F7">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="I7">
             <v>1.8274214</v>
           </cell>
           <cell r="J7">
-            <v>1.0101445714285715</v>
+            <v>1.531511523809524</v>
           </cell>
           <cell r="L7">
             <v>1.74</v>
@@ -17914,8 +17961,9 @@
             <v>0.7</v>
           </cell>
           <cell r="J9">
-            <v>0.251112</v>
+            <v>0.19523809523809524</v>
           </cell>
+          <cell r="L9"/>
         </row>
         <row r="10">
           <cell r="I10">
@@ -17933,7 +17981,7 @@
             <v>2.96</v>
           </cell>
           <cell r="J11">
-            <v>0.24822390476190476</v>
+            <v>1.9486154285714288</v>
           </cell>
           <cell r="L11">
             <v>2.96</v>
@@ -17944,7 +17992,7 @@
             <v>1.32</v>
           </cell>
           <cell r="J12">
-            <v>0.62946580952380948</v>
+            <v>1.0580372380952381</v>
           </cell>
           <cell r="L12">
             <v>1.32</v>
@@ -17952,19 +18000,19 @@
         </row>
         <row r="13">
           <cell r="C13">
-            <v>36.135609299999999</v>
+            <v>36.268466400000001</v>
           </cell>
           <cell r="D13">
-            <v>35.697580685714279</v>
+            <v>38.381090785714285</v>
           </cell>
           <cell r="E13">
-            <v>1.4995108952380953</v>
+            <v>0.85153347619047615</v>
           </cell>
           <cell r="I13">
             <v>7.0531195000000002</v>
           </cell>
           <cell r="J13">
-            <v>1.8878342857142858</v>
+            <v>4.5381641904761905</v>
           </cell>
           <cell r="L13">
             <v>6.9700000000000006</v>
@@ -17972,23 +18020,23 @@
         </row>
         <row r="18">
           <cell r="L18">
-            <v>0.93933931428571438</v>
+            <v>0.31219203809523804</v>
           </cell>
         </row>
         <row r="19">
           <cell r="L19">
-            <v>0</v>
+            <v>4.3803000000000002E-2</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="F20">
             <v>1</v>
           </cell>
           <cell r="L20">
-            <v>9.745938571428571E-2</v>
+            <v>3.4285704761904755E-2</v>
           </cell>
         </row>
         <row r="21">
@@ -17998,7 +18046,7 @@
         </row>
         <row r="22">
           <cell r="L22">
-            <v>1.7014095238095231E-2</v>
+            <v>1.5554633333333326E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -18055,13 +18103,13 @@
         </row>
         <row r="7">
           <cell r="B7">
-            <v>56</v>
+            <v>57</v>
           </cell>
           <cell r="D7">
             <v>0</v>
           </cell>
           <cell r="E7">
-            <v>3.8064526714285707</v>
+            <v>7.3371716142857135</v>
           </cell>
           <cell r="F7">
             <v>4</v>
@@ -18070,7 +18118,7 @@
             <v>2.410911</v>
           </cell>
           <cell r="J7">
-            <v>1.4609841952380953</v>
+            <v>0.6769339380952375</v>
           </cell>
           <cell r="L7">
             <v>2.1</v>
@@ -18081,7 +18129,7 @@
             <v>0.52</v>
           </cell>
           <cell r="J8">
-            <v>0.20471047619047619</v>
+            <v>0</v>
           </cell>
           <cell r="L8">
             <v>0.52</v>
@@ -18092,15 +18140,16 @@
             <v>0.18</v>
           </cell>
           <cell r="J9">
-            <v>0</v>
+            <v>1.4285714285714284E-2</v>
           </cell>
+          <cell r="L9"/>
         </row>
         <row r="10">
           <cell r="I10">
             <v>1.7152883000000001</v>
           </cell>
           <cell r="J10">
-            <v>1.0194376190476191</v>
+            <v>1.5744300857142859</v>
           </cell>
           <cell r="L10">
             <v>1.71</v>
@@ -18111,7 +18160,7 @@
             <v>2.02</v>
           </cell>
           <cell r="J11">
-            <v>0.30264676190476192</v>
+            <v>0.31099816190476187</v>
           </cell>
           <cell r="L11">
             <v>2.02</v>
@@ -18122,7 +18171,7 @@
             <v>4.3600000000000003</v>
           </cell>
           <cell r="J12">
-            <v>0.81867361904761904</v>
+            <v>3.9889016190476192</v>
           </cell>
           <cell r="L12">
             <v>3.49</v>
@@ -18130,19 +18179,19 @@
         </row>
         <row r="13">
           <cell r="C13">
-            <v>34.304362699999999</v>
+            <v>33.5674992</v>
           </cell>
           <cell r="D13">
-            <v>28.990686871428569</v>
+            <v>31.888382104761909</v>
           </cell>
           <cell r="E13">
-            <v>6.2245148047619034</v>
+            <v>3.282729719047619</v>
           </cell>
           <cell r="I13">
             <v>11.026199300000002</v>
           </cell>
           <cell r="J13">
-            <v>3.8064526714285716</v>
+            <v>6.5512638047619038</v>
           </cell>
           <cell r="L13">
             <v>9.84</v>
@@ -18150,20 +18199,20 @@
         </row>
         <row r="18">
           <cell r="L18">
-            <v>4.1346330333333334</v>
+            <v>1.869566176190476</v>
           </cell>
         </row>
         <row r="19">
           <cell r="L19">
-            <v>0.38415322380952377</v>
+            <v>0.27078962380952376</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>9</v>
+            <v>10</v>
           </cell>
           <cell r="F20">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="L20">
             <v>0</v>
@@ -18171,12 +18220,12 @@
         </row>
         <row r="21">
           <cell r="L21">
-            <v>0.79152638095238093</v>
+            <v>0.23760991904761902</v>
           </cell>
         </row>
         <row r="22">
           <cell r="L22">
-            <v>0.91420216666666665</v>
+            <v>0.90476400000000001</v>
           </cell>
         </row>
       </sheetData>
@@ -18209,6 +18258,7 @@
       <sheetName val="Collection MTD - LTD"/>
       <sheetName val="Project Summary"/>
       <sheetName val="Payment Schedule"/>
+      <sheetName val="Sheet2"/>
       <sheetName val="Sheet1"/>
       <sheetName val="Working Sheet"/>
       <sheetName val="Slots"/>
@@ -18231,13 +18281,13 @@
         </row>
         <row r="7">
           <cell r="B7">
-            <v>18</v>
+            <v>17</v>
           </cell>
           <cell r="D7">
             <v>0</v>
           </cell>
           <cell r="E7">
-            <v>0.95730709999999997</v>
+            <v>1.2688853</v>
           </cell>
           <cell r="F7">
             <v>0</v>
@@ -18248,19 +18298,23 @@
           <cell r="J7">
             <v>0</v>
           </cell>
+          <cell r="L7"/>
         </row>
         <row r="8">
           <cell r="I8">
             <v>0.5664766</v>
           </cell>
           <cell r="J8">
-            <v>0.79708190000000001</v>
+            <v>0</v>
           </cell>
+          <cell r="L8"/>
         </row>
         <row r="9">
+          <cell r="I9"/>
           <cell r="J9">
             <v>0.16022520000000001</v>
           </cell>
+          <cell r="L9"/>
         </row>
         <row r="10">
           <cell r="I10">
@@ -18269,6 +18323,7 @@
           <cell r="J10">
             <v>0</v>
           </cell>
+          <cell r="L10"/>
         </row>
         <row r="11">
           <cell r="I11">
@@ -18277,6 +18332,7 @@
           <cell r="J11">
             <v>0</v>
           </cell>
+          <cell r="L11"/>
         </row>
         <row r="12">
           <cell r="I12">
@@ -18285,22 +18341,23 @@
           <cell r="J12">
             <v>0</v>
           </cell>
+          <cell r="L12"/>
         </row>
         <row r="13">
           <cell r="C13">
             <v>4.6401152000000003</v>
           </cell>
           <cell r="D13">
-            <v>2.5436453000000001</v>
+            <v>2.8052234999999999</v>
           </cell>
           <cell r="E13">
-            <v>2.9440563000000002</v>
+            <v>2.6824781</v>
           </cell>
           <cell r="I13">
             <v>0.73647660000000004</v>
           </cell>
           <cell r="J13">
-            <v>0.79708190000000001</v>
+            <v>0</v>
           </cell>
           <cell r="L13">
             <v>0</v>
@@ -18319,15 +18376,15 @@
             <v>0</v>
           </cell>
           <cell r="L19">
-            <v>2.7761472</v>
+            <v>2.5145689999999998</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>15</v>
+            <v>14</v>
           </cell>
           <cell r="F20">
-            <v>7</v>
+            <v>10</v>
           </cell>
           <cell r="I20">
             <v>0</v>
@@ -18362,6 +18419,7 @@
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -18413,7 +18471,7 @@
             <v>0</v>
           </cell>
           <cell r="E7">
-            <v>1.2641908285714285</v>
+            <v>3.92332261904762</v>
           </cell>
           <cell r="F7">
             <v>1</v>
@@ -18422,7 +18480,7 @@
             <v>1.54</v>
           </cell>
           <cell r="J7">
-            <v>0.15494892380952385</v>
+            <v>0.60045633333333326</v>
           </cell>
           <cell r="L7">
             <v>1.3</v>
@@ -18433,7 +18491,7 @@
             <v>0.19</v>
           </cell>
           <cell r="J8">
-            <v>4.7619047619047623E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L8">
             <v>0.19</v>
@@ -18444,13 +18502,16 @@
             <v>0.2</v>
           </cell>
           <cell r="J9">
-            <v>0.34945942857142859</v>
+            <v>0.34850704761904766</v>
           </cell>
+          <cell r="L9"/>
         </row>
         <row r="10">
+          <cell r="I10"/>
           <cell r="J10">
             <v>0</v>
           </cell>
+          <cell r="L10"/>
         </row>
         <row r="11">
           <cell r="I11">
@@ -18468,7 +18529,7 @@
             <v>1.99</v>
           </cell>
           <cell r="J12">
-            <v>0.71216342857142856</v>
+            <v>2.9267401904761905</v>
           </cell>
           <cell r="L12">
             <v>1.99</v>
@@ -18479,19 +18540,19 @@
             <v>24.316816500000002</v>
           </cell>
           <cell r="D13">
-            <v>19.54784562857143</v>
+            <v>22.224215519047622</v>
           </cell>
           <cell r="E13">
-            <v>4.8549033190476196</v>
+            <v>2.1785335666666672</v>
           </cell>
           <cell r="I13">
             <v>4.9799999999999995</v>
           </cell>
           <cell r="J13">
-            <v>0.91473139999999997</v>
+            <v>3.5271965238095242</v>
           </cell>
           <cell r="K13">
-            <v>0.18368100401606427</v>
+            <v>0.70827239433926192</v>
           </cell>
           <cell r="L13">
             <v>4.74</v>
@@ -18499,7 +18560,7 @@
         </row>
         <row r="18">
           <cell r="L18">
-            <v>4.8191245476190474</v>
+            <v>2.1418024142857144</v>
           </cell>
         </row>
         <row r="19">
@@ -18515,7 +18576,7 @@
             <v>1</v>
           </cell>
           <cell r="L20">
-            <v>3.5778771428571408E-2</v>
+            <v>3.6731152380952356E-2</v>
           </cell>
         </row>
         <row r="21">
@@ -18665,10 +18726,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18990,43 +19047,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439E3C76-FA5F-47B8-A56E-AEDB699F28E9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:AN60"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="66.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="0.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="0.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="62.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="29.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="1.44140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="69.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.88671875" style="1"/>
-    <col min="12" max="12" width="44.5546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="19.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="66.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="0.54296875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="0.90625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="62.90625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.54296875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="29.453125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="1.453125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="69.453125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.90625" style="1"/>
+    <col min="12" max="12" width="44.54296875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19.453125" style="1" customWidth="1"/>
     <col min="14" max="14" width="24" style="1" customWidth="1"/>
-    <col min="15" max="15" width="24.44140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="29.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.453125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="29.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="21" style="1" customWidth="1"/>
-    <col min="18" max="18" width="15.5546875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="44.44140625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="21.5546875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="20.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="15.54296875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="44.453125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="21.54296875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="20.54296875" style="1" customWidth="1"/>
     <col min="22" max="22" width="37" style="1" customWidth="1"/>
-    <col min="23" max="23" width="23.44140625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="30.6640625" style="1" customWidth="1"/>
-    <col min="25" max="26" width="19.5546875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="30.44140625" style="1" customWidth="1"/>
-    <col min="28" max="28" width="25.5546875" style="1" customWidth="1"/>
-    <col min="29" max="31" width="17.109375" style="1" customWidth="1"/>
-    <col min="32" max="32" width="30.109375" style="91" customWidth="1"/>
-    <col min="33" max="36" width="17.109375" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.5546875" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="8.88671875" style="1"/>
+    <col min="23" max="23" width="23.453125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="30.6328125" style="1" customWidth="1"/>
+    <col min="25" max="26" width="19.54296875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="30.453125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="25.54296875" style="1" customWidth="1"/>
+    <col min="29" max="31" width="17.08984375" style="1" customWidth="1"/>
+    <col min="32" max="32" width="30.08984375" style="91" customWidth="1"/>
+    <col min="33" max="36" width="17.08984375" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.54296875" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:32" s="95" customFormat="1" ht="47.4" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="1" spans="2:32" s="95" customFormat="1" ht="47.4" customHeight="1" x14ac:dyDescent="0.95">
       <c r="B1" s="228" t="s">
         <v>0</v>
       </c>
@@ -19039,7 +19096,7 @@
       <c r="H1" s="97"/>
       <c r="I1" s="98">
         <f ca="1">TODAY()</f>
-        <v>46165</v>
+        <v>46176</v>
       </c>
       <c r="L1" s="110"/>
       <c r="M1" s="110" t="s">
@@ -19049,7 +19106,7 @@
       <c r="O1" s="110"/>
       <c r="AF1" s="99"/>
     </row>
-    <row r="2" spans="2:32" s="78" customFormat="1" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:32" s="78" customFormat="1" ht="48.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="B2" s="229" t="s">
         <v>3</v>
       </c>
@@ -19065,19 +19122,19 @@
       <c r="J2" s="77"/>
       <c r="AF2" s="90"/>
     </row>
-    <row r="3" spans="2:32" ht="134.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:32" ht="134.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="100" t="str">
         <f>CONCATENATE("₹ ",ROUND($N$27,2)," / ",ROUND($M$27,2)," (",ROUND($O$27,3)*100,"%)")</f>
-        <v>₹ 12.84 / 40.23 (31.9%)</v>
+        <v>₹ 24.15 / 40.23 (60%)</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="85" t="str">
-        <f ca="1">CONCATENATE("₹ ",ROUND($N$11,2), "  |  ", "₹ ",ROUND($O$11,2))</f>
-        <v>₹ 0  |  ₹ 13.81</v>
+        <f>CONCATENATE("₹ ",ROUND($N$11,2), "  |  ", "₹ ",ROUND($O$11,2))</f>
+        <v>₹ 0  |  ₹ 26.26</v>
       </c>
       <c r="G3" s="242" t="str">
-        <f ca="1">CONCATENATE($U$11, "    |    ", $T$11)</f>
-        <v>20    |    38</v>
+        <f>CONCATENATE($U$11, "    |    ", $T$11)</f>
+        <v>23    |    40</v>
       </c>
       <c r="H3" s="243"/>
       <c r="I3" s="244"/>
@@ -19123,7 +19180,7 @@
       <c r="Y3" s="66"/>
       <c r="Z3" s="66"/>
     </row>
-    <row r="4" spans="2:32" s="72" customFormat="1" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:32" s="72" customFormat="1" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B4" s="27" t="s">
         <v>8</v>
       </c>
@@ -19149,7 +19206,7 @@
       </c>
       <c r="O4" s="101">
         <f>'[1]Project Summary'!$E$7</f>
-        <v>1.337979</v>
+        <v>2.3498838000000002</v>
       </c>
       <c r="P4" s="104">
         <f>'[1]Project Summary'!$F$7</f>
@@ -19161,11 +19218,11 @@
       </c>
       <c r="R4" s="79">
         <f>'[1]Project Summary'!$D$14</f>
-        <v>206.96726649999999</v>
+        <v>208.8346166</v>
       </c>
       <c r="S4" s="79">
         <f>'[1]Project Summary'!$E$14</f>
-        <v>2.2594641000000002</v>
+        <v>1.3896314000000001</v>
       </c>
       <c r="T4" s="69">
         <f>'[1]Project Summary'!$D$21</f>
@@ -19173,7 +19230,7 @@
       </c>
       <c r="U4" s="69">
         <f>'[1]Project Summary'!$F$21</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V4" s="69">
         <f>'[1]Project Summary'!$Q$3</f>
@@ -19190,7 +19247,7 @@
       <c r="Z4" s="75"/>
       <c r="AF4" s="92"/>
     </row>
-    <row r="5" spans="2:32" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:32" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L5" s="109" t="s">
         <v>20</v>
       </c>
@@ -19204,7 +19261,7 @@
       </c>
       <c r="O5" s="102">
         <f>'[2]Project Summary'!$E$7</f>
-        <v>2.5260024666666676</v>
+        <v>2.8898566238095249</v>
       </c>
       <c r="P5" s="105">
         <f>'[2]Project Summary'!$F$7</f>
@@ -19216,11 +19273,11 @@
       </c>
       <c r="R5" s="82">
         <f>'[2]Project Summary'!$D$13</f>
-        <v>100.57513296666666</v>
+        <v>100.93898712380951</v>
       </c>
       <c r="S5" s="82">
         <f>'[2]Project Summary'!$E$13</f>
-        <v>3.2601844095238097</v>
+        <v>2.9382042238095241</v>
       </c>
       <c r="T5" s="69">
         <f>'[2]Project Summary'!$D$20</f>
@@ -19247,10 +19304,10 @@
       </c>
       <c r="Z5" s="66"/>
     </row>
-    <row r="6" spans="2:32" ht="135" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:32" ht="135" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="84">
         <f>$S$11</f>
-        <v>19.822732958571429</v>
+        <v>13.227876290476191</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="9"/>
@@ -19260,7 +19317,7 @@
       </c>
       <c r="G6" s="248" t="str">
         <f>CONCATENATE($P$11," / ",V11)</f>
-        <v>9 / 15</v>
+        <v>11 / 15</v>
       </c>
       <c r="H6" s="249"/>
       <c r="I6" s="250"/>
@@ -19269,38 +19326,38 @@
       </c>
       <c r="M6" s="69">
         <f>'[3]Project Summary'!$B$7</f>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N6" s="102">
-        <f ca="1">'[3]Project Summary'!$D$7</f>
+        <f>'[3]Project Summary'!$D$7</f>
         <v>0</v>
       </c>
       <c r="O6" s="102">
         <f>'[3]Project Summary'!$E$7</f>
-        <v>2.7321155142857152</v>
+        <v>4.9375963761904789</v>
       </c>
       <c r="P6" s="105">
         <f>'[3]Project Summary'!$F$7</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="82">
         <f>'[3]Project Summary'!$C$13</f>
-        <v>49.654334429999999</v>
+        <v>52.623265600000003</v>
       </c>
       <c r="R6" s="82">
         <f>'[3]Project Summary'!$D$13</f>
-        <v>49.215646423809524</v>
+        <v>51.599938876190471</v>
       </c>
       <c r="S6" s="82">
         <f>'[3]Project Summary'!$E$13</f>
-        <v>1.4952999300000001</v>
+        <v>2.358388404761905</v>
       </c>
       <c r="T6" s="69">
         <f>'[3]Project Summary'!$D$20</f>
         <v>16</v>
       </c>
       <c r="U6" s="69">
-        <f ca="1">'[3]Project Summary'!$F$20</f>
+        <f>'[3]Project Summary'!$F$20</f>
         <v>9</v>
       </c>
       <c r="V6" s="69">
@@ -19317,7 +19374,7 @@
       <c r="Y6" s="68"/>
       <c r="Z6" s="66"/>
     </row>
-    <row r="7" spans="2:32" s="28" customFormat="1" ht="40.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:32" s="28" customFormat="1" ht="40.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="27" t="s">
         <v>22</v>
       </c>
@@ -19336,38 +19393,38 @@
       </c>
       <c r="M7" s="69">
         <f>'[4]Project Summary'!$B$7</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N7" s="102">
-        <f ca="1">'[4]Project Summary'!$D$7</f>
+        <f>'[4]Project Summary'!$D$7</f>
         <v>0</v>
       </c>
       <c r="O7" s="102">
         <f>'[4]Project Summary'!$E$7</f>
-        <v>2.1389462857142854</v>
+        <v>4.8224563857142861</v>
       </c>
       <c r="P7" s="105">
         <f>'[4]Project Summary'!$F$7</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q7" s="82">
         <f>'[4]Project Summary'!$C$13</f>
-        <v>36.135609299999999</v>
+        <v>36.268466400000001</v>
       </c>
       <c r="R7" s="82">
         <f>'[4]Project Summary'!$D$13</f>
-        <v>35.697580685714279</v>
+        <v>38.381090785714285</v>
       </c>
       <c r="S7" s="82">
         <f>'[4]Project Summary'!$E$13</f>
-        <v>1.4995108952380953</v>
+        <v>0.85153347619047615</v>
       </c>
       <c r="T7" s="69">
         <f>'[4]Project Summary'!$D$20</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7" s="69">
-        <f ca="1">'[4]Project Summary'!$F$20</f>
+        <f>'[4]Project Summary'!$F$20</f>
         <v>1</v>
       </c>
       <c r="V7" s="69">
@@ -19385,21 +19442,21 @@
       <c r="Z7" s="71"/>
       <c r="AF7" s="93"/>
     </row>
-    <row r="8" spans="2:32" s="28" customFormat="1" ht="28.35" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:32" s="28" customFormat="1" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="L8" s="109" t="s">
         <v>26</v>
       </c>
       <c r="M8" s="69">
         <f>'[5]Project Summary'!$B$7</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N8" s="102">
-        <f ca="1">'[5]Project Summary'!$D$7</f>
+        <f>'[5]Project Summary'!$D$7</f>
         <v>0</v>
       </c>
       <c r="O8" s="102">
         <f>'[5]Project Summary'!$E$7</f>
-        <v>3.8064526714285707</v>
+        <v>7.3371716142857135</v>
       </c>
       <c r="P8" s="105">
         <f>'[5]Project Summary'!$F$7</f>
@@ -19407,23 +19464,23 @@
       </c>
       <c r="Q8" s="82">
         <f>'[5]Project Summary'!$C$13</f>
-        <v>34.304362699999999</v>
+        <v>33.5674992</v>
       </c>
       <c r="R8" s="82">
         <f>'[5]Project Summary'!$D$13</f>
-        <v>28.990686871428569</v>
+        <v>31.888382104761909</v>
       </c>
       <c r="S8" s="82">
         <f>'[5]Project Summary'!$E$13</f>
-        <v>6.2245148047619034</v>
+        <v>3.282729719047619</v>
       </c>
       <c r="T8" s="69">
         <f>'[5]Project Summary'!$D$20</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8" s="69">
-        <f ca="1">'[5]Project Summary'!$F$20</f>
-        <v>5</v>
+        <f>'[5]Project Summary'!$F$20</f>
+        <v>7</v>
       </c>
       <c r="V8" s="69">
         <f>'[5]Project Summary'!$Q$3</f>
@@ -19438,7 +19495,7 @@
       <c r="Z8" s="71"/>
       <c r="AF8" s="93"/>
     </row>
-    <row r="9" spans="2:32" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:32" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L9" s="109" t="s">
         <v>27</v>
       </c>
@@ -19492,7 +19549,7 @@
       <c r="Y9" s="68"/>
       <c r="Z9" s="66"/>
     </row>
-    <row r="10" spans="2:32" ht="18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:32" ht="18" x14ac:dyDescent="0.3">
       <c r="L10" s="109" t="s">
         <v>28</v>
       </c>
@@ -19501,12 +19558,12 @@
         <v>25</v>
       </c>
       <c r="N10" s="102">
-        <f ca="1">'[7]Project Summary'!$D$7</f>
+        <f>'[7]Project Summary'!$D$7</f>
         <v>0</v>
       </c>
       <c r="O10" s="103">
         <f>'[7]Project Summary'!$E$7</f>
-        <v>1.2641908285714285</v>
+        <v>3.92332261904762</v>
       </c>
       <c r="P10" s="106">
         <f>'[7]Project Summary'!$F$7</f>
@@ -19518,18 +19575,18 @@
       </c>
       <c r="R10" s="82">
         <f>'[7]Project Summary'!$D$13</f>
-        <v>19.54784562857143</v>
+        <v>22.224215519047622</v>
       </c>
       <c r="S10" s="82">
         <f>'[7]Project Summary'!$E$13</f>
-        <v>4.8549033190476196</v>
+        <v>2.1785335666666672</v>
       </c>
       <c r="T10" s="69">
         <f>'[7]Project Summary'!$D$20</f>
         <v>3</v>
       </c>
       <c r="U10" s="69">
-        <f ca="1">'[7]Project Summary'!$F$20</f>
+        <f>'[7]Project Summary'!$F$20</f>
         <v>1</v>
       </c>
       <c r="V10" s="69">
@@ -19546,45 +19603,45 @@
       <c r="Y10" s="68"/>
       <c r="Z10" s="66"/>
     </row>
-    <row r="11" spans="2:32" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:32" ht="17.5" x14ac:dyDescent="0.3">
       <c r="L11" s="116" t="s">
         <v>29</v>
       </c>
       <c r="M11" s="117">
         <f>SUM(M4:M10)</f>
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="N11" s="118">
-        <f t="shared" ref="N11:W11" ca="1" si="0">SUM(N4:N10)</f>
+        <f t="shared" ref="N11:W11" si="0">SUM(N4:N10)</f>
         <v>0</v>
       </c>
       <c r="O11" s="118">
         <f>SUM(O4:O10)</f>
-        <v>13.805686766666668</v>
+        <v>26.260287419047625</v>
       </c>
       <c r="P11" s="119">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q11" s="120">
         <f t="shared" si="0"/>
-        <v>534.44098363000001</v>
+        <v>536.80590840000002</v>
       </c>
       <c r="R11" s="120">
         <f t="shared" si="0"/>
-        <v>519.35189567619045</v>
+        <v>532.22496760952379</v>
       </c>
       <c r="S11" s="120">
         <f t="shared" si="0"/>
-        <v>19.822732958571429</v>
+        <v>13.227876290476191</v>
       </c>
       <c r="T11" s="121">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U11" s="121">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>23</v>
       </c>
       <c r="V11" s="121">
         <f t="shared" si="0"/>
@@ -19601,30 +19658,30 @@
       <c r="Y11" s="66"/>
       <c r="Z11" s="66"/>
     </row>
-    <row r="12" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.3">
       <c r="Y12" s="66"/>
       <c r="Z12" s="66"/>
     </row>
-    <row r="13" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.3">
       <c r="Y13" s="66"/>
       <c r="Z13" s="66"/>
     </row>
-    <row r="14" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.3">
       <c r="Y14" s="66"/>
       <c r="Z14" s="66"/>
     </row>
-    <row r="15" spans="2:32" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:32" ht="35.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y15" s="66"/>
       <c r="Z15" s="66"/>
     </row>
-    <row r="16" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
     </row>
-    <row r="18" spans="2:32" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:32" ht="22.5" x14ac:dyDescent="0.3">
       <c r="L18" s="234" t="s">
         <v>30</v>
       </c>
@@ -19639,7 +19696,7 @@
       <c r="V18" s="233"/>
       <c r="AF18" s="1"/>
     </row>
-    <row r="19" spans="2:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L19" s="6" t="s">
         <v>32</v>
       </c>
@@ -19676,7 +19733,7 @@
       </c>
       <c r="AF19" s="1"/>
     </row>
-    <row r="20" spans="2:32" ht="31.2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:32" ht="31" x14ac:dyDescent="0.3">
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
       <c r="D20" s="17"/>
@@ -19689,11 +19746,11 @@
       </c>
       <c r="N20" s="18">
         <f>'[1]Project Summary'!$J$13</f>
-        <v>1.337979</v>
+        <v>2.2578117</v>
       </c>
       <c r="O20" s="19">
         <f t="shared" ref="O20:O25" si="1">N20/M20</f>
-        <v>0.38077896646428716</v>
+        <v>0.64255657644624853</v>
       </c>
       <c r="P20" s="18">
         <f>'[1]Project Summary'!$L$13</f>
@@ -19701,7 +19758,7 @@
       </c>
       <c r="Q20" s="153">
         <f>M20-N20</f>
-        <v>2.1758154000000003</v>
+        <v>1.2559827000000001</v>
       </c>
       <c r="S20" s="65" t="s">
         <v>41</v>
@@ -19712,11 +19769,11 @@
       </c>
       <c r="U20" s="64">
         <f>N43</f>
-        <v>6.6289399190476193</v>
+        <v>9.3398698904761908</v>
       </c>
       <c r="V20" s="88">
         <f>O43</f>
-        <v>0.38745336663015251</v>
+        <v>0.54590388163791081</v>
       </c>
       <c r="W20" s="64">
         <f>P43</f>
@@ -19728,7 +19785,7 @@
       </c>
       <c r="AF20" s="1"/>
     </row>
-    <row r="21" spans="2:32" ht="31.2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:32" ht="31" x14ac:dyDescent="0.3">
       <c r="L21" s="30" t="s">
         <v>42</v>
       </c>
@@ -19738,11 +19795,11 @@
       </c>
       <c r="N21" s="18">
         <f>'[2]Project Summary'!$J$13</f>
-        <v>2.5260024666666663</v>
+        <v>2.889856623809524</v>
       </c>
       <c r="O21" s="19">
         <f t="shared" si="1"/>
-        <v>0.42163935669956537</v>
+        <v>0.48237375216222106</v>
       </c>
       <c r="P21" s="18">
         <f>'[2]Project Summary'!$L$13</f>
@@ -19750,7 +19807,7 @@
       </c>
       <c r="Q21" s="153">
         <f t="shared" ref="Q21:Q27" si="2">M21-N21</f>
-        <v>3.4649052285714292</v>
+        <v>3.1010510714285715</v>
       </c>
       <c r="S21" s="65" t="s">
         <v>43</v>
@@ -19761,11 +19818,11 @@
       </c>
       <c r="U21" s="64">
         <f>R43</f>
-        <v>0.62403561904761906</v>
+        <v>0.41932514285714284</v>
       </c>
       <c r="V21" s="88">
         <f>S43</f>
-        <v>0.43090005329157366</v>
+        <v>0.28954633499830984</v>
       </c>
       <c r="W21" s="64">
         <f>T43</f>
@@ -19777,7 +19834,7 @@
       </c>
       <c r="AF21" s="1"/>
     </row>
-    <row r="22" spans="2:32" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:32" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L22" s="30" t="s">
         <v>44</v>
       </c>
@@ -19787,11 +19844,11 @@
       </c>
       <c r="N22" s="18">
         <f>'[3]Project Summary'!$J$13</f>
-        <v>2.3628282142857149</v>
+        <v>4.3864693285714287</v>
       </c>
       <c r="O22" s="19">
         <f t="shared" si="1"/>
-        <v>0.31776064806918003</v>
+        <v>0.58990633688695793</v>
       </c>
       <c r="P22" s="18">
         <f>'[3]Project Summary'!$L$13</f>
@@ -19799,7 +19856,7 @@
       </c>
       <c r="Q22" s="153">
         <f t="shared" si="2"/>
-        <v>5.0730460157142847</v>
+        <v>3.0494049014285709</v>
       </c>
       <c r="S22" s="65" t="s">
         <v>45</v>
@@ -19810,11 +19867,11 @@
       </c>
       <c r="U22" s="64">
         <f>V43</f>
-        <v>0.78628523809523809</v>
+        <v>1.1091579047619047</v>
       </c>
       <c r="V22" s="88">
         <f>W43</f>
-        <v>0.37802174908424907</v>
+        <v>0.53324899267399262</v>
       </c>
       <c r="W22" s="64">
         <f>X43</f>
@@ -19826,7 +19883,7 @@
       </c>
       <c r="AF22" s="1"/>
     </row>
-    <row r="23" spans="2:32" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:32" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L23" s="30" t="s">
         <v>46</v>
       </c>
@@ -19836,11 +19893,11 @@
       </c>
       <c r="N23" s="18">
         <f>'[4]Project Summary'!$J$13</f>
-        <v>1.8878342857142858</v>
+        <v>4.5381641904761905</v>
       </c>
       <c r="O23" s="19">
         <f>N23/M23</f>
-        <v>0.26765947829386499</v>
+        <v>0.64342652786135135</v>
       </c>
       <c r="P23" s="18">
         <f>'[4]Project Summary'!$L$13</f>
@@ -19848,7 +19905,7 @@
       </c>
       <c r="Q23" s="153">
         <f t="shared" si="2"/>
-        <v>5.1652852142857144</v>
+        <v>2.5149553095238097</v>
       </c>
       <c r="S23" s="65" t="str">
         <f>CONCATENATE("Demand For Registrations 
@@ -19862,11 +19919,11 @@
       </c>
       <c r="U23" s="64">
         <f>Z43</f>
-        <v>2.8716789761904766</v>
+        <v>3.4387666428571433</v>
       </c>
       <c r="V23" s="88">
         <f>AA43</f>
-        <v>0.71565110678046417</v>
+        <v>0.85697502204272225</v>
       </c>
       <c r="W23" s="64">
         <f>AB43</f>
@@ -19878,7 +19935,7 @@
       </c>
       <c r="AF23" s="1"/>
     </row>
-    <row r="24" spans="2:32" ht="34.799999999999997" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:32" ht="35" x14ac:dyDescent="0.3">
       <c r="L24" s="123" t="s">
         <v>47</v>
       </c>
@@ -19888,11 +19945,11 @@
       </c>
       <c r="N24" s="18">
         <f>'[5]Project Summary'!$J$13</f>
-        <v>3.8064526714285716</v>
+        <v>6.5512638047619038</v>
       </c>
       <c r="O24" s="19">
         <f>N24/M24</f>
-        <v>0.3452189252037709</v>
+        <v>0.59415430707495942</v>
       </c>
       <c r="P24" s="18">
         <f>'[5]Project Summary'!$L$13</f>
@@ -19914,11 +19971,11 @@
       </c>
       <c r="U24" s="64">
         <f>AD43</f>
-        <v>0.55087066666666673</v>
+        <v>2.8792148761904763</v>
       </c>
       <c r="V24" s="88">
         <f>AE43</f>
-        <v>5.9682629107981222E-2</v>
+        <v>0.31194093999896816</v>
       </c>
       <c r="W24" s="64">
         <f>AF43</f>
@@ -19930,7 +19987,7 @@
       </c>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="2:32" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:32" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L25" s="30" t="s">
         <v>48</v>
       </c>
@@ -19963,11 +20020,11 @@
       </c>
       <c r="U25" s="64">
         <f>AH43</f>
-        <v>2.1603028571428569</v>
+        <v>8.0735856190476198</v>
       </c>
       <c r="V25" s="88">
         <f>AI43</f>
-        <v>0.25626368412133532</v>
+        <v>0.95772071400327641</v>
       </c>
       <c r="W25" s="64">
         <f>AJ43</f>
@@ -19979,7 +20036,7 @@
       </c>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="2:32" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:32" ht="28" x14ac:dyDescent="0.3">
       <c r="L26" s="30" t="s">
         <v>50</v>
       </c>
@@ -19989,11 +20046,11 @@
       </c>
       <c r="N26" s="18">
         <f>'[7]Project Summary'!$J$13</f>
-        <v>0.91473139999999997</v>
+        <v>3.5271965238095242</v>
       </c>
       <c r="O26" s="19">
         <f>'[7]Project Summary'!$K$13</f>
-        <v>0.18368100401606427</v>
+        <v>0.70827239433926192</v>
       </c>
       <c r="P26" s="18">
         <f>'[7]Project Summary'!$L$13</f>
@@ -20001,11 +20058,11 @@
       </c>
       <c r="Q26" s="153">
         <f t="shared" si="2"/>
-        <v>4.0652685999999996</v>
+        <v>1.4528034761904753</v>
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="2:32" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:32" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L27" s="24" t="s">
         <v>51</v>
       </c>
@@ -20015,11 +20072,11 @@
       </c>
       <c r="N27" s="18">
         <f>SUM(N20:N26)</f>
-        <v>12.835828038095237</v>
+        <v>24.150762171428571</v>
       </c>
       <c r="O27" s="19">
         <f>N27/M27</f>
-        <v>0.31906193138551642</v>
+        <v>0.60031879517075037</v>
       </c>
       <c r="P27" s="18">
         <f>SUM(P20:P26)</f>
@@ -20027,20 +20084,20 @@
       </c>
       <c r="Q27" s="153">
         <f t="shared" si="2"/>
-        <v>27.394067087142851</v>
+        <v>16.079132953809516</v>
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="2:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="P28" s="86"/>
       <c r="Q28" s="10"/>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="2:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="P29" s="86"/>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="2:32" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:32" ht="37.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E30" s="148"/>
       <c r="L30" s="89"/>
       <c r="M30" s="89"/>
@@ -20048,10 +20105,10 @@
       <c r="O30" s="89"/>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:32" x14ac:dyDescent="0.3">
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="2:32" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:32" ht="16" x14ac:dyDescent="0.3">
       <c r="L32" s="54"/>
       <c r="M32" s="54"/>
       <c r="N32" s="54"/>
@@ -20059,7 +20116,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="54"/>
     </row>
-    <row r="33" spans="7:40" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="7:40" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L33" s="55"/>
       <c r="M33" s="56"/>
       <c r="N33" s="56"/>
@@ -20067,7 +20124,7 @@
       <c r="P33" s="56"/>
       <c r="Q33" s="56"/>
     </row>
-    <row r="34" spans="7:40" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="7:40" ht="32.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L34" s="55"/>
       <c r="M34" s="230" t="s">
         <v>52</v>
@@ -20096,8 +20153,8 @@
       <c r="AA34" s="231"/>
       <c r="AB34" s="235"/>
       <c r="AC34" s="230" t="str">
-        <f ca="1">CONCATENATE("Expected Registrations in August ",$D$3,"'",$E$3," ")</f>
-        <v xml:space="preserve">Expected Registrations in August '₹ 0  |  ₹ 13.81 </v>
+        <f>CONCATENATE("Expected Registrations in August ",$D$3,"'",$E$3," ")</f>
+        <v xml:space="preserve">Expected Registrations in August '₹ 0  |  ₹ 26.26 </v>
       </c>
       <c r="AD34" s="231"/>
       <c r="AE34" s="231"/>
@@ -20109,7 +20166,7 @@
       <c r="AI34" s="231"/>
       <c r="AJ34" s="232"/>
     </row>
-    <row r="35" spans="7:40" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="7:40" ht="30.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L35" s="135" t="s">
         <v>55</v>
       </c>
@@ -20186,7 +20243,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="7:40" ht="101.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:40" ht="101.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G36" s="1" t="s">
         <v>58</v>
       </c>
@@ -20200,11 +20257,11 @@
       </c>
       <c r="N36" s="128">
         <f>'[1]Project Summary'!$J$7</f>
-        <v>1.337979</v>
+        <v>2.2578117</v>
       </c>
       <c r="O36" s="129">
         <f t="shared" ref="O36:O42" si="4">N36/M36</f>
-        <v>0.38077896646428716</v>
+        <v>0.64255657644624853</v>
       </c>
       <c r="P36" s="145">
         <f>'[1]Project Summary'!$L$7</f>
@@ -20293,7 +20350,7 @@
       <c r="AL36" s="87"/>
       <c r="AN36" s="87"/>
     </row>
-    <row r="37" spans="7:40" ht="155.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:40" ht="155.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I37" s="150"/>
       <c r="L37" s="137" t="s">
         <v>60</v>
@@ -20304,11 +20361,11 @@
       </c>
       <c r="N37" s="63">
         <f>'[2]Project Summary'!$J$7</f>
-        <v>2.5260024666666663</v>
+        <v>2.889856623809524</v>
       </c>
       <c r="O37" s="88">
         <f t="shared" si="4"/>
-        <v>0.42434614030135703</v>
+        <v>0.48547043026292735</v>
       </c>
       <c r="P37" s="146">
         <f>'[2]Project Summary'!$L$7</f>
@@ -20401,7 +20458,7 @@
       <c r="AL37" s="87"/>
       <c r="AN37" s="87"/>
     </row>
-    <row r="38" spans="7:40" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:40" ht="38.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I38" s="148"/>
       <c r="L38" s="30" t="s">
         <v>44</v>
@@ -20412,11 +20469,11 @@
       </c>
       <c r="N38" s="63">
         <f>'[3]Project Summary'!$J$7</f>
-        <v>0.1388807619047619</v>
+        <v>1.3832997714285715</v>
       </c>
       <c r="O38" s="88">
         <f t="shared" si="4"/>
-        <v>8.4984958457625631E-2</v>
+        <v>0.84647918111161613</v>
       </c>
       <c r="P38" s="146">
         <f>'[3]Project Summary'!$L$7</f>
@@ -20428,11 +20485,11 @@
       </c>
       <c r="R38" s="63">
         <f>'[3]Project Summary'!$J$8</f>
-        <v>0.37170609523809517</v>
+        <v>0.41932514285714284</v>
       </c>
       <c r="S38" s="88">
         <f t="shared" si="5"/>
-        <v>1.8585304761904757</v>
+        <v>2.0966257142857141</v>
       </c>
       <c r="T38" s="124">
         <f>'[3]Project Summary'!$L$8</f>
@@ -20444,11 +20501,11 @@
       </c>
       <c r="V38" s="63">
         <f>'[3]Project Summary'!$J$9</f>
-        <v>0.1857138095238095</v>
+        <v>0.55112704761904763</v>
       </c>
       <c r="W38" s="88">
         <f t="shared" si="6"/>
-        <v>0.1857138095238095</v>
+        <v>0.55112704761904763</v>
       </c>
       <c r="X38" s="146">
         <f>'[3]Project Summary'!$L$9</f>
@@ -20460,11 +20517,11 @@
       </c>
       <c r="Z38" s="63">
         <f>'[3]Project Summary'!$J$10</f>
-        <v>1.8522413571428575</v>
+        <v>1.8643365571428574</v>
       </c>
       <c r="AA38" s="88">
         <f t="shared" si="8"/>
-        <v>1.0002957439094733</v>
+        <v>1.0068277096465934</v>
       </c>
       <c r="AB38" s="146">
         <f>'[3]Project Summary'!$L$10</f>
@@ -20476,11 +20533,11 @@
       </c>
       <c r="AD38" s="63">
         <f>'[3]Project Summary'!$J$11</f>
-        <v>0</v>
+        <v>0.61960128571428563</v>
       </c>
       <c r="AE38" s="88">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>0.20722451027233632</v>
       </c>
       <c r="AF38" s="146">
         <f>'[3]Project Summary'!$L$11</f>
@@ -20492,11 +20549,11 @@
       </c>
       <c r="AH38" s="63">
         <f>'[3]Project Summary'!$J$12</f>
-        <v>0</v>
+        <v>9.9906571428571414E-2</v>
       </c>
       <c r="AI38" s="88">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.13145601503759397</v>
       </c>
       <c r="AJ38" s="124">
         <f>'[3]Project Summary'!$L$12</f>
@@ -20505,7 +20562,7 @@
       <c r="AL38" s="87"/>
       <c r="AN38" s="87"/>
     </row>
-    <row r="39" spans="7:40" ht="91.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:40" ht="91.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I39" s="150"/>
       <c r="L39" s="137" t="s">
         <v>61</v>
@@ -20516,11 +20573,11 @@
       </c>
       <c r="N39" s="63">
         <f>'[4]Project Summary'!$J$7</f>
-        <v>1.0101445714285715</v>
+        <v>1.531511523809524</v>
       </c>
       <c r="O39" s="88">
         <f t="shared" si="4"/>
-        <v>0.55277046193536505</v>
+        <v>0.83807244667788394</v>
       </c>
       <c r="P39" s="146">
         <f>'[4]Project Summary'!$L$7</f>
@@ -20548,11 +20605,11 @@
       </c>
       <c r="V39" s="63">
         <f>'[4]Project Summary'!$J$9</f>
-        <v>0.251112</v>
+        <v>0.19523809523809524</v>
       </c>
       <c r="W39" s="88">
         <f t="shared" si="6"/>
-        <v>0.35873142857142859</v>
+        <v>0.27891156462585037</v>
       </c>
       <c r="X39" s="146">
         <f>'[4]Project Summary'!$L$9</f>
@@ -20580,11 +20637,11 @@
       </c>
       <c r="AD39" s="63">
         <f>'[4]Project Summary'!$J$11</f>
-        <v>0.24822390476190476</v>
+        <v>1.9486154285714288</v>
       </c>
       <c r="AE39" s="88">
         <f t="shared" si="9"/>
-        <v>8.3859427284427288E-2</v>
+        <v>0.65831602316602322</v>
       </c>
       <c r="AF39" s="146">
         <f>'[4]Project Summary'!$L$11</f>
@@ -20596,11 +20653,11 @@
       </c>
       <c r="AH39" s="63">
         <f>'[4]Project Summary'!$J$12</f>
-        <v>0.62946580952380948</v>
+        <v>1.0580372380952381</v>
       </c>
       <c r="AI39" s="88">
         <f t="shared" si="7"/>
-        <v>0.47686803751803747</v>
+        <v>0.8015433621933622</v>
       </c>
       <c r="AJ39" s="124">
         <f>'[4]Project Summary'!$L$12</f>
@@ -20609,7 +20666,7 @@
       <c r="AL39" s="87"/>
       <c r="AN39" s="87"/>
     </row>
-    <row r="40" spans="7:40" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:40" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I40" s="150"/>
       <c r="L40" s="138" t="s">
         <v>47</v>
@@ -20620,11 +20677,11 @@
       </c>
       <c r="N40" s="63">
         <f>'[5]Project Summary'!$J$7</f>
-        <v>1.4609841952380953</v>
+        <v>0.6769339380952375</v>
       </c>
       <c r="O40" s="88">
         <f t="shared" si="4"/>
-        <v>0.60598843973837913</v>
+        <v>0.28077931458076949</v>
       </c>
       <c r="P40" s="146">
         <f>'[5]Project Summary'!$L$7</f>
@@ -20636,11 +20693,11 @@
       </c>
       <c r="R40" s="63">
         <f>'[5]Project Summary'!$J$8</f>
-        <v>0.20471047619047619</v>
+        <v>0</v>
       </c>
       <c r="S40" s="88">
         <f t="shared" si="5"/>
-        <v>0.39367399267399267</v>
+        <v>0</v>
       </c>
       <c r="T40" s="124">
         <f>'[5]Project Summary'!$L$8</f>
@@ -20652,11 +20709,11 @@
       </c>
       <c r="V40" s="63">
         <f>'[5]Project Summary'!$J$9</f>
-        <v>0</v>
+        <v>1.4285714285714284E-2</v>
       </c>
       <c r="W40" s="88">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>7.9365079365079361E-2</v>
       </c>
       <c r="X40" s="146">
         <f>'[5]Project Summary'!$L$9</f>
@@ -20668,11 +20725,11 @@
       </c>
       <c r="Z40" s="63">
         <f>'[5]Project Summary'!$J$10</f>
-        <v>1.0194376190476191</v>
+        <v>1.5744300857142859</v>
       </c>
       <c r="AA40" s="88">
         <f t="shared" si="8"/>
-        <v>0.59432435879590562</v>
+        <v>0.91788073510108226</v>
       </c>
       <c r="AB40" s="146">
         <f>'[5]Project Summary'!$L$10</f>
@@ -20684,11 +20741,11 @@
       </c>
       <c r="AD40" s="63">
         <f>'[5]Project Summary'!$J$11</f>
-        <v>0.30264676190476192</v>
+        <v>0.31099816190476187</v>
       </c>
       <c r="AE40" s="88">
         <f t="shared" si="9"/>
-        <v>0.14982512965582273</v>
+        <v>0.15395948609146629</v>
       </c>
       <c r="AF40" s="146">
         <f>'[5]Project Summary'!$L$11</f>
@@ -20700,11 +20757,11 @@
       </c>
       <c r="AH40" s="63">
         <f>'[5]Project Summary'!$J$12</f>
-        <v>0.81867361904761904</v>
+        <v>3.9889016190476192</v>
       </c>
       <c r="AI40" s="88">
         <f t="shared" si="7"/>
-        <v>0.18776917868064655</v>
+        <v>0.91488569244211437</v>
       </c>
       <c r="AJ40" s="124">
         <f>'[5]Project Summary'!$L$12</f>
@@ -20713,7 +20770,7 @@
       <c r="AL40" s="87"/>
       <c r="AN40" s="87"/>
     </row>
-    <row r="41" spans="7:40" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:40" ht="38.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I41" s="151"/>
       <c r="L41" s="139" t="s">
         <v>62</v>
@@ -20817,7 +20874,7 @@
       <c r="AL41" s="87"/>
       <c r="AN41" s="87"/>
     </row>
-    <row r="42" spans="7:40" ht="192.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:40" ht="192.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I42" s="150"/>
       <c r="L42" s="137" t="s">
         <v>63</v>
@@ -20828,11 +20885,11 @@
       </c>
       <c r="N42" s="63">
         <f>'[7]Project Summary'!$J$7</f>
-        <v>0.15494892380952385</v>
+        <v>0.60045633333333326</v>
       </c>
       <c r="O42" s="88">
         <f t="shared" si="4"/>
-        <v>0.1006161842918986</v>
+        <v>0.3899067099567099</v>
       </c>
       <c r="P42" s="146">
         <f>'[7]Project Summary'!$L$7</f>
@@ -20844,11 +20901,11 @@
       </c>
       <c r="R42" s="63">
         <f>'[7]Project Summary'!$J$8</f>
-        <v>4.7619047619047623E-2</v>
+        <v>0</v>
       </c>
       <c r="S42" s="88">
         <f t="shared" si="5"/>
-        <v>0.25062656641604014</v>
+        <v>0</v>
       </c>
       <c r="T42" s="124">
         <f>'[7]Project Summary'!$L$8</f>
@@ -20860,11 +20917,11 @@
       </c>
       <c r="V42" s="63">
         <f>'[7]Project Summary'!$J$9</f>
-        <v>0.34945942857142859</v>
+        <v>0.34850704761904766</v>
       </c>
       <c r="W42" s="88">
         <f t="shared" si="6"/>
-        <v>1.7472971428571429</v>
+        <v>1.7425352380952381</v>
       </c>
       <c r="X42" s="146">
         <f>'[7]Project Summary'!$L$9</f>
@@ -20908,11 +20965,11 @@
       </c>
       <c r="AH42" s="63">
         <f>'[7]Project Summary'!$J$12</f>
-        <v>0.71216342857142856</v>
+        <v>2.9267401904761905</v>
       </c>
       <c r="AI42" s="88">
         <f t="shared" si="7"/>
-        <v>0.35787106963388371</v>
+        <v>1.470723713807131</v>
       </c>
       <c r="AJ42" s="124">
         <f>'[7]Project Summary'!$L$12</f>
@@ -20921,7 +20978,7 @@
       <c r="AL42" s="87"/>
       <c r="AN42" s="87"/>
     </row>
-    <row r="43" spans="7:40" ht="38.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="7:40" ht="38.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I43" s="152"/>
       <c r="L43" s="140" t="s">
         <v>51</v>
@@ -20932,11 +20989,11 @@
       </c>
       <c r="N43" s="125">
         <f>SUM(N36:N42)</f>
-        <v>6.6289399190476193</v>
+        <v>9.3398698904761908</v>
       </c>
       <c r="O43" s="126">
         <f>N43/M43</f>
-        <v>0.38745336663015251</v>
+        <v>0.54590388163791081</v>
       </c>
       <c r="P43" s="147">
         <f>SUM(P36:P42)</f>
@@ -20948,11 +21005,11 @@
       </c>
       <c r="R43" s="125">
         <f>SUM(R36:R42)</f>
-        <v>0.62403561904761906</v>
+        <v>0.41932514285714284</v>
       </c>
       <c r="S43" s="126">
         <f>R43/Q43</f>
-        <v>0.43090005329157366</v>
+        <v>0.28954633499830984</v>
       </c>
       <c r="T43" s="127">
         <f>SUM(T36:T42)</f>
@@ -20964,11 +21021,11 @@
       </c>
       <c r="V43" s="125">
         <f>SUM(V36:V42)</f>
-        <v>0.78628523809523809</v>
+        <v>1.1091579047619047</v>
       </c>
       <c r="W43" s="126">
         <f>V43/U43</f>
-        <v>0.37802174908424907</v>
+        <v>0.53324899267399262</v>
       </c>
       <c r="X43" s="147">
         <f>SUM(X36:X42)</f>
@@ -20980,11 +21037,11 @@
       </c>
       <c r="Z43" s="125">
         <f>SUM(Z36:Z42)</f>
-        <v>2.8716789761904766</v>
+        <v>3.4387666428571433</v>
       </c>
       <c r="AA43" s="126">
         <f>Z43/Y43</f>
-        <v>0.71565110678046417</v>
+        <v>0.85697502204272225</v>
       </c>
       <c r="AB43" s="147">
         <f>SUM(AB36:AB42)</f>
@@ -20996,11 +21053,11 @@
       </c>
       <c r="AD43" s="125">
         <f>SUM(AD36:AD42)</f>
-        <v>0.55087066666666673</v>
+        <v>2.8792148761904763</v>
       </c>
       <c r="AE43" s="126">
         <f>AD43/AC43</f>
-        <v>5.9682629107981222E-2</v>
+        <v>0.31194093999896816</v>
       </c>
       <c r="AF43" s="147">
         <f>SUM(AF36:AF42)</f>
@@ -21012,18 +21069,18 @@
       </c>
       <c r="AH43" s="125">
         <f>SUM(AH36:AH42)</f>
-        <v>2.1603028571428569</v>
+        <v>8.0735856190476198</v>
       </c>
       <c r="AI43" s="126">
         <f>AH43/AG43</f>
-        <v>0.25626368412133532</v>
+        <v>0.95772071400327641</v>
       </c>
       <c r="AJ43" s="127">
         <f>SUM(AJ36:AJ42)</f>
         <v>7.5600000000000005</v>
       </c>
     </row>
-    <row r="44" spans="7:40" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:40" ht="15" x14ac:dyDescent="0.3">
       <c r="L44" s="111"/>
       <c r="M44" s="112"/>
       <c r="N44" s="112"/>
@@ -21050,7 +21107,7 @@
       <c r="AI44" s="113"/>
       <c r="AJ44" s="112"/>
     </row>
-    <row r="45" spans="7:40" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="45" spans="7:40" ht="15" x14ac:dyDescent="0.3">
       <c r="L45" s="111"/>
       <c r="M45" s="112"/>
       <c r="N45" s="112"/>
@@ -21062,7 +21119,7 @@
       </c>
       <c r="R45" s="112">
         <f>N27-R43</f>
-        <v>12.211792419047617</v>
+        <v>23.731437028571428</v>
       </c>
       <c r="S45" s="113"/>
       <c r="T45" s="112"/>
@@ -21083,7 +21140,7 @@
       <c r="AI45" s="113"/>
       <c r="AJ45" s="112"/>
     </row>
-    <row r="46" spans="7:40" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="46" spans="7:40" ht="15" x14ac:dyDescent="0.3">
       <c r="L46" s="111"/>
       <c r="M46" s="112"/>
       <c r="N46" s="112"/>
@@ -21110,7 +21167,7 @@
       <c r="AI46" s="113"/>
       <c r="AJ46" s="112"/>
     </row>
-    <row r="47" spans="7:40" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="47" spans="7:40" ht="15" x14ac:dyDescent="0.3">
       <c r="L47" s="111"/>
       <c r="M47" s="112"/>
       <c r="N47" s="112"/>
@@ -21137,10 +21194,10 @@
       <c r="AI47" s="113"/>
       <c r="AJ47" s="112"/>
     </row>
-    <row r="51" spans="12:30" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="12:30" ht="29.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="R51" s="66"/>
     </row>
-    <row r="52" spans="12:30" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="12:30" ht="35.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L52" s="233" t="s">
         <v>64</v>
       </c>
@@ -21177,7 +21234,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="12:30" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="12:30" ht="31.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L53" s="13" t="s">
         <v>66</v>
       </c>
@@ -21207,37 +21264,37 @@
       </c>
       <c r="W53" s="168">
         <f>'[1]Project Summary'!$L$18</f>
-        <v>2.2594639999999999</v>
+        <v>1.3896313</v>
       </c>
       <c r="X53" s="169">
         <f>'[2]Project Summary'!$L$18</f>
-        <v>3.2219701095238098</v>
+        <v>2.8999899238095237</v>
       </c>
       <c r="Y53" s="169">
-        <f>'[3]Project Summary'!$L$18</f>
-        <v>1.495299738095238</v>
+        <f>'[3]Project Summary'!$M$18</f>
+        <v>0.86600460952380953</v>
       </c>
       <c r="Z53" s="169">
         <f>'[4]Project Summary'!$L$18</f>
-        <v>0.93933931428571438</v>
+        <v>0.31219203809523804</v>
       </c>
       <c r="AA53" s="169">
         <f>'[5]Project Summary'!$L$18</f>
-        <v>4.1346330333333334</v>
+        <v>1.869566176190476</v>
       </c>
       <c r="AB53" s="169">
         <v>0.23</v>
       </c>
       <c r="AC53" s="169">
         <f>'[7]Project Summary'!$L$18</f>
-        <v>4.8191245476190474</v>
+        <v>2.1418024142857144</v>
       </c>
       <c r="AD53" s="169">
         <f>SUM(W53:AC53)</f>
-        <v>17.099830742857144</v>
+        <v>9.7091864619047623</v>
       </c>
     </row>
-    <row r="54" spans="12:30" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="12:30" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L54" s="20" t="s">
         <v>68</v>
       </c>
@@ -21266,16 +21323,16 @@
         <v>3.82143E-2</v>
       </c>
       <c r="Y54" s="169">
-        <f>'[3]Project Summary'!$L$19</f>
+        <f>'[3]Project Summary'!$M$19</f>
         <v>9.9999999999999995E-8</v>
       </c>
       <c r="Z54" s="169">
         <f>'[4]Project Summary'!$L$19</f>
-        <v>0</v>
+        <v>4.3803000000000002E-2</v>
       </c>
       <c r="AA54" s="169">
         <f>'[5]Project Summary'!$L$19</f>
-        <v>0.38415322380952377</v>
+        <v>0.27078962380952376</v>
       </c>
       <c r="AB54" s="169"/>
       <c r="AC54" s="169">
@@ -21284,10 +21341,10 @@
       </c>
       <c r="AD54" s="169">
         <f>SUM(W54:AC54)</f>
-        <v>0.42236762380952375</v>
+        <v>0.35280702380952378</v>
       </c>
     </row>
-    <row r="55" spans="12:30" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="12:30" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L55" s="22" t="s">
         <v>69</v>
       </c>
@@ -21316,12 +21373,12 @@
         <v>0</v>
       </c>
       <c r="Y55" s="169">
-        <f>'[3]Project Summary'!$L$20</f>
-        <v>0</v>
+        <f>'[3]Project Summary'!$M$20</f>
+        <v>3.5868595238095241E-2</v>
       </c>
       <c r="Z55" s="169">
         <f>'[4]Project Summary'!$L$20</f>
-        <v>9.745938571428571E-2</v>
+        <v>3.4285704761904755E-2</v>
       </c>
       <c r="AA55" s="169">
         <f>'[5]Project Summary'!$L$20</f>
@@ -21330,14 +21387,14 @@
       <c r="AB55" s="169"/>
       <c r="AC55" s="169">
         <f>'[7]Project Summary'!$L$20</f>
-        <v>3.5778771428571408E-2</v>
+        <v>3.6731152380952356E-2</v>
       </c>
       <c r="AD55" s="169">
         <f>SUM(W55:AC55)</f>
-        <v>0.13323815714285711</v>
+        <v>0.10688545238095236</v>
       </c>
     </row>
-    <row r="56" spans="12:30" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="12:30" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L56" s="22" t="s">
         <v>71</v>
       </c>
@@ -21369,8 +21426,8 @@
         <v>0</v>
       </c>
       <c r="Y56" s="169">
-        <f>'[3]Project Summary'!$L$21</f>
-        <v>9.190476201474667E-8</v>
+        <f>'[3]Project Summary'!$M$21</f>
+        <v>0</v>
       </c>
       <c r="Z56" s="169">
         <f>'[4]Project Summary'!$L$21</f>
@@ -21378,7 +21435,7 @@
       </c>
       <c r="AA56" s="169">
         <f>'[5]Project Summary'!$L$21</f>
-        <v>0.79152638095238093</v>
+        <v>0.23760991904761902</v>
       </c>
       <c r="AB56" s="169"/>
       <c r="AC56" s="169">
@@ -21387,10 +21444,10 @@
       </c>
       <c r="AD56" s="169">
         <f>SUM(W56:AC56)</f>
-        <v>1.2372245728571429</v>
+        <v>0.68330801904761906</v>
       </c>
     </row>
-    <row r="57" spans="12:30" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="12:30" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L57" s="22" t="s">
         <v>72</v>
       </c>
@@ -21422,16 +21479,16 @@
         <v>0</v>
       </c>
       <c r="Y57" s="169">
-        <f>'[3]Project Summary'!$L$22</f>
-        <v>0</v>
+        <f>'[3]Project Summary'!$M$22</f>
+        <v>1.4565151000000001</v>
       </c>
       <c r="Z57" s="169">
         <f>'[4]Project Summary'!$L$22</f>
-        <v>1.7014095238095231E-2</v>
+        <v>1.5554633333333326E-2</v>
       </c>
       <c r="AA57" s="169">
         <f>'[5]Project Summary'!$L$22</f>
-        <v>0.91420216666666665</v>
+        <v>0.90476400000000001</v>
       </c>
       <c r="AB57" s="169"/>
       <c r="AC57" s="169">
@@ -21440,10 +21497,10 @@
       </c>
       <c r="AD57" s="169">
         <f>SUM(W57:AC57)</f>
-        <v>0.93121626190476192</v>
+        <v>2.3768337333333336</v>
       </c>
     </row>
-    <row r="58" spans="12:30" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="12:30" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L58" s="22" t="s">
         <v>73</v>
       </c>
@@ -21465,23 +21522,23 @@
       </c>
       <c r="W58" s="167">
         <f t="shared" ref="W58:AD58" si="11">SUM(W53:W57)</f>
-        <v>2.2594639999999999</v>
+        <v>1.3896313</v>
       </c>
       <c r="X58" s="167">
         <f t="shared" si="11"/>
-        <v>3.2601844095238097</v>
+        <v>2.9382042238095236</v>
       </c>
       <c r="Y58" s="167">
         <f t="shared" si="11"/>
-        <v>1.4952999300000001</v>
+        <v>2.3583884047619046</v>
       </c>
       <c r="Z58" s="167">
         <f t="shared" si="11"/>
-        <v>1.4995108952380953</v>
+        <v>0.85153347619047604</v>
       </c>
       <c r="AA58" s="167">
         <f t="shared" si="11"/>
-        <v>6.2245148047619043</v>
+        <v>3.282729719047619</v>
       </c>
       <c r="AB58" s="167">
         <f t="shared" si="11"/>
@@ -21489,14 +21546,14 @@
       </c>
       <c r="AC58" s="167">
         <f t="shared" si="11"/>
-        <v>4.8549033190476187</v>
+        <v>2.1785335666666668</v>
       </c>
       <c r="AD58" s="167">
         <f t="shared" si="11"/>
-        <v>19.82387735857143</v>
+        <v>13.22902069047619</v>
       </c>
     </row>
-    <row r="59" spans="12:30" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="12:30" ht="26.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L59" s="23" t="s">
         <v>75</v>
       </c>
@@ -21514,7 +21571,7 @@
       <c r="R59" s="45"/>
       <c r="S59" s="45"/>
     </row>
-    <row r="60" spans="12:30" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="12:30" ht="15.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L60" s="25" t="s">
         <v>76</v>
       </c>
@@ -21550,6 +21607,13 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="16">
+    <mergeCell ref="S18:V18"/>
+    <mergeCell ref="M34:P34"/>
+    <mergeCell ref="AG34:AJ34"/>
+    <mergeCell ref="AC34:AF34"/>
+    <mergeCell ref="Y34:AB34"/>
+    <mergeCell ref="U34:X34"/>
+    <mergeCell ref="Q34:T34"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="L18:O18"/>
     <mergeCell ref="L52:Q52"/>
@@ -21559,13 +21623,6 @@
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="S18:V18"/>
-    <mergeCell ref="M34:P34"/>
-    <mergeCell ref="AG34:AJ34"/>
-    <mergeCell ref="AC34:AF34"/>
-    <mergeCell ref="Y34:AB34"/>
-    <mergeCell ref="U34:X34"/>
-    <mergeCell ref="Q34:T34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -21577,61 +21634,61 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89C9A0C-B59D-45A5-A92C-FB9FBEAAEEC4}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B1:AJ32"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="1.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="32.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.90625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.453125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="1.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="32.453125" style="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="29.44140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="1.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="24.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.88671875" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.453125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="1.453125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.54296875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.90625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.90625" style="1" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="8.88671875" style="1"/>
-    <col min="17" max="17" width="28.88671875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="17.44140625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="22.5546875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="24.5546875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="17.44140625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="23.44140625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="15.5546875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.5546875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="20.5546875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="8.88671875" style="1"/>
-    <col min="30" max="30" width="40.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="18.109375" style="1" customWidth="1"/>
-    <col min="33" max="33" width="19.5546875" style="1" customWidth="1"/>
+    <col min="15" max="16" width="8.90625" style="1"/>
+    <col min="17" max="17" width="28.90625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="17.453125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="22.54296875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="24.54296875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="17.453125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="23.453125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="15.54296875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="16.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.54296875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="20.54296875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="15.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.08984375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="8.90625" style="1"/>
+    <col min="30" max="30" width="40.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="18.08984375" style="1" customWidth="1"/>
+    <col min="33" max="33" width="19.54296875" style="1" customWidth="1"/>
     <col min="34" max="34" width="20" style="1" customWidth="1"/>
-    <col min="35" max="35" width="23.44140625" style="1" customWidth="1"/>
-    <col min="36" max="36" width="17.5546875" style="1" customWidth="1"/>
-    <col min="37" max="16384" width="8.88671875" style="1"/>
+    <col min="35" max="35" width="23.453125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="17.54296875" style="1" customWidth="1"/>
+    <col min="37" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:36" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="255" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="255"/>
-      <c r="D1" s="255"/>
-      <c r="E1" s="255"/>
-      <c r="F1" s="255"/>
+    <row r="1" spans="2:36" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="252" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="252"/>
+      <c r="D1" s="252"/>
+      <c r="E1" s="252"/>
+      <c r="F1" s="252"/>
       <c r="H1" s="37" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="35"/>
       <c r="J1" s="36">
         <f ca="1">TODAY()</f>
-        <v>46165</v>
+        <v>46176</v>
       </c>
       <c r="Q1" s="233" t="s">
         <v>77</v>
@@ -21640,26 +21697,26 @@
       <c r="S1" s="233"/>
       <c r="T1" s="233"/>
     </row>
-    <row r="2" spans="2:36" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="256" t="s">
+    <row r="2" spans="2:36" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="253" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="256"/>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
+      <c r="C2" s="253"/>
+      <c r="D2" s="253"/>
+      <c r="E2" s="253"/>
+      <c r="F2" s="253"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="256" t="s">
+      <c r="H2" s="253" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
+      <c r="I2" s="253"/>
+      <c r="J2" s="253"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="2:36" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:36" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="58">
         <f>$R$19</f>
         <v>22.274084900000002</v>
@@ -21673,12 +21730,12 @@
         <f>$S$9</f>
         <v>0</v>
       </c>
-      <c r="H3" s="257" t="str">
+      <c r="H3" s="254" t="str">
         <f>CONCATENATE($Z$9, " / ", $Y$9)</f>
         <v>9 / 17</v>
       </c>
-      <c r="I3" s="258"/>
-      <c r="J3" s="259"/>
+      <c r="I3" s="255"/>
+      <c r="J3" s="256"/>
       <c r="L3" s="5">
         <v>8</v>
       </c>
@@ -21716,7 +21773,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="2:36" ht="35.4" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:36" ht="35.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="27" t="s">
         <v>79</v>
       </c>
@@ -21769,7 +21826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:36" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:36" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="Q5" s="32" t="s">
         <v>84</v>
       </c>
@@ -21804,7 +21861,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="2:36" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:36" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="58">
         <f>$X$9</f>
         <v>10.826593257142859</v>
@@ -21819,12 +21876,12 @@
         <f>$W$19</f>
         <v>6.6640613999999996</v>
       </c>
-      <c r="H6" s="252" t="str">
+      <c r="H6" s="257" t="str">
         <f>CONCATENATE($U$9," / ",AA9)</f>
         <v>17 / 20</v>
       </c>
-      <c r="I6" s="253"/>
-      <c r="J6" s="254"/>
+      <c r="I6" s="258"/>
+      <c r="J6" s="259"/>
       <c r="L6" s="10"/>
       <c r="Q6" s="11" t="s">
         <v>86</v>
@@ -21860,7 +21917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:36" ht="59.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:36" ht="59.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="27" t="s">
         <v>87</v>
       </c>
@@ -21912,7 +21969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:36" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:36" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q8" s="32" t="s">
         <v>91</v>
       </c>
@@ -21947,7 +22004,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:36" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:36" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q9" s="11" t="s">
         <v>29</v>
       </c>
@@ -21992,7 +22049,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="12"/>
@@ -22000,7 +22057,7 @@
       <c r="F10" s="12"/>
       <c r="G10" s="12"/>
     </row>
-    <row r="12" spans="2:36" ht="23.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:36" ht="23" thickBot="1" x14ac:dyDescent="0.35">
       <c r="Q12" s="233" t="s">
         <v>92</v>
       </c>
@@ -22016,7 +22073,7 @@
       <c r="Z12" s="233"/>
       <c r="AA12" s="233"/>
     </row>
-    <row r="13" spans="2:36" ht="47.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:36" ht="45.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="Q13" s="6" t="s">
         <v>32</v>
       </c>
@@ -22075,7 +22132,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="2:36" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:36" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
       <c r="D14" s="17"/>
@@ -22141,7 +22198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:36" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:36" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q15" s="30" t="s">
         <v>60</v>
       </c>
@@ -22203,7 +22260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:36" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:36" ht="28" x14ac:dyDescent="0.3">
       <c r="Q16" s="30" t="s">
         <v>98</v>
       </c>
@@ -22265,7 +22322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="13:36" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="17" spans="13:36" ht="28" x14ac:dyDescent="0.3">
       <c r="Q17" s="30" t="s">
         <v>100</v>
       </c>
@@ -22327,7 +22384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="13:36" ht="28.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="13:36" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="Q18" s="31" t="s">
         <v>62</v>
       </c>
@@ -22389,7 +22446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="13:36" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="13:36" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="Q19" s="24" t="s">
         <v>51</v>
       </c>
@@ -22456,7 +22513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="13:36" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="20" spans="13:36" ht="26" x14ac:dyDescent="0.3">
       <c r="AD20" s="21" t="s">
         <v>104</v>
       </c>
@@ -22480,7 +22537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="13:36" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="13:36" ht="24.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AD21" s="26" t="s">
         <v>29</v>
       </c>
@@ -22509,7 +22566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="13:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="13:36" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M23" s="1" t="s">
         <v>105</v>
       </c>
@@ -22518,7 +22575,7 @@
       <c r="S23" s="233"/>
       <c r="T23" s="233"/>
     </row>
-    <row r="24" spans="13:36" x14ac:dyDescent="0.25">
+    <row r="24" spans="13:36" x14ac:dyDescent="0.3">
       <c r="M24" s="60" t="s">
         <v>106</v>
       </c>
@@ -22526,7 +22583,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="13:36" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="25" spans="13:36" ht="16" x14ac:dyDescent="0.3">
       <c r="Q25" s="54"/>
       <c r="R25" s="54"/>
       <c r="S25" s="54"/>
@@ -22534,7 +22591,7 @@
       <c r="U25" s="54"/>
       <c r="V25" s="54"/>
     </row>
-    <row r="26" spans="13:36" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="26" spans="13:36" ht="16" x14ac:dyDescent="0.3">
       <c r="Q26" s="55"/>
       <c r="R26" s="56"/>
       <c r="S26" s="56"/>
@@ -22542,7 +22599,7 @@
       <c r="U26" s="56"/>
       <c r="V26" s="56"/>
     </row>
-    <row r="27" spans="13:36" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="27" spans="13:36" ht="16" x14ac:dyDescent="0.3">
       <c r="Q27" s="55"/>
       <c r="R27" s="56"/>
       <c r="S27" s="56"/>
@@ -22550,7 +22607,7 @@
       <c r="U27" s="56"/>
       <c r="V27" s="56"/>
     </row>
-    <row r="28" spans="13:36" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="28" spans="13:36" ht="16" x14ac:dyDescent="0.3">
       <c r="Q28" s="55"/>
       <c r="R28" s="56"/>
       <c r="S28" s="56"/>
@@ -22558,7 +22615,7 @@
       <c r="U28" s="56"/>
       <c r="V28" s="56"/>
     </row>
-    <row r="29" spans="13:36" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="29" spans="13:36" ht="16" x14ac:dyDescent="0.3">
       <c r="Q29" s="55"/>
       <c r="R29" s="56"/>
       <c r="S29" s="56"/>
@@ -22566,7 +22623,7 @@
       <c r="U29" s="56"/>
       <c r="V29" s="56"/>
     </row>
-    <row r="30" spans="13:36" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="30" spans="13:36" ht="16" x14ac:dyDescent="0.3">
       <c r="Q30" s="55"/>
       <c r="R30" s="56"/>
       <c r="S30" s="56"/>
@@ -22574,7 +22631,7 @@
       <c r="U30" s="56"/>
       <c r="V30" s="56"/>
     </row>
-    <row r="31" spans="13:36" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="31" spans="13:36" ht="16" x14ac:dyDescent="0.3">
       <c r="Q31" s="55"/>
       <c r="R31" s="56"/>
       <c r="S31" s="56"/>
@@ -22582,7 +22639,7 @@
       <c r="U31" s="56"/>
       <c r="V31" s="56"/>
     </row>
-    <row r="32" spans="13:36" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="32" spans="13:36" ht="16" x14ac:dyDescent="0.3">
       <c r="Q32" s="57"/>
       <c r="R32" s="56"/>
       <c r="S32" s="56"/>
@@ -22593,17 +22650,17 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="11">
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="Q12:T12"/>
+    <mergeCell ref="V12:AA12"/>
+    <mergeCell ref="Q23:T23"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="Q1:T1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="H3:J3"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="Q12:T12"/>
-    <mergeCell ref="V12:AA12"/>
-    <mergeCell ref="Q23:T23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -22615,43 +22672,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6748CFE-CC1A-45C5-889F-FA6D6C4D712A}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B1:AN60"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="48.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="0.5546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="48.6328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="0.54296875" style="1" customWidth="1"/>
     <col min="4" max="4" width="39" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="52.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="46.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="61.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="33.6640625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="19.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.54296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="52.36328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="46.54296875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="5.90625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="61.36328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.08984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="33.6328125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19.453125" style="1" customWidth="1"/>
     <col min="14" max="14" width="24" style="1" customWidth="1"/>
-    <col min="15" max="15" width="24.44140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="29.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.453125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="29.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="21" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.6640625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="44.44140625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="21.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.6328125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="44.453125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="21.54296875" style="1" customWidth="1"/>
     <col min="21" max="21" width="25" style="1" customWidth="1"/>
-    <col min="22" max="22" width="25.5546875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="23.44140625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="17.5546875" style="1" customWidth="1"/>
-    <col min="25" max="26" width="19.5546875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="30.44140625" style="1" customWidth="1"/>
-    <col min="28" max="28" width="25.5546875" style="1" customWidth="1"/>
-    <col min="29" max="31" width="17.109375" style="1" customWidth="1"/>
-    <col min="32" max="32" width="30.109375" style="91" customWidth="1"/>
-    <col min="33" max="35" width="17.109375" style="1" customWidth="1"/>
-    <col min="36" max="37" width="21.5546875" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="8.88671875" style="1"/>
+    <col min="22" max="22" width="25.54296875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="23.453125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="17.54296875" style="1" customWidth="1"/>
+    <col min="25" max="26" width="19.54296875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="30.453125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="25.54296875" style="1" customWidth="1"/>
+    <col min="29" max="31" width="17.08984375" style="1" customWidth="1"/>
+    <col min="32" max="32" width="30.08984375" style="91" customWidth="1"/>
+    <col min="33" max="35" width="17.08984375" style="1" customWidth="1"/>
+    <col min="36" max="37" width="21.54296875" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:32" s="95" customFormat="1" ht="47.4" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="1" spans="2:32" s="95" customFormat="1" ht="47.4" customHeight="1" x14ac:dyDescent="0.95">
       <c r="B1" s="228" t="s">
         <v>0</v>
       </c>
@@ -22662,16 +22719,16 @@
       </c>
       <c r="I1" s="98">
         <f ca="1">TODAY()</f>
-        <v>46165</v>
+        <v>46176</v>
       </c>
       <c r="K1" s="170"/>
-      <c r="L1" s="110"/>
+      <c r="L1" s="97"/>
       <c r="M1" s="110"/>
       <c r="N1" s="110"/>
       <c r="O1" s="110"/>
       <c r="AF1" s="99"/>
     </row>
-    <row r="2" spans="2:32" s="78" customFormat="1" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:32" s="78" customFormat="1" ht="48.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="B2" s="229" t="s">
         <v>108</v>
       </c>
@@ -22688,29 +22745,33 @@
       </c>
       <c r="J2" s="77"/>
       <c r="K2" s="171"/>
+      <c r="L2" s="78">
+        <f>24.46+1.77+1.27</f>
+        <v>27.5</v>
+      </c>
       <c r="N2" s="78" t="s">
         <v>58</v>
       </c>
       <c r="AF2" s="90"/>
     </row>
-    <row r="3" spans="2:32" ht="134.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:32" ht="134.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="237" t="str">
         <f>CONCATENATE("₹ ",ROUND($N$27,2)," / ",ROUND($M$27,2)," (",ROUND($O$27,3)*100,"%)")</f>
-        <v>₹ 12.21 / 38.72 (31.5%)</v>
+        <v>₹ 23.73 / 38.72 (61.3%)</v>
       </c>
       <c r="C3" s="238"/>
       <c r="D3" s="239"/>
       <c r="F3" s="161" t="str">
         <f>CONCATENATE("₹ ", ROUND($U$21,2), "  /  ", "₹ ", ROUND($T$21,2))</f>
-        <v>₹ 1.42  /  ₹ 2.01</v>
+        <v>₹ 0.42  /  ₹ 2.01</v>
       </c>
       <c r="G3" s="160" t="str">
         <f>CONCATENATE("₹ ", ROUND($U$22,2), "  /  ", "₹ ", ROUND($T$22,2))</f>
-        <v>₹ 0.95  /  ₹ 2.08</v>
+        <v>₹ 1.27  /  ₹ 2.08</v>
       </c>
       <c r="I3" s="85" t="str">
-        <f ca="1">CONCATENATE("₹ ",ROUND($N$11,2), "  |  ", "₹ ",ROUND($O$11,2))</f>
-        <v>₹ 0  |  ₹ 14.76</v>
+        <f>CONCATENATE("₹ ",ROUND($N$11,2), "  |  ", "₹ ",ROUND($O$11,2))</f>
+        <v>₹ 0  |  ₹ 27.53</v>
       </c>
       <c r="L3" s="114" t="s">
         <v>5</v>
@@ -22752,7 +22813,7 @@
       <c r="Y3" s="66"/>
       <c r="Z3" s="66"/>
     </row>
-    <row r="4" spans="2:32" s="72" customFormat="1" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:32" s="72" customFormat="1" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B4" s="240" t="s">
         <v>111</v>
       </c>
@@ -22781,7 +22842,7 @@
       </c>
       <c r="O4" s="101">
         <f>'[1]Project Summary'!$E$7</f>
-        <v>1.337979</v>
+        <v>2.3498838000000002</v>
       </c>
       <c r="P4" s="104">
         <f>'[1]Project Summary'!$F$7</f>
@@ -22793,11 +22854,11 @@
       </c>
       <c r="R4" s="79">
         <f>'[1]Project Summary'!$D$14</f>
-        <v>206.96726649999999</v>
+        <v>208.8346166</v>
       </c>
       <c r="S4" s="79">
         <f>'[1]Project Summary'!$E$14</f>
-        <v>2.2594641000000002</v>
+        <v>1.3896314000000001</v>
       </c>
       <c r="T4" s="69">
         <f>'[1]Project Summary'!$D$21</f>
@@ -22805,7 +22866,7 @@
       </c>
       <c r="U4" s="69">
         <f>'[1]Project Summary'!$F$21</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V4" s="69">
         <f>'[1]Project Summary'!$Q$3</f>
@@ -22820,7 +22881,7 @@
       <c r="Z4" s="75"/>
       <c r="AF4" s="92"/>
     </row>
-    <row r="5" spans="2:32" ht="46.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:32" ht="46.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F5" s="229" t="s">
         <v>115</v>
       </c>
@@ -22838,7 +22899,7 @@
       </c>
       <c r="O5" s="102">
         <f>'[2]Project Summary'!$E$7</f>
-        <v>2.5260024666666676</v>
+        <v>2.8898566238095249</v>
       </c>
       <c r="P5" s="105">
         <f>'[2]Project Summary'!$F$7</f>
@@ -22850,11 +22911,11 @@
       </c>
       <c r="R5" s="82">
         <f>'[2]Project Summary'!$D$13</f>
-        <v>100.57513296666666</v>
+        <v>100.93898712380951</v>
       </c>
       <c r="S5" s="82">
         <f>'[2]Project Summary'!$E$13</f>
-        <v>3.2601844095238097</v>
+        <v>2.9382042238095241</v>
       </c>
       <c r="T5" s="69">
         <f>'[2]Project Summary'!$D$20</f>
@@ -22876,7 +22937,7 @@
       <c r="Y5" s="68"/>
       <c r="Z5" s="66"/>
     </row>
-    <row r="6" spans="2:32" ht="135" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:32" ht="135" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="85">
         <f>P27</f>
         <v>32.51</v>
@@ -22884,57 +22945,57 @@
       <c r="C6" s="8"/>
       <c r="D6" s="84">
         <f>$S$11-AC54-AC55</f>
-        <v>19.206180777619046</v>
+        <v>12.707237414285714</v>
       </c>
       <c r="F6" s="154" t="str">
-        <f ca="1">CONCATENATE($U$11, "      |    ", $T$11)</f>
-        <v>26      |    52</v>
+        <f>CONCATENATE($U$11, "      |    ", $T$11)</f>
+        <v>32      |    53</v>
       </c>
       <c r="G6" s="156" t="str">
         <f>CONCATENATE($P$11," / ",V11)</f>
-        <v>9 / 15</v>
+        <v>11 / 15</v>
       </c>
       <c r="I6" s="84">
         <f>$S$11</f>
-        <v>22.537933758571427</v>
+        <v>15.68149889047619</v>
       </c>
       <c r="L6" s="109" t="s">
         <v>149</v>
       </c>
       <c r="M6" s="69">
         <f>'[3]Project Summary'!$B$7</f>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N6" s="102">
-        <f ca="1">'[3]Project Summary'!$D$7</f>
+        <f>'[3]Project Summary'!$D$7</f>
         <v>0</v>
       </c>
       <c r="O6" s="102">
         <f>'[3]Project Summary'!$E$7</f>
-        <v>2.7321155142857152</v>
+        <v>4.9375963761904789</v>
       </c>
       <c r="P6" s="105">
         <f>'[3]Project Summary'!$F$7</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="82">
         <f>'[3]Project Summary'!$C$13</f>
-        <v>49.654334429999999</v>
+        <v>52.623265600000003</v>
       </c>
       <c r="R6" s="82">
         <f>'[3]Project Summary'!$D$13</f>
-        <v>49.215646423809524</v>
+        <v>51.599938876190471</v>
       </c>
       <c r="S6" s="82">
         <f>'[3]Project Summary'!$E$13</f>
-        <v>1.4952999300000001</v>
+        <v>2.358388404761905</v>
       </c>
       <c r="T6" s="69">
         <f>'[3]Project Summary'!$D$20</f>
         <v>16</v>
       </c>
       <c r="U6" s="69">
-        <f ca="1">'[3]Project Summary'!$F$20</f>
+        <f>'[3]Project Summary'!$F$20</f>
         <v>9</v>
       </c>
       <c r="V6" s="69">
@@ -22949,7 +23010,7 @@
       <c r="Y6" s="68"/>
       <c r="Z6" s="66"/>
     </row>
-    <row r="7" spans="2:32" s="28" customFormat="1" ht="40.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:32" s="28" customFormat="1" ht="40.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="27" t="s">
         <v>116</v>
       </c>
@@ -22972,38 +23033,38 @@
       </c>
       <c r="M7" s="69">
         <f>'[4]Project Summary'!$B$7</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N7" s="102">
-        <f ca="1">'[4]Project Summary'!$D$7</f>
+        <f>'[4]Project Summary'!$D$7</f>
         <v>0</v>
       </c>
       <c r="O7" s="102">
         <f>'[4]Project Summary'!$E$7</f>
-        <v>2.1389462857142854</v>
+        <v>4.8224563857142861</v>
       </c>
       <c r="P7" s="105">
         <f>'[4]Project Summary'!$F$7</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q7" s="82">
         <f>'[4]Project Summary'!$C$13</f>
-        <v>36.135609299999999</v>
+        <v>36.268466400000001</v>
       </c>
       <c r="R7" s="82">
         <f>'[4]Project Summary'!$D$13</f>
-        <v>35.697580685714279</v>
+        <v>38.381090785714285</v>
       </c>
       <c r="S7" s="82">
         <f>'[4]Project Summary'!$E$13</f>
-        <v>1.4995108952380953</v>
+        <v>0.85153347619047615</v>
       </c>
       <c r="T7" s="69">
         <f>'[4]Project Summary'!$D$20</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7" s="69">
-        <f ca="1">'[4]Project Summary'!$F$20</f>
+        <f>'[4]Project Summary'!$F$20</f>
         <v>1</v>
       </c>
       <c r="V7" s="69">
@@ -23019,22 +23080,22 @@
       <c r="Z7" s="71"/>
       <c r="AF7" s="93"/>
     </row>
-    <row r="8" spans="2:32" s="28" customFormat="1" ht="28.35" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:32" s="28" customFormat="1" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="K8" s="173"/>
       <c r="L8" s="109" t="s">
         <v>26</v>
       </c>
       <c r="M8" s="69">
         <f>'[5]Project Summary'!$B$7</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N8" s="102">
-        <f ca="1">'[5]Project Summary'!$D$7</f>
+        <f>'[5]Project Summary'!$D$7</f>
         <v>0</v>
       </c>
       <c r="O8" s="102">
         <f>'[5]Project Summary'!$E$7</f>
-        <v>3.8064526714285707</v>
+        <v>7.3371716142857135</v>
       </c>
       <c r="P8" s="105">
         <f>'[5]Project Summary'!$F$7</f>
@@ -23042,23 +23103,23 @@
       </c>
       <c r="Q8" s="82">
         <f>'[5]Project Summary'!$C$13</f>
-        <v>34.304362699999999</v>
+        <v>33.5674992</v>
       </c>
       <c r="R8" s="82">
         <f>'[5]Project Summary'!$D$13</f>
-        <v>28.990686871428569</v>
+        <v>31.888382104761909</v>
       </c>
       <c r="S8" s="82">
         <f>'[5]Project Summary'!$E$13</f>
-        <v>6.2245148047619034</v>
+        <v>3.282729719047619</v>
       </c>
       <c r="T8" s="69">
         <f>'[5]Project Summary'!$D$20</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8" s="69">
-        <f ca="1">'[5]Project Summary'!$F$20</f>
-        <v>5</v>
+        <f>'[5]Project Summary'!$F$20</f>
+        <v>7</v>
       </c>
       <c r="V8" s="69">
         <f>'[5]Project Summary'!$Q$3</f>
@@ -23073,21 +23134,21 @@
       <c r="Z8" s="71"/>
       <c r="AF8" s="93"/>
     </row>
-    <row r="9" spans="2:32" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:32" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L9" s="109" t="s">
         <v>150</v>
       </c>
       <c r="M9" s="69">
         <f>'[6]Project Summary'!$B$7</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N9" s="102">
-        <f ca="1">'[6]Project Summary'!$D$7</f>
+        <f>'[6]Project Summary'!$D$7</f>
         <v>0</v>
       </c>
       <c r="O9" s="103">
         <f>'[6]Project Summary'!$E$7</f>
-        <v>0.95730709999999997</v>
+        <v>1.2688853</v>
       </c>
       <c r="P9" s="106">
         <f>'[6]Project Summary'!$F$7</f>
@@ -23099,19 +23160,19 @@
       </c>
       <c r="R9" s="82">
         <f>'[6]Project Summary'!$D$13</f>
-        <v>2.5436453000000001</v>
+        <v>2.8052234999999999</v>
       </c>
       <c r="S9" s="82">
         <f>'[6]Project Summary'!$E$13</f>
-        <v>2.9440563000000002</v>
+        <v>2.6824781</v>
       </c>
       <c r="T9" s="69">
         <f>'[6]Project Summary'!$D$20</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U9" s="69">
-        <f ca="1">'[6]Project Summary'!$F$20</f>
-        <v>7</v>
+        <f>'[6]Project Summary'!$F$20</f>
+        <v>10</v>
       </c>
       <c r="V9" s="69">
         <f>'[6]Project Summary'!$Q$3</f>
@@ -23125,7 +23186,7 @@
       <c r="Y9" s="68"/>
       <c r="Z9" s="66"/>
     </row>
-    <row r="10" spans="2:32" ht="18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:32" ht="18" x14ac:dyDescent="0.3">
       <c r="L10" s="109" t="s">
         <v>28</v>
       </c>
@@ -23134,12 +23195,12 @@
         <v>25</v>
       </c>
       <c r="N10" s="102">
-        <f ca="1">'[7]Project Summary'!$D$7</f>
+        <f>'[7]Project Summary'!$D$7</f>
         <v>0</v>
       </c>
       <c r="O10" s="103">
         <f>'[7]Project Summary'!$E$7</f>
-        <v>1.2641908285714285</v>
+        <v>3.92332261904762</v>
       </c>
       <c r="P10" s="106">
         <f>'[7]Project Summary'!$F$7</f>
@@ -23151,18 +23212,18 @@
       </c>
       <c r="R10" s="82">
         <f>'[7]Project Summary'!$D$13</f>
-        <v>19.54784562857143</v>
+        <v>22.224215519047622</v>
       </c>
       <c r="S10" s="82">
         <f>'[7]Project Summary'!$E$13</f>
-        <v>4.8549033190476196</v>
+        <v>2.1785335666666672</v>
       </c>
       <c r="T10" s="69">
         <f>'[7]Project Summary'!$D$20</f>
         <v>3</v>
       </c>
       <c r="U10" s="69">
-        <f ca="1">'[7]Project Summary'!$F$20</f>
+        <f>'[7]Project Summary'!$F$20</f>
         <v>1</v>
       </c>
       <c r="V10" s="69">
@@ -23177,45 +23238,45 @@
       <c r="Y10" s="68"/>
       <c r="Z10" s="66"/>
     </row>
-    <row r="11" spans="2:32" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:32" ht="17.5" x14ac:dyDescent="0.3">
       <c r="L11" s="116" t="s">
         <v>29</v>
       </c>
       <c r="M11" s="117">
         <f t="shared" ref="M11:W11" si="0">SUM(M4:M10)</f>
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="N11" s="118">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O11" s="118">
         <f t="shared" si="0"/>
-        <v>14.762993866666665</v>
+        <v>27.529172719047626</v>
       </c>
       <c r="P11" s="119">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q11" s="120">
         <f t="shared" si="0"/>
-        <v>460.49450673000007</v>
+        <v>462.85943150000008</v>
       </c>
       <c r="R11" s="120">
         <f t="shared" si="0"/>
-        <v>443.53780437619048</v>
+        <v>456.67245450952379</v>
       </c>
       <c r="S11" s="120">
         <f t="shared" si="0"/>
-        <v>22.537933758571427</v>
+        <v>15.68149889047619</v>
       </c>
       <c r="T11" s="121">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U11" s="121">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="V11" s="121">
         <f t="shared" si="0"/>
@@ -23232,29 +23293,29 @@
       <c r="Y11" s="66"/>
       <c r="Z11" s="66"/>
     </row>
-    <row r="12" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.3">
       <c r="Y12" s="66"/>
       <c r="Z12" s="66"/>
     </row>
-    <row r="13" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.3">
       <c r="Y13" s="66"/>
       <c r="Z13" s="66"/>
     </row>
-    <row r="14" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.3">
       <c r="Y14" s="66"/>
       <c r="Z14" s="66"/>
     </row>
-    <row r="15" spans="2:32" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:32" ht="35.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y15" s="66"/>
       <c r="Z15" s="66"/>
     </row>
-    <row r="16" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
     </row>
-    <row r="18" spans="2:32" ht="45.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:32" ht="45.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L18" s="234" t="s">
         <v>30</v>
       </c>
@@ -23269,7 +23330,7 @@
       <c r="V18" s="233"/>
       <c r="AF18" s="1"/>
     </row>
-    <row r="19" spans="2:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:32" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L19" s="6" t="s">
         <v>32</v>
       </c>
@@ -23308,7 +23369,7 @@
       </c>
       <c r="AF19" s="1"/>
     </row>
-    <row r="20" spans="2:32" ht="31.2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:32" ht="31" x14ac:dyDescent="0.3">
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
       <c r="D20" s="17"/>
@@ -23321,11 +23382,11 @@
       </c>
       <c r="N20" s="18">
         <f>'[1]Project Summary'!$J$13-R36</f>
-        <v>1.337979</v>
+        <v>2.2578117</v>
       </c>
       <c r="O20" s="19">
         <f t="shared" ref="O20:O25" si="1">N20/M20</f>
-        <v>0.38077896646428716</v>
+        <v>0.64255657644624853</v>
       </c>
       <c r="P20" s="18">
         <f>'[1]Project Summary'!$L$13-T36</f>
@@ -23333,7 +23394,7 @@
       </c>
       <c r="Q20" s="18">
         <f t="shared" ref="Q20:Q27" si="2">P20-N20</f>
-        <v>0.85202099999999992</v>
+        <v>-6.781170000000003E-2</v>
       </c>
       <c r="S20" s="65" t="s">
         <v>41</v>
@@ -23344,11 +23405,11 @@
       </c>
       <c r="U20" s="64">
         <f>N43</f>
-        <v>6.6289399190476193</v>
+        <v>9.3398698904761908</v>
       </c>
       <c r="V20" s="88">
         <f>O43</f>
-        <v>0.39273296083919096</v>
+        <v>0.55334258580314866</v>
       </c>
       <c r="W20" s="64">
         <f>P43</f>
@@ -23360,7 +23421,7 @@
       </c>
       <c r="AF20" s="1"/>
     </row>
-    <row r="21" spans="2:32" ht="31.2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:32" ht="31" x14ac:dyDescent="0.3">
       <c r="L21" s="30" t="s">
         <v>42</v>
       </c>
@@ -23370,11 +23431,11 @@
       </c>
       <c r="N21" s="18">
         <f>'[2]Project Summary'!$J$13-R37</f>
-        <v>2.5260024666666663</v>
+        <v>2.889856623809524</v>
       </c>
       <c r="O21" s="19">
         <f t="shared" si="1"/>
-        <v>0.42434614030135703</v>
+        <v>0.48547043026292735</v>
       </c>
       <c r="P21" s="18">
         <f>'[2]Project Summary'!$L$13-T37</f>
@@ -23382,7 +23443,7 @@
       </c>
       <c r="Q21" s="18">
         <f t="shared" si="2"/>
-        <v>0.62399753333333363</v>
+        <v>0.26014337619047589</v>
       </c>
       <c r="S21" s="65" t="s">
         <v>119</v>
@@ -23393,23 +23454,23 @@
       </c>
       <c r="U21" s="64">
         <f>R43</f>
-        <v>1.4211175190476191</v>
+        <v>0.41932514285714284</v>
       </c>
       <c r="V21" s="88">
         <f>S43</f>
-        <v>0.70537744477210818</v>
+        <v>0.20813373548128042</v>
       </c>
       <c r="W21" s="64">
         <f>T43</f>
         <v>1.41</v>
       </c>
       <c r="X21" s="63">
-        <f t="shared" ref="X20:X25" si="3">T21-W21</f>
+        <f t="shared" ref="X21:X25" si="3">T21-W21</f>
         <v>0.60469090000000025</v>
       </c>
       <c r="AF21" s="1"/>
     </row>
-    <row r="22" spans="2:32" ht="46.8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:32" ht="46.5" x14ac:dyDescent="0.3">
       <c r="L22" s="30" t="s">
         <v>152</v>
       </c>
@@ -23419,11 +23480,11 @@
       </c>
       <c r="N22" s="18">
         <f>'[3]Project Summary'!$J$13-R38</f>
-        <v>1.9911221190476196</v>
+        <v>3.967144185714286</v>
       </c>
       <c r="O22" s="19">
         <f t="shared" si="1"/>
-        <v>0.27517367712009277</v>
+        <v>0.54826052244889367</v>
       </c>
       <c r="P22" s="18">
         <f>'[3]Project Summary'!$L$13-T38</f>
@@ -23431,7 +23492,7 @@
       </c>
       <c r="Q22" s="18">
         <f t="shared" si="2"/>
-        <v>4.8388778809523805</v>
+        <v>2.8628558142857141</v>
       </c>
       <c r="S22" s="65" t="s">
         <v>120</v>
@@ -23442,11 +23503,11 @@
       </c>
       <c r="U22" s="64">
         <f>V43</f>
-        <v>0.94651043809523805</v>
+        <v>1.2693831047619049</v>
       </c>
       <c r="V22" s="88">
         <f>W43</f>
-        <v>0.45505309523809517</v>
+        <v>0.61028033882783883</v>
       </c>
       <c r="W22" s="64">
         <f>X43</f>
@@ -23458,7 +23519,7 @@
       </c>
       <c r="AF22" s="1"/>
     </row>
-    <row r="23" spans="2:32" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:32" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L23" s="30" t="s">
         <v>46</v>
       </c>
@@ -23468,11 +23529,11 @@
       </c>
       <c r="N23" s="18">
         <f>'[4]Project Summary'!$J$13-R39</f>
-        <v>1.8878342857142858</v>
+        <v>4.5381641904761905</v>
       </c>
       <c r="O23" s="19">
         <f t="shared" si="1"/>
-        <v>0.28808177322484135</v>
+        <v>0.69251967562566041</v>
       </c>
       <c r="P23" s="18">
         <f>'[4]Project Summary'!$L$13-T39</f>
@@ -23480,7 +23541,7 @@
       </c>
       <c r="Q23" s="18">
         <f t="shared" si="2"/>
-        <v>4.5821657142857148</v>
+        <v>1.9318358095238102</v>
       </c>
       <c r="S23" s="65" t="str">
         <f>CONCATENATE("Demand For Registrations 
@@ -23494,11 +23555,11 @@
       </c>
       <c r="U23" s="64">
         <f>Z43</f>
-        <v>2.8716789761904766</v>
+        <v>3.4387666428571433</v>
       </c>
       <c r="V23" s="88">
         <f>AA43</f>
-        <v>0.71565110678046417</v>
+        <v>0.85697502204272225</v>
       </c>
       <c r="W23" s="64">
         <f>AB43</f>
@@ -23510,7 +23571,7 @@
       </c>
       <c r="AF23" s="1"/>
     </row>
-    <row r="24" spans="2:32" ht="34.799999999999997" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:32" ht="35" x14ac:dyDescent="0.3">
       <c r="L24" s="123" t="s">
         <v>47</v>
       </c>
@@ -23520,11 +23581,11 @@
       </c>
       <c r="N24" s="18">
         <f>'[5]Project Summary'!$J$13-R40</f>
-        <v>3.6017421952380952</v>
+        <v>6.5512638047619038</v>
       </c>
       <c r="O24" s="19">
         <f t="shared" si="1"/>
-        <v>0.34282066162956709</v>
+        <v>0.62356172938408871</v>
       </c>
       <c r="P24" s="18">
         <f>'[5]Project Summary'!$L$13-T40</f>
@@ -23532,7 +23593,7 @@
       </c>
       <c r="Q24" s="18">
         <f t="shared" si="2"/>
-        <v>5.7182578047619046</v>
+        <v>2.7687361952380964</v>
       </c>
       <c r="S24" s="65" t="str">
         <f>CONCATENATE("Expected New Monthly
@@ -23546,11 +23607,11 @@
       </c>
       <c r="U24" s="64">
         <f>AD43</f>
-        <v>0.55087066666666673</v>
+        <v>2.8792148761904763</v>
       </c>
       <c r="V24" s="88">
         <f>AE43</f>
-        <v>5.9682629107981222E-2</v>
+        <v>0.31194093999896816</v>
       </c>
       <c r="W24" s="64">
         <f>AF43</f>
@@ -23562,7 +23623,7 @@
       </c>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="2:32" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:32" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L25" s="30" t="s">
         <v>151</v>
       </c>
@@ -23595,11 +23656,11 @@
       </c>
       <c r="U25" s="64">
         <f>AH43</f>
-        <v>2.1603028571428569</v>
+        <v>8.0735856190476198</v>
       </c>
       <c r="V25" s="88">
         <f>AI43</f>
-        <v>0.25119800664451825</v>
+        <v>0.93878902547065346</v>
       </c>
       <c r="W25" s="64">
         <f>AJ43</f>
@@ -23611,7 +23672,7 @@
       </c>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="2:32" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:32" ht="28" x14ac:dyDescent="0.3">
       <c r="L26" s="30" t="s">
         <v>50</v>
       </c>
@@ -23621,11 +23682,11 @@
       </c>
       <c r="N26" s="18">
         <f>'[7]Project Summary'!$J$13-R42</f>
-        <v>0.8671123523809523</v>
+        <v>3.5271965238095242</v>
       </c>
       <c r="O26" s="19">
         <f>'[7]Project Summary'!$K$13</f>
-        <v>0.18368100401606427</v>
+        <v>0.70827239433926192</v>
       </c>
       <c r="P26" s="18">
         <f>'[7]Project Summary'!$L$13-T42</f>
@@ -23633,11 +23694,11 @@
       </c>
       <c r="Q26" s="18">
         <f t="shared" si="2"/>
-        <v>3.6828876476190473</v>
+        <v>1.0228034761904756</v>
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="2:32" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:32" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L27" s="24" t="s">
         <v>51</v>
       </c>
@@ -23647,11 +23708,11 @@
       </c>
       <c r="N27" s="18">
         <f>SUM(N20:N26)</f>
-        <v>12.211792419047619</v>
+        <v>23.731437028571431</v>
       </c>
       <c r="O27" s="19">
         <f>N27/M27</f>
-        <v>0.31537351062219876</v>
+        <v>0.61287207896987006</v>
       </c>
       <c r="P27" s="18">
         <f>SUM(P20:P26)</f>
@@ -23659,30 +23720,30 @@
       </c>
       <c r="Q27" s="18">
         <f t="shared" si="2"/>
-        <v>20.298207580952379</v>
+        <v>8.7785629714285669</v>
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="2:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="P28" s="86"/>
       <c r="Q28" s="10"/>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="2:32" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="P29" s="86"/>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="2:32" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:32" ht="37.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L30" s="89"/>
       <c r="M30" s="89"/>
       <c r="N30" s="94"/>
       <c r="O30" s="89"/>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:32" x14ac:dyDescent="0.3">
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="2:32" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:32" ht="16" x14ac:dyDescent="0.3">
       <c r="L32" s="54"/>
       <c r="M32" s="54"/>
       <c r="N32" s="54"/>
@@ -23690,7 +23751,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="54"/>
     </row>
-    <row r="33" spans="6:40" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="6:40" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L33" s="55"/>
       <c r="M33" s="56"/>
       <c r="N33" s="56"/>
@@ -23698,7 +23759,7 @@
       <c r="P33" s="56"/>
       <c r="Q33" s="56"/>
     </row>
-    <row r="34" spans="6:40" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="6:40" ht="32.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L34" s="55"/>
       <c r="M34" s="230" t="s">
         <v>52</v>
@@ -23727,8 +23788,8 @@
       <c r="AA34" s="231"/>
       <c r="AB34" s="235"/>
       <c r="AC34" s="230" t="str">
-        <f ca="1">CONCATENATE("Expected Registrations in August ",$D$3,"'",$I$3," ")</f>
-        <v xml:space="preserve">Expected Registrations in August '₹ 0  |  ₹ 14.76 </v>
+        <f>CONCATENATE("Expected Registrations in August ",$D$3,"'",$I$3," ")</f>
+        <v xml:space="preserve">Expected Registrations in August '₹ 0  |  ₹ 27.53 </v>
       </c>
       <c r="AD34" s="231"/>
       <c r="AE34" s="231"/>
@@ -23740,7 +23801,7 @@
       <c r="AI34" s="231"/>
       <c r="AJ34" s="232"/>
     </row>
-    <row r="35" spans="6:40" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="6:40" ht="30.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L35" s="176" t="s">
         <v>55</v>
       </c>
@@ -23817,7 +23878,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="6:40" ht="101.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="6:40" ht="101.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F36" s="1" t="s">
         <v>58</v>
       </c>
@@ -23831,11 +23892,11 @@
       </c>
       <c r="N36" s="128">
         <f>'[1]Project Summary'!$J$7</f>
-        <v>1.337979</v>
+        <v>2.2578117</v>
       </c>
       <c r="O36" s="129">
         <f t="shared" ref="O36:O43" si="4">N36/M36</f>
-        <v>0.38077896646428716</v>
+        <v>0.64255657644624853</v>
       </c>
       <c r="P36" s="145">
         <f>'[1]Project Summary'!$L$7</f>
@@ -23924,7 +23985,7 @@
       <c r="AL36" s="87"/>
       <c r="AN36" s="87"/>
     </row>
-    <row r="37" spans="6:40" ht="155.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="6:40" ht="155.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G37" s="150"/>
       <c r="L37" s="185" t="s">
         <v>60</v>
@@ -23935,11 +23996,11 @@
       </c>
       <c r="N37" s="63">
         <f>'[2]Project Summary'!$J$7</f>
-        <v>2.5260024666666663</v>
+        <v>2.889856623809524</v>
       </c>
       <c r="O37" s="88">
         <f t="shared" si="4"/>
-        <v>0.42434614030135703</v>
+        <v>0.48547043026292735</v>
       </c>
       <c r="P37" s="146">
         <f>'[2]Project Summary'!$L$7</f>
@@ -24032,7 +24093,7 @@
       <c r="AL37" s="87"/>
       <c r="AN37" s="87"/>
     </row>
-    <row r="38" spans="6:40" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="6:40" ht="38.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G38" s="148"/>
       <c r="L38" s="187" t="s">
         <v>44</v>
@@ -24043,11 +24104,11 @@
       </c>
       <c r="N38" s="63">
         <f>'[3]Project Summary'!$J$7</f>
-        <v>0.1388807619047619</v>
+        <v>1.3832997714285715</v>
       </c>
       <c r="O38" s="88">
         <f t="shared" si="4"/>
-        <v>8.4984958457625631E-2</v>
+        <v>0.84647918111161613</v>
       </c>
       <c r="P38" s="146">
         <f>'[3]Project Summary'!$L$7</f>
@@ -24059,11 +24120,11 @@
       </c>
       <c r="R38" s="63">
         <f>'[3]Project Summary'!$J$8</f>
-        <v>0.37170609523809517</v>
+        <v>0.41932514285714284</v>
       </c>
       <c r="S38" s="88">
         <f t="shared" si="5"/>
-        <v>1.8585304761904757</v>
+        <v>2.0966257142857141</v>
       </c>
       <c r="T38" s="124">
         <f>'[3]Project Summary'!$L$8</f>
@@ -24075,11 +24136,11 @@
       </c>
       <c r="V38" s="63">
         <f>'[3]Project Summary'!$J$9</f>
-        <v>0.1857138095238095</v>
+        <v>0.55112704761904763</v>
       </c>
       <c r="W38" s="88">
         <f t="shared" si="6"/>
-        <v>0.1857138095238095</v>
+        <v>0.55112704761904763</v>
       </c>
       <c r="X38" s="146">
         <f>'[3]Project Summary'!$L$9</f>
@@ -24091,11 +24152,11 @@
       </c>
       <c r="Z38" s="63">
         <f>'[3]Project Summary'!$J$10</f>
-        <v>1.8522413571428575</v>
+        <v>1.8643365571428574</v>
       </c>
       <c r="AA38" s="88">
         <f t="shared" si="7"/>
-        <v>1.0002957439094733</v>
+        <v>1.0068277096465934</v>
       </c>
       <c r="AB38" s="146">
         <f>'[3]Project Summary'!$L$10</f>
@@ -24107,11 +24168,11 @@
       </c>
       <c r="AD38" s="63">
         <f>'[3]Project Summary'!$J$11</f>
-        <v>0</v>
+        <v>0.61960128571428563</v>
       </c>
       <c r="AE38" s="88">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.20722451027233632</v>
       </c>
       <c r="AF38" s="146">
         <f>'[3]Project Summary'!$L$11</f>
@@ -24123,11 +24184,11 @@
       </c>
       <c r="AH38" s="63">
         <f>'[3]Project Summary'!$J$12</f>
-        <v>0</v>
+        <v>9.9906571428571414E-2</v>
       </c>
       <c r="AI38" s="88">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>0.13145601503759397</v>
       </c>
       <c r="AJ38" s="186">
         <f>'[3]Project Summary'!$L$12</f>
@@ -24136,7 +24197,7 @@
       <c r="AL38" s="87"/>
       <c r="AN38" s="87"/>
     </row>
-    <row r="39" spans="6:40" ht="91.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="6:40" ht="91.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G39" s="150"/>
       <c r="L39" s="185" t="s">
         <v>61</v>
@@ -24147,11 +24208,11 @@
       </c>
       <c r="N39" s="63">
         <f>'[4]Project Summary'!$J$7</f>
-        <v>1.0101445714285715</v>
+        <v>1.531511523809524</v>
       </c>
       <c r="O39" s="88">
         <f t="shared" si="4"/>
-        <v>0.55277046193536505</v>
+        <v>0.83807244667788394</v>
       </c>
       <c r="P39" s="146">
         <f>'[4]Project Summary'!$L$7</f>
@@ -24179,11 +24240,11 @@
       </c>
       <c r="V39" s="63">
         <f>'[4]Project Summary'!$J$9</f>
-        <v>0.251112</v>
+        <v>0.19523809523809524</v>
       </c>
       <c r="W39" s="88">
         <f t="shared" si="6"/>
-        <v>0.35873142857142859</v>
+        <v>0.27891156462585037</v>
       </c>
       <c r="X39" s="146">
         <f>'[4]Project Summary'!$L$9</f>
@@ -24211,11 +24272,11 @@
       </c>
       <c r="AD39" s="63">
         <f>'[4]Project Summary'!$J$11</f>
-        <v>0.24822390476190476</v>
+        <v>1.9486154285714288</v>
       </c>
       <c r="AE39" s="88">
         <f t="shared" si="8"/>
-        <v>8.3859427284427288E-2</v>
+        <v>0.65831602316602322</v>
       </c>
       <c r="AF39" s="146">
         <f>'[4]Project Summary'!$L$11</f>
@@ -24227,11 +24288,11 @@
       </c>
       <c r="AH39" s="63">
         <f>'[4]Project Summary'!$J$12</f>
-        <v>0.62946580952380948</v>
+        <v>1.0580372380952381</v>
       </c>
       <c r="AI39" s="88">
         <f t="shared" si="9"/>
-        <v>0.47686803751803747</v>
+        <v>0.8015433621933622</v>
       </c>
       <c r="AJ39" s="186">
         <f>'[4]Project Summary'!$L$12</f>
@@ -24240,7 +24301,7 @@
       <c r="AL39" s="87"/>
       <c r="AN39" s="87"/>
     </row>
-    <row r="40" spans="6:40" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="6:40" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G40" s="150"/>
       <c r="L40" s="188" t="s">
         <v>47</v>
@@ -24251,11 +24312,11 @@
       </c>
       <c r="N40" s="63">
         <f>'[5]Project Summary'!$J$7</f>
-        <v>1.4609841952380953</v>
+        <v>0.6769339380952375</v>
       </c>
       <c r="O40" s="88">
         <f t="shared" si="4"/>
-        <v>0.60598843973837913</v>
+        <v>0.28077931458076949</v>
       </c>
       <c r="P40" s="146">
         <f>'[5]Project Summary'!$L$7</f>
@@ -24267,11 +24328,11 @@
       </c>
       <c r="R40" s="63">
         <f>'[5]Project Summary'!$J$8</f>
-        <v>0.20471047619047619</v>
+        <v>0</v>
       </c>
       <c r="S40" s="88">
         <f t="shared" si="5"/>
-        <v>0.39367399267399267</v>
+        <v>0</v>
       </c>
       <c r="T40" s="124">
         <f>'[5]Project Summary'!$L$8</f>
@@ -24283,11 +24344,11 @@
       </c>
       <c r="V40" s="63">
         <f>'[5]Project Summary'!$J$9</f>
-        <v>0</v>
+        <v>1.4285714285714284E-2</v>
       </c>
       <c r="W40" s="88">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>7.9365079365079361E-2</v>
       </c>
       <c r="X40" s="146">
         <f>'[5]Project Summary'!$L$9</f>
@@ -24299,11 +24360,11 @@
       </c>
       <c r="Z40" s="63">
         <f>'[5]Project Summary'!$J$10</f>
-        <v>1.0194376190476191</v>
+        <v>1.5744300857142859</v>
       </c>
       <c r="AA40" s="88">
         <f t="shared" si="7"/>
-        <v>0.59432435879590562</v>
+        <v>0.91788073510108226</v>
       </c>
       <c r="AB40" s="146">
         <f>'[5]Project Summary'!$L$10</f>
@@ -24315,11 +24376,11 @@
       </c>
       <c r="AD40" s="63">
         <f>'[5]Project Summary'!$J$11</f>
-        <v>0.30264676190476192</v>
+        <v>0.31099816190476187</v>
       </c>
       <c r="AE40" s="88">
         <f t="shared" si="8"/>
-        <v>0.14982512965582273</v>
+        <v>0.15395948609146629</v>
       </c>
       <c r="AF40" s="146">
         <f>'[5]Project Summary'!$L$11</f>
@@ -24331,11 +24392,11 @@
       </c>
       <c r="AH40" s="63">
         <f>'[5]Project Summary'!$J$12</f>
-        <v>0.81867361904761904</v>
+        <v>3.9889016190476192</v>
       </c>
       <c r="AI40" s="88">
         <f t="shared" si="9"/>
-        <v>0.18776917868064655</v>
+        <v>0.91488569244211437</v>
       </c>
       <c r="AJ40" s="186">
         <f>'[5]Project Summary'!$L$12</f>
@@ -24344,7 +24405,7 @@
       <c r="AL40" s="87"/>
       <c r="AN40" s="87"/>
     </row>
-    <row r="41" spans="6:40" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="6:40" ht="38.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G41" s="151"/>
       <c r="L41" s="189" t="s">
         <v>122</v>
@@ -24371,11 +24432,11 @@
       </c>
       <c r="R41" s="63">
         <f>'[6]Project Summary'!$J$8</f>
-        <v>0.79708190000000001</v>
+        <v>0</v>
       </c>
       <c r="S41" s="88">
         <f t="shared" si="5"/>
-        <v>1.4070870712047066</v>
+        <v>0</v>
       </c>
       <c r="T41" s="124">
         <f>'[6]Project Summary'!$L$8</f>
@@ -24448,7 +24509,7 @@
       <c r="AL41" s="87"/>
       <c r="AN41" s="87"/>
     </row>
-    <row r="42" spans="6:40" ht="192.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="6:40" ht="192.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G42" s="150"/>
       <c r="L42" s="185" t="s">
         <v>63</v>
@@ -24459,11 +24520,11 @@
       </c>
       <c r="N42" s="63">
         <f>'[7]Project Summary'!$J$7</f>
-        <v>0.15494892380952385</v>
+        <v>0.60045633333333326</v>
       </c>
       <c r="O42" s="88">
         <f t="shared" si="4"/>
-        <v>0.1006161842918986</v>
+        <v>0.3899067099567099</v>
       </c>
       <c r="P42" s="146">
         <f>'[7]Project Summary'!$L$7</f>
@@ -24475,11 +24536,11 @@
       </c>
       <c r="R42" s="63">
         <f>'[7]Project Summary'!$J$8</f>
-        <v>4.7619047619047623E-2</v>
+        <v>0</v>
       </c>
       <c r="S42" s="88">
         <f t="shared" si="5"/>
-        <v>0.25062656641604014</v>
+        <v>0</v>
       </c>
       <c r="T42" s="124">
         <f>'[7]Project Summary'!$L$8</f>
@@ -24491,11 +24552,11 @@
       </c>
       <c r="V42" s="63">
         <f>'[7]Project Summary'!$J$9</f>
-        <v>0.34945942857142859</v>
+        <v>0.34850704761904766</v>
       </c>
       <c r="W42" s="88">
         <f t="shared" si="6"/>
-        <v>1.7472971428571429</v>
+        <v>1.7425352380952381</v>
       </c>
       <c r="X42" s="146">
         <f>'[7]Project Summary'!$L$9</f>
@@ -24539,11 +24600,11 @@
       </c>
       <c r="AH42" s="63">
         <f>'[7]Project Summary'!$J$12</f>
-        <v>0.71216342857142856</v>
+        <v>2.9267401904761905</v>
       </c>
       <c r="AI42" s="88">
         <f t="shared" si="9"/>
-        <v>0.35787106963388371</v>
+        <v>1.470723713807131</v>
       </c>
       <c r="AJ42" s="186">
         <f>'[7]Project Summary'!$L$12</f>
@@ -24552,7 +24613,7 @@
       <c r="AL42" s="87"/>
       <c r="AN42" s="87"/>
     </row>
-    <row r="43" spans="6:40" ht="38.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="6:40" ht="38.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G43" s="152"/>
       <c r="L43" s="190" t="s">
         <v>51</v>
@@ -24563,11 +24624,11 @@
       </c>
       <c r="N43" s="192">
         <f>SUM(N36:N42)</f>
-        <v>6.6289399190476193</v>
+        <v>9.3398698904761908</v>
       </c>
       <c r="O43" s="193">
         <f t="shared" si="4"/>
-        <v>0.39273296083919096</v>
+        <v>0.55334258580314866</v>
       </c>
       <c r="P43" s="194">
         <f>SUM(P36:P42)</f>
@@ -24579,11 +24640,11 @@
       </c>
       <c r="R43" s="192">
         <f>SUM(R36:R42)</f>
-        <v>1.4211175190476191</v>
+        <v>0.41932514285714284</v>
       </c>
       <c r="S43" s="193">
         <f t="shared" si="5"/>
-        <v>0.70537744477210818</v>
+        <v>0.20813373548128042</v>
       </c>
       <c r="T43" s="195">
         <f>SUM(T36:T42)</f>
@@ -24595,11 +24656,11 @@
       </c>
       <c r="V43" s="192">
         <f>SUM(V36:V42)</f>
-        <v>0.94651043809523805</v>
+        <v>1.2693831047619049</v>
       </c>
       <c r="W43" s="193">
         <f t="shared" si="6"/>
-        <v>0.45505309523809517</v>
+        <v>0.61028033882783883</v>
       </c>
       <c r="X43" s="194">
         <f>SUM(X36:X42)</f>
@@ -24611,11 +24672,11 @@
       </c>
       <c r="Z43" s="192">
         <f>SUM(Z36:Z42)</f>
-        <v>2.8716789761904766</v>
+        <v>3.4387666428571433</v>
       </c>
       <c r="AA43" s="193">
         <f t="shared" si="7"/>
-        <v>0.71565110678046417</v>
+        <v>0.85697502204272225</v>
       </c>
       <c r="AB43" s="194">
         <f>SUM(AB36:AB42)</f>
@@ -24627,11 +24688,11 @@
       </c>
       <c r="AD43" s="192">
         <f>SUM(AD36:AD42)</f>
-        <v>0.55087066666666673</v>
+        <v>2.8792148761904763</v>
       </c>
       <c r="AE43" s="193">
         <f t="shared" si="8"/>
-        <v>5.9682629107981222E-2</v>
+        <v>0.31194093999896816</v>
       </c>
       <c r="AF43" s="194">
         <f>SUM(AF36:AF42)</f>
@@ -24643,18 +24704,18 @@
       </c>
       <c r="AH43" s="192">
         <f>SUM(AH36:AH42)</f>
-        <v>2.1603028571428569</v>
+        <v>8.0735856190476198</v>
       </c>
       <c r="AI43" s="193">
         <f t="shared" si="9"/>
-        <v>0.25119800664451825</v>
+        <v>0.93878902547065346</v>
       </c>
       <c r="AJ43" s="197">
         <f>SUM(AJ36:AJ42)</f>
         <v>7.5600000000000005</v>
       </c>
     </row>
-    <row r="44" spans="6:40" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="44" spans="6:40" ht="15" x14ac:dyDescent="0.3">
       <c r="L44" s="111"/>
       <c r="M44" s="112"/>
       <c r="N44" s="112"/>
@@ -24681,7 +24742,7 @@
       <c r="AI44" s="158"/>
       <c r="AJ44" s="112"/>
     </row>
-    <row r="45" spans="6:40" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="6:40" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L45" s="111"/>
       <c r="M45" s="112"/>
       <c r="N45" s="112"/>
@@ -24696,7 +24757,7 @@
       </c>
       <c r="R45" s="112">
         <f>N27-R43</f>
-        <v>10.790674899999999</v>
+        <v>23.312111885714287</v>
       </c>
       <c r="S45" s="158"/>
       <c r="T45" s="112"/>
@@ -24717,7 +24778,7 @@
       <c r="AI45" s="158"/>
       <c r="AJ45" s="112"/>
     </row>
-    <row r="46" spans="6:40" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="46" spans="6:40" ht="15" x14ac:dyDescent="0.3">
       <c r="L46" s="111"/>
       <c r="M46" s="112"/>
       <c r="N46" s="112"/>
@@ -24744,7 +24805,7 @@
       <c r="AI46" s="158"/>
       <c r="AJ46" s="112"/>
     </row>
-    <row r="47" spans="6:40" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="47" spans="6:40" ht="15" x14ac:dyDescent="0.3">
       <c r="L47" s="111"/>
       <c r="M47" s="112"/>
       <c r="N47" s="112">
@@ -24774,13 +24835,13 @@
       <c r="AI47" s="158"/>
       <c r="AJ47" s="112"/>
     </row>
-    <row r="51" spans="12:29" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="12:29" ht="29.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="R51" s="66"/>
       <c r="U51" s="60" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="52" spans="12:29" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="12:29" ht="35.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L52" s="233" t="s">
         <v>64</v>
       </c>
@@ -24817,7 +24878,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="12:29" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="12:29" ht="31.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L53" s="13" t="s">
         <v>66</v>
       </c>
@@ -24847,23 +24908,23 @@
       </c>
       <c r="V53" s="168">
         <f>'[1]Project Summary'!$L$18</f>
-        <v>2.2594639999999999</v>
+        <v>1.3896313</v>
       </c>
       <c r="W53" s="169">
         <f>'[2]Project Summary'!$L$18</f>
-        <v>3.2219701095238098</v>
+        <v>2.8999899238095237</v>
       </c>
       <c r="X53" s="169">
-        <f>'[3]Project Summary'!$L$18</f>
-        <v>1.495299738095238</v>
+        <f>'[3]Project Summary'!$M$18</f>
+        <v>0.86600460952380953</v>
       </c>
       <c r="Y53" s="169">
         <f>'[4]Project Summary'!$L$18</f>
-        <v>0.93933931428571438</v>
+        <v>0.31219203809523804</v>
       </c>
       <c r="Z53" s="169">
         <f>'[5]Project Summary'!$L$18</f>
-        <v>4.1346330333333334</v>
+        <v>1.869566176190476</v>
       </c>
       <c r="AA53" s="169">
         <f>'[6]Project Summary'!$L$18</f>
@@ -24871,14 +24932,14 @@
       </c>
       <c r="AB53" s="169">
         <f>'[7]Project Summary'!$L$18</f>
-        <v>4.8191245476190474</v>
+        <v>2.1418024142857144</v>
       </c>
       <c r="AC53" s="169">
         <f>SUM(V53:AB53)</f>
-        <v>17.037739842857142</v>
+        <v>9.6470955619047629</v>
       </c>
     </row>
-    <row r="54" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="12:29" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L54" s="20" t="s">
         <v>68</v>
       </c>
@@ -24910,20 +24971,20 @@
         <v>3.82143E-2</v>
       </c>
       <c r="X54" s="169">
-        <f>'[3]Project Summary'!$L$19</f>
+        <f>'[3]Project Summary'!$M$19</f>
         <v>9.9999999999999995E-8</v>
       </c>
       <c r="Y54" s="169">
         <f>'[4]Project Summary'!$L$19</f>
-        <v>0</v>
+        <v>4.3803000000000002E-2</v>
       </c>
       <c r="Z54" s="169">
         <f>'[5]Project Summary'!$L$19</f>
-        <v>0.38415322380952377</v>
+        <v>0.27078962380952376</v>
       </c>
       <c r="AA54" s="169">
         <f>'[6]Project Summary'!$L$19</f>
-        <v>2.7761472</v>
+        <v>2.5145689999999998</v>
       </c>
       <c r="AB54" s="169">
         <f>'[7]Project Summary'!$L$19</f>
@@ -24931,10 +24992,10 @@
       </c>
       <c r="AC54" s="169">
         <f>SUM(V54:AB54)</f>
-        <v>3.198514823809524</v>
+        <v>2.8673760238095234</v>
       </c>
     </row>
-    <row r="55" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="12:29" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L55" s="22" t="s">
         <v>69</v>
       </c>
@@ -24966,12 +25027,12 @@
         <v>0</v>
       </c>
       <c r="X55" s="169">
-        <f>'[3]Project Summary'!$L$20</f>
-        <v>0</v>
+        <f>'[3]Project Summary'!$M$20</f>
+        <v>3.5868595238095241E-2</v>
       </c>
       <c r="Y55" s="169">
         <f>'[4]Project Summary'!$L$20</f>
-        <v>9.745938571428571E-2</v>
+        <v>3.4285704761904755E-2</v>
       </c>
       <c r="Z55" s="169">
         <f>'[5]Project Summary'!$L$20</f>
@@ -24983,14 +25044,14 @@
       </c>
       <c r="AB55" s="169">
         <f>'[7]Project Summary'!$L$20</f>
-        <v>3.5778771428571408E-2</v>
+        <v>3.6731152380952356E-2</v>
       </c>
       <c r="AC55" s="169">
         <f>SUM(V55:AB55)</f>
-        <v>0.13323815714285711</v>
+        <v>0.10688545238095236</v>
       </c>
     </row>
-    <row r="56" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="12:29" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L56" s="22" t="s">
         <v>71</v>
       </c>
@@ -25025,8 +25086,8 @@
         <v>0</v>
       </c>
       <c r="X56" s="169">
-        <f>'[3]Project Summary'!$L$21</f>
-        <v>9.190476201474667E-8</v>
+        <f>'[3]Project Summary'!$M$21</f>
+        <v>0</v>
       </c>
       <c r="Y56" s="169">
         <f>'[4]Project Summary'!$L$21</f>
@@ -25034,7 +25095,7 @@
       </c>
       <c r="Z56" s="169">
         <f>'[5]Project Summary'!$L$21</f>
-        <v>0.79152638095238093</v>
+        <v>0.23760991904761902</v>
       </c>
       <c r="AA56" s="169">
         <f>'[6]Project Summary'!$L$21</f>
@@ -25046,10 +25107,10 @@
       </c>
       <c r="AC56" s="169">
         <f>SUM(V56:AB56)</f>
-        <v>1.2372245728571429</v>
+        <v>0.68330801904761906</v>
       </c>
     </row>
-    <row r="57" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="12:29" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L57" s="22" t="s">
         <v>72</v>
       </c>
@@ -25084,16 +25145,16 @@
         <v>0</v>
       </c>
       <c r="X57" s="169">
-        <f>'[3]Project Summary'!$L$22</f>
-        <v>0</v>
+        <f>'[3]Project Summary'!$M$22</f>
+        <v>1.4565151000000001</v>
       </c>
       <c r="Y57" s="169">
         <f>'[4]Project Summary'!$L$22</f>
-        <v>1.7014095238095231E-2</v>
+        <v>1.5554633333333326E-2</v>
       </c>
       <c r="Z57" s="169">
         <f>'[5]Project Summary'!$L$22</f>
-        <v>0.91420216666666665</v>
+        <v>0.90476400000000001</v>
       </c>
       <c r="AA57" s="169">
         <f>'[6]Project Summary'!$L$22</f>
@@ -25105,10 +25166,10 @@
       </c>
       <c r="AC57" s="169">
         <f>SUM(V57:AB57)</f>
-        <v>0.93121626190476192</v>
+        <v>2.3768337333333336</v>
       </c>
     </row>
-    <row r="58" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="12:29" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L58" s="22" t="s">
         <v>73</v>
       </c>
@@ -25133,38 +25194,38 @@
       </c>
       <c r="V58" s="167">
         <f t="shared" ref="V58:AC58" si="11">SUM(V53:V57)</f>
-        <v>2.2594639999999999</v>
+        <v>1.3896313</v>
       </c>
       <c r="W58" s="167">
         <f t="shared" si="11"/>
-        <v>3.2601844095238097</v>
+        <v>2.9382042238095236</v>
       </c>
       <c r="X58" s="167">
         <f t="shared" si="11"/>
-        <v>1.4952999300000001</v>
+        <v>2.3583884047619046</v>
       </c>
       <c r="Y58" s="167">
         <f t="shared" si="11"/>
-        <v>1.4995108952380953</v>
+        <v>0.85153347619047604</v>
       </c>
       <c r="Z58" s="167">
         <f t="shared" si="11"/>
-        <v>6.2245148047619043</v>
+        <v>3.282729719047619</v>
       </c>
       <c r="AA58" s="167">
         <f t="shared" si="11"/>
-        <v>2.9440563000000002</v>
+        <v>2.6824781</v>
       </c>
       <c r="AB58" s="167">
         <f t="shared" si="11"/>
-        <v>4.8549033190476187</v>
+        <v>2.1785335666666668</v>
       </c>
       <c r="AC58" s="167">
         <f t="shared" si="11"/>
-        <v>22.537933658571429</v>
+        <v>15.681498790476191</v>
       </c>
     </row>
-    <row r="59" spans="12:29" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="12:29" ht="26.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L59" s="23" t="s">
         <v>75</v>
       </c>
@@ -25185,7 +25246,7 @@
       </c>
       <c r="S59" s="45"/>
     </row>
-    <row r="60" spans="12:29" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="12:29" ht="15.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L60" s="25" t="s">
         <v>76</v>
       </c>
@@ -25247,63 +25308,63 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CFB7E58-C50C-4044-8BD5-6955ABCC76AE}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B1:BA12"/>
-  <sheetFormatPr defaultColWidth="25.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="25.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.77734375" customWidth="1"/>
-    <col min="2" max="2" width="24.109375" customWidth="1"/>
-    <col min="3" max="3" width="20.5546875" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.81640625" customWidth="1"/>
+    <col min="2" max="2" width="24.08984375" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" customWidth="1"/>
+    <col min="4" max="4" width="17.6328125" customWidth="1"/>
+    <col min="5" max="5" width="21.6328125" customWidth="1"/>
+    <col min="6" max="6" width="18.36328125" customWidth="1"/>
+    <col min="7" max="7" width="22.36328125" customWidth="1"/>
     <col min="8" max="8" width="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.88671875" customWidth="1"/>
-    <col min="11" max="11" width="20.6640625" customWidth="1"/>
-    <col min="12" max="12" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.33203125" customWidth="1"/>
-    <col min="14" max="14" width="25.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.90625" customWidth="1"/>
+    <col min="11" max="11" width="20.6328125" customWidth="1"/>
+    <col min="12" max="12" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.36328125" customWidth="1"/>
+    <col min="14" max="14" width="25.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.6328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.6328125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.109375" customWidth="1"/>
-    <col min="21" max="21" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.6328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25.6328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.08984375" customWidth="1"/>
+    <col min="21" max="21" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="25.08984375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="23.36328125" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="20" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="38.88671875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="38.88671875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="21.90625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="34.6328125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="38.90625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="32.90625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="38.90625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="23.36328125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="20.36328125" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="27" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="0" hidden="1" customWidth="1"/>
-    <col min="47" max="47" width="5.109375" customWidth="1"/>
-    <col min="48" max="48" width="35.88671875" customWidth="1"/>
-    <col min="49" max="51" width="21.109375" customWidth="1"/>
+    <col min="47" max="47" width="5.08984375" customWidth="1"/>
+    <col min="48" max="48" width="35.90625" customWidth="1"/>
+    <col min="49" max="51" width="21.08984375" customWidth="1"/>
     <col min="52" max="52" width="17" customWidth="1"/>
-    <col min="53" max="53" width="21.109375" customWidth="1"/>
-    <col min="54" max="54" width="11.5546875" customWidth="1"/>
-    <col min="55" max="55" width="13.21875" customWidth="1"/>
+    <col min="53" max="53" width="21.08984375" customWidth="1"/>
+    <col min="54" max="54" width="11.54296875" customWidth="1"/>
+    <col min="55" max="55" width="13.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:53" ht="57.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:53" ht="57.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="13" t="s">
         <v>32</v>
       </c>
@@ -25474,7 +25535,7 @@
         <v>Balance</v>
       </c>
     </row>
-    <row r="2" spans="2:53" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:53" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="216" t="str">
         <f>Overall_Draft!L20</f>
         <v>RAGHAV 
@@ -25486,11 +25547,11 @@
       </c>
       <c r="D2" s="217">
         <f>Overall_Draft!N20</f>
-        <v>1.337979</v>
+        <v>2.2578117</v>
       </c>
       <c r="E2" s="218">
         <f t="shared" ref="E2:E9" si="0">IFERROR(D2/C2,"")</f>
-        <v>0.38077896646428716</v>
+        <v>0.64255657644624853</v>
       </c>
       <c r="F2" s="217">
         <f>Overall_Draft!P20</f>
@@ -25498,7 +25559,7 @@
       </c>
       <c r="G2" s="217">
         <f>Overall_Draft!Q20</f>
-        <v>0.85202099999999992</v>
+        <v>-6.781170000000003E-2</v>
       </c>
       <c r="H2" s="219" t="str">
         <f>Overall_Draft!L4</f>
@@ -25514,7 +25575,7 @@
       </c>
       <c r="K2" s="205">
         <f>Overall_Draft!O4</f>
-        <v>1.337979</v>
+        <v>2.3498838000000002</v>
       </c>
       <c r="L2" s="219">
         <f>Overall_Draft!P4</f>
@@ -25526,11 +25587,11 @@
       </c>
       <c r="N2" s="205">
         <f>Overall_Draft!R4</f>
-        <v>206.96726649999999</v>
+        <v>208.8346166</v>
       </c>
       <c r="O2" s="205">
         <f>Overall_Draft!S4</f>
-        <v>2.2594641000000002</v>
+        <v>1.3896314000000001</v>
       </c>
       <c r="P2" s="219">
         <f>Overall_Draft!T4</f>
@@ -25538,7 +25599,7 @@
       </c>
       <c r="Q2" s="219">
         <f>Overall_Draft!U4</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" s="219">
         <f>Overall_Draft!V4</f>
@@ -25560,11 +25621,11 @@
       </c>
       <c r="W2" s="205">
         <f>Overall_Draft!N36</f>
-        <v>1.337979</v>
+        <v>2.2578117</v>
       </c>
       <c r="X2" s="206">
         <f>Overall_Draft!O36</f>
-        <v>0.38077896646428716</v>
+        <v>0.64255657644624853</v>
       </c>
       <c r="Y2" s="205">
         <f>Overall_Draft!P36</f>
@@ -25661,11 +25722,11 @@
       </c>
       <c r="AX2" s="205">
         <f>Overall!U20</f>
-        <v>6.6289399190476193</v>
+        <v>9.3398698904761908</v>
       </c>
       <c r="AY2" s="206">
         <f>Overall!V20</f>
-        <v>0.38745336663015251</v>
+        <v>0.54590388163791081</v>
       </c>
       <c r="AZ2" s="205">
         <f>Overall!W20</f>
@@ -25676,7 +25737,7 @@
         <v>5.3990006952380938</v>
       </c>
     </row>
-    <row r="3" spans="2:53" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:53" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="220" t="str">
         <f>Overall_Draft!L21</f>
         <v>RAGHAV 
@@ -25688,11 +25749,11 @@
       </c>
       <c r="D3" s="221">
         <f>Overall_Draft!N21</f>
-        <v>2.5260024666666663</v>
+        <v>2.889856623809524</v>
       </c>
       <c r="E3" s="222">
         <f t="shared" si="0"/>
-        <v>0.42434614030135703</v>
+        <v>0.48547043026292735</v>
       </c>
       <c r="F3" s="221">
         <f>Overall_Draft!P21</f>
@@ -25700,7 +25761,7 @@
       </c>
       <c r="G3" s="221">
         <f>Overall_Draft!Q21</f>
-        <v>0.62399753333333363</v>
+        <v>0.26014337619047589</v>
       </c>
       <c r="H3" s="123" t="str">
         <f>Overall_Draft!L5</f>
@@ -25716,7 +25777,7 @@
       </c>
       <c r="K3" s="209">
         <f>Overall_Draft!O5</f>
-        <v>2.5260024666666676</v>
+        <v>2.8898566238095249</v>
       </c>
       <c r="L3" s="123">
         <f>Overall_Draft!P5</f>
@@ -25728,11 +25789,11 @@
       </c>
       <c r="N3" s="209">
         <f>Overall_Draft!R5</f>
-        <v>100.57513296666666</v>
+        <v>100.93898712380951</v>
       </c>
       <c r="O3" s="209">
         <f>Overall_Draft!S5</f>
-        <v>3.2601844095238097</v>
+        <v>2.9382042238095241</v>
       </c>
       <c r="P3" s="123">
         <f>Overall_Draft!T5</f>
@@ -25762,11 +25823,11 @@
       </c>
       <c r="W3" s="209">
         <f>Overall_Draft!N37</f>
-        <v>2.5260024666666663</v>
+        <v>2.889856623809524</v>
       </c>
       <c r="X3" s="210">
         <f>Overall_Draft!O37</f>
-        <v>0.42434614030135703</v>
+        <v>0.48547043026292735</v>
       </c>
       <c r="Y3" s="209">
         <f>Overall_Draft!P37</f>
@@ -25863,11 +25924,11 @@
       </c>
       <c r="AX3" s="209">
         <f>Overall!U21</f>
-        <v>0.62403561904761906</v>
+        <v>0.41932514285714284</v>
       </c>
       <c r="AY3" s="210">
         <f>Overall!V21</f>
-        <v>0.43090005329157366</v>
+        <v>0.28954633499830984</v>
       </c>
       <c r="AZ3" s="209">
         <f>Overall!W21</f>
@@ -25878,7 +25939,7 @@
         <v>3.8214300000000145E-2</v>
       </c>
     </row>
-    <row r="4" spans="2:53" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:53" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="220" t="str">
         <f>Overall_Draft!L22</f>
         <v>RAGHAV 
@@ -25890,11 +25951,11 @@
       </c>
       <c r="D4" s="221">
         <f>Overall_Draft!N22</f>
-        <v>1.9911221190476196</v>
+        <v>3.967144185714286</v>
       </c>
       <c r="E4" s="222">
         <f t="shared" si="0"/>
-        <v>0.27517367712009277</v>
+        <v>0.54826052244889367</v>
       </c>
       <c r="F4" s="221">
         <f>Overall_Draft!P22</f>
@@ -25902,7 +25963,7 @@
       </c>
       <c r="G4" s="221">
         <f>Overall_Draft!Q22</f>
-        <v>4.8388778809523805</v>
+        <v>2.8628558142857141</v>
       </c>
       <c r="H4" s="123" t="str">
         <f>Overall_Draft!L6</f>
@@ -25910,38 +25971,38 @@
       </c>
       <c r="I4" s="123">
         <f>Overall_Draft!M6</f>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J4" s="209">
-        <f ca="1">Overall_Draft!N6</f>
+        <f>Overall_Draft!N6</f>
         <v>0</v>
       </c>
       <c r="K4" s="209">
         <f>Overall_Draft!O6</f>
-        <v>2.7321155142857152</v>
+        <v>4.9375963761904789</v>
       </c>
       <c r="L4" s="123">
         <f>Overall_Draft!P6</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4" s="209">
         <f>Overall_Draft!Q6</f>
-        <v>49.654334429999999</v>
+        <v>52.623265600000003</v>
       </c>
       <c r="N4" s="209">
         <f>Overall_Draft!R6</f>
-        <v>49.215646423809524</v>
+        <v>51.599938876190471</v>
       </c>
       <c r="O4" s="209">
         <f>Overall_Draft!S6</f>
-        <v>1.4952999300000001</v>
+        <v>2.358388404761905</v>
       </c>
       <c r="P4" s="123">
         <f>Overall_Draft!T6</f>
         <v>16</v>
       </c>
       <c r="Q4" s="123">
-        <f ca="1">Overall_Draft!U6</f>
+        <f>Overall_Draft!U6</f>
         <v>9</v>
       </c>
       <c r="R4" s="123">
@@ -25964,11 +26025,11 @@
       </c>
       <c r="W4" s="209">
         <f>Overall_Draft!N38</f>
-        <v>0.1388807619047619</v>
+        <v>1.3832997714285715</v>
       </c>
       <c r="X4" s="210">
         <f>Overall_Draft!O38</f>
-        <v>8.4984958457625631E-2</v>
+        <v>0.84647918111161613</v>
       </c>
       <c r="Y4" s="209">
         <f>Overall_Draft!P38</f>
@@ -25980,11 +26041,11 @@
       </c>
       <c r="AA4" s="209">
         <f>Overall_Draft!R38</f>
-        <v>0.37170609523809517</v>
+        <v>0.41932514285714284</v>
       </c>
       <c r="AB4" s="210">
         <f>Overall_Draft!S38</f>
-        <v>1.8585304761904757</v>
+        <v>2.0966257142857141</v>
       </c>
       <c r="AC4" s="209">
         <f>Overall_Draft!T38</f>
@@ -25996,11 +26057,11 @@
       </c>
       <c r="AE4" s="209">
         <f>Overall_Draft!V38</f>
-        <v>0.1857138095238095</v>
+        <v>0.55112704761904763</v>
       </c>
       <c r="AF4" s="210">
         <f>Overall_Draft!W38</f>
-        <v>0.1857138095238095</v>
+        <v>0.55112704761904763</v>
       </c>
       <c r="AG4" s="209">
         <f>Overall_Draft!X38</f>
@@ -26012,11 +26073,11 @@
       </c>
       <c r="AI4" s="209">
         <f>Overall_Draft!Z38</f>
-        <v>1.8522413571428575</v>
+        <v>1.8643365571428574</v>
       </c>
       <c r="AJ4" s="210">
         <f>Overall_Draft!AA38</f>
-        <v>1.0002957439094733</v>
+        <v>1.0068277096465934</v>
       </c>
       <c r="AK4" s="209">
         <f>Overall_Draft!AB38</f>
@@ -26028,11 +26089,11 @@
       </c>
       <c r="AM4" s="209">
         <f>Overall_Draft!AD38</f>
-        <v>0</v>
+        <v>0.61960128571428563</v>
       </c>
       <c r="AN4" s="210">
         <f>Overall_Draft!AE38</f>
-        <v>0</v>
+        <v>0.20722451027233632</v>
       </c>
       <c r="AO4" s="209">
         <f>Overall_Draft!AF38</f>
@@ -26044,11 +26105,11 @@
       </c>
       <c r="AQ4" s="209">
         <f>Overall_Draft!AH38</f>
-        <v>0</v>
+        <v>9.9906571428571414E-2</v>
       </c>
       <c r="AR4" s="210">
         <f>Overall_Draft!AI38</f>
-        <v>0</v>
+        <v>0.13145601503759397</v>
       </c>
       <c r="AS4" s="211">
         <f>Overall_Draft!AJ38</f>
@@ -26065,11 +26126,11 @@
       </c>
       <c r="AX4" s="209">
         <f>Overall!U22</f>
-        <v>0.78628523809523809</v>
+        <v>1.1091579047619047</v>
       </c>
       <c r="AY4" s="210">
         <f>Overall!V22</f>
-        <v>0.37802174908424907</v>
+        <v>0.53324899267399262</v>
       </c>
       <c r="AZ4" s="209">
         <f>Overall!W22</f>
@@ -26080,7 +26141,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="5" spans="2:53" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:53" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="220" t="str">
         <f>Overall_Draft!L23</f>
         <v>RAGHAV 
@@ -26092,11 +26153,11 @@
       </c>
       <c r="D5" s="221">
         <f>Overall_Draft!N23</f>
-        <v>1.8878342857142858</v>
+        <v>4.5381641904761905</v>
       </c>
       <c r="E5" s="222">
         <f t="shared" si="0"/>
-        <v>0.28808177322484135</v>
+        <v>0.69251967562566041</v>
       </c>
       <c r="F5" s="221">
         <f>Overall_Draft!P23</f>
@@ -26104,7 +26165,7 @@
       </c>
       <c r="G5" s="221">
         <f>Overall_Draft!Q23</f>
-        <v>4.5821657142857148</v>
+        <v>1.9318358095238102</v>
       </c>
       <c r="H5" s="123" t="str">
         <f>Overall_Draft!L7</f>
@@ -26112,38 +26173,38 @@
       </c>
       <c r="I5" s="123">
         <f>Overall_Draft!M7</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J5" s="209">
-        <f ca="1">Overall_Draft!N7</f>
+        <f>Overall_Draft!N7</f>
         <v>0</v>
       </c>
       <c r="K5" s="209">
         <f>Overall_Draft!O7</f>
-        <v>2.1389462857142854</v>
+        <v>4.8224563857142861</v>
       </c>
       <c r="L5" s="123">
         <f>Overall_Draft!P7</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="209">
         <f>Overall_Draft!Q7</f>
-        <v>36.135609299999999</v>
+        <v>36.268466400000001</v>
       </c>
       <c r="N5" s="209">
         <f>Overall_Draft!R7</f>
-        <v>35.697580685714279</v>
+        <v>38.381090785714285</v>
       </c>
       <c r="O5" s="209">
         <f>Overall_Draft!S7</f>
-        <v>1.4995108952380953</v>
+        <v>0.85153347619047615</v>
       </c>
       <c r="P5" s="123">
         <f>Overall_Draft!T7</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q5" s="123">
-        <f ca="1">Overall_Draft!U7</f>
+        <f>Overall_Draft!U7</f>
         <v>1</v>
       </c>
       <c r="R5" s="123">
@@ -26166,11 +26227,11 @@
       </c>
       <c r="W5" s="209">
         <f>Overall_Draft!N39</f>
-        <v>1.0101445714285715</v>
+        <v>1.531511523809524</v>
       </c>
       <c r="X5" s="210">
         <f>Overall_Draft!O39</f>
-        <v>0.55277046193536505</v>
+        <v>0.83807244667788394</v>
       </c>
       <c r="Y5" s="209">
         <f>Overall_Draft!P39</f>
@@ -26198,11 +26259,11 @@
       </c>
       <c r="AE5" s="209">
         <f>Overall_Draft!V39</f>
-        <v>0.251112</v>
+        <v>0.19523809523809524</v>
       </c>
       <c r="AF5" s="210">
         <f>Overall_Draft!W39</f>
-        <v>0.35873142857142859</v>
+        <v>0.27891156462585037</v>
       </c>
       <c r="AG5" s="209">
         <f>Overall_Draft!X39</f>
@@ -26230,11 +26291,11 @@
       </c>
       <c r="AM5" s="209">
         <f>Overall_Draft!AD39</f>
-        <v>0.24822390476190476</v>
+        <v>1.9486154285714288</v>
       </c>
       <c r="AN5" s="210">
         <f>Overall_Draft!AE39</f>
-        <v>8.3859427284427288E-2</v>
+        <v>0.65831602316602322</v>
       </c>
       <c r="AO5" s="209">
         <f>Overall_Draft!AF39</f>
@@ -26246,11 +26307,11 @@
       </c>
       <c r="AQ5" s="209">
         <f>Overall_Draft!AH39</f>
-        <v>0.62946580952380948</v>
+        <v>1.0580372380952381</v>
       </c>
       <c r="AR5" s="210">
         <f>Overall_Draft!AI39</f>
-        <v>0.47686803751803747</v>
+        <v>0.8015433621933622</v>
       </c>
       <c r="AS5" s="211">
         <f>Overall_Draft!AJ39</f>
@@ -26267,11 +26328,11 @@
       </c>
       <c r="AX5" s="209">
         <f>Overall!U23</f>
-        <v>2.8716789761904766</v>
+        <v>3.4387666428571433</v>
       </c>
       <c r="AY5" s="210">
         <f>Overall!V23</f>
-        <v>0.71565110678046417</v>
+        <v>0.85697502204272225</v>
       </c>
       <c r="AZ5" s="209">
         <f>Overall!W23</f>
@@ -26282,7 +26343,7 @@
         <v>2.6801299999998918E-3</v>
       </c>
     </row>
-    <row r="6" spans="2:53" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:53" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="220" t="str">
         <f>Overall_Draft!L24</f>
         <v>RAGHAV 
@@ -26294,11 +26355,11 @@
       </c>
       <c r="D6" s="221">
         <f>Overall_Draft!N24</f>
-        <v>3.6017421952380952</v>
+        <v>6.5512638047619038</v>
       </c>
       <c r="E6" s="222">
         <f t="shared" si="0"/>
-        <v>0.34282066162956709</v>
+        <v>0.62356172938408871</v>
       </c>
       <c r="F6" s="221">
         <f>Overall_Draft!P24</f>
@@ -26306,7 +26367,7 @@
       </c>
       <c r="G6" s="221">
         <f>Overall_Draft!Q24</f>
-        <v>5.7182578047619046</v>
+        <v>2.7687361952380964</v>
       </c>
       <c r="H6" s="123" t="str">
         <f>Overall_Draft!L8</f>
@@ -26314,15 +26375,15 @@
       </c>
       <c r="I6" s="123">
         <f>Overall_Draft!M8</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J6" s="209">
-        <f ca="1">Overall_Draft!N8</f>
+        <f>Overall_Draft!N8</f>
         <v>0</v>
       </c>
       <c r="K6" s="209">
         <f>Overall_Draft!O8</f>
-        <v>3.8064526714285707</v>
+        <v>7.3371716142857135</v>
       </c>
       <c r="L6" s="123">
         <f>Overall_Draft!P8</f>
@@ -26330,23 +26391,23 @@
       </c>
       <c r="M6" s="209">
         <f>Overall_Draft!Q8</f>
-        <v>34.304362699999999</v>
+        <v>33.5674992</v>
       </c>
       <c r="N6" s="209">
         <f>Overall_Draft!R8</f>
-        <v>28.990686871428569</v>
+        <v>31.888382104761909</v>
       </c>
       <c r="O6" s="209">
         <f>Overall_Draft!S8</f>
-        <v>6.2245148047619034</v>
+        <v>3.282729719047619</v>
       </c>
       <c r="P6" s="123">
         <f>Overall_Draft!T8</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q6" s="123">
-        <f ca="1">Overall_Draft!U8</f>
-        <v>5</v>
+        <f>Overall_Draft!U8</f>
+        <v>7</v>
       </c>
       <c r="R6" s="123">
         <f>Overall_Draft!V8</f>
@@ -26368,11 +26429,11 @@
       </c>
       <c r="W6" s="209">
         <f>Overall_Draft!N40</f>
-        <v>1.4609841952380953</v>
+        <v>0.6769339380952375</v>
       </c>
       <c r="X6" s="210">
         <f>Overall_Draft!O40</f>
-        <v>0.60598843973837913</v>
+        <v>0.28077931458076949</v>
       </c>
       <c r="Y6" s="209">
         <f>Overall_Draft!P40</f>
@@ -26384,11 +26445,11 @@
       </c>
       <c r="AA6" s="209">
         <f>Overall_Draft!R40</f>
-        <v>0.20471047619047619</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="210">
         <f>Overall_Draft!S40</f>
-        <v>0.39367399267399267</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="209">
         <f>Overall_Draft!T40</f>
@@ -26400,11 +26461,11 @@
       </c>
       <c r="AE6" s="209">
         <f>Overall_Draft!V40</f>
-        <v>0</v>
+        <v>1.4285714285714284E-2</v>
       </c>
       <c r="AF6" s="210">
         <f>Overall_Draft!W40</f>
-        <v>0</v>
+        <v>7.9365079365079361E-2</v>
       </c>
       <c r="AG6" s="209">
         <f>Overall_Draft!X40</f>
@@ -26416,11 +26477,11 @@
       </c>
       <c r="AI6" s="209">
         <f>Overall_Draft!Z40</f>
-        <v>1.0194376190476191</v>
+        <v>1.5744300857142859</v>
       </c>
       <c r="AJ6" s="210">
         <f>Overall_Draft!AA40</f>
-        <v>0.59432435879590562</v>
+        <v>0.91788073510108226</v>
       </c>
       <c r="AK6" s="209">
         <f>Overall_Draft!AB40</f>
@@ -26432,11 +26493,11 @@
       </c>
       <c r="AM6" s="209">
         <f>Overall_Draft!AD40</f>
-        <v>0.30264676190476192</v>
+        <v>0.31099816190476187</v>
       </c>
       <c r="AN6" s="210">
         <f>Overall_Draft!AE40</f>
-        <v>0.14982512965582273</v>
+        <v>0.15395948609146629</v>
       </c>
       <c r="AO6" s="209">
         <f>Overall_Draft!AF40</f>
@@ -26448,11 +26509,11 @@
       </c>
       <c r="AQ6" s="209">
         <f>Overall_Draft!AH40</f>
-        <v>0.81867361904761904</v>
+        <v>3.9889016190476192</v>
       </c>
       <c r="AR6" s="210">
         <f>Overall_Draft!AI40</f>
-        <v>0.18776917868064655</v>
+        <v>0.91488569244211437</v>
       </c>
       <c r="AS6" s="211">
         <f>Overall_Draft!AJ40</f>
@@ -26469,11 +26530,11 @@
       </c>
       <c r="AX6" s="209">
         <f>Overall!U24</f>
-        <v>0.55087066666666673</v>
+        <v>2.8792148761904763</v>
       </c>
       <c r="AY6" s="210">
         <f>Overall!V24</f>
-        <v>5.9682629107981222E-2</v>
+        <v>0.31194093999896816</v>
       </c>
       <c r="AZ6" s="209">
         <f>Overall!W24</f>
@@ -26484,7 +26545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:53" ht="68.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:53" ht="68.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="220" t="str">
         <f>Overall_Draft!L25</f>
         <v>RAGHAV 
@@ -26516,15 +26577,15 @@
       </c>
       <c r="I7" s="123">
         <f>Overall_Draft!M9</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J7" s="209">
-        <f ca="1">Overall_Draft!N9</f>
+        <f>Overall_Draft!N9</f>
         <v>0</v>
       </c>
       <c r="K7" s="209">
         <f>Overall_Draft!O9</f>
-        <v>0.95730709999999997</v>
+        <v>1.2688853</v>
       </c>
       <c r="L7" s="123">
         <f>Overall_Draft!P9</f>
@@ -26536,19 +26597,19 @@
       </c>
       <c r="N7" s="209">
         <f>Overall_Draft!R9</f>
-        <v>2.5436453000000001</v>
+        <v>2.8052234999999999</v>
       </c>
       <c r="O7" s="209">
         <f>Overall_Draft!S9</f>
-        <v>2.9440563000000002</v>
+        <v>2.6824781</v>
       </c>
       <c r="P7" s="123">
         <f>Overall_Draft!T9</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q7" s="123">
-        <f ca="1">Overall_Draft!U9</f>
-        <v>7</v>
+        <f>Overall_Draft!U9</f>
+        <v>10</v>
       </c>
       <c r="R7" s="123">
         <f>Overall_Draft!V9</f>
@@ -26586,11 +26647,11 @@
       </c>
       <c r="AA7" s="209">
         <f>Overall_Draft!R41</f>
-        <v>0.79708190000000001</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="210">
         <f>Overall_Draft!S41</f>
-        <v>1.4070870712047066</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="209">
         <f>Overall_Draft!T41</f>
@@ -26671,11 +26732,11 @@
       </c>
       <c r="AX7" s="213">
         <f>Overall!U25</f>
-        <v>2.1603028571428569</v>
+        <v>8.0735856190476198</v>
       </c>
       <c r="AY7" s="214">
         <f>Overall!V25</f>
-        <v>0.25626368412133532</v>
+        <v>0.95772071400327641</v>
       </c>
       <c r="AZ7" s="213">
         <f>Overall!W25</f>
@@ -26686,7 +26747,7 @@
         <v>0.86999999999999922</v>
       </c>
     </row>
-    <row r="8" spans="2:53" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:53" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="220" t="str">
         <f>Overall_Draft!L26</f>
         <v>RAGHAV 
@@ -26698,11 +26759,11 @@
       </c>
       <c r="D8" s="221">
         <f>Overall_Draft!N26</f>
-        <v>0.8671123523809523</v>
+        <v>3.5271965238095242</v>
       </c>
       <c r="E8" s="222">
         <f t="shared" si="0"/>
-        <v>0.18102554329456211</v>
+        <v>0.73636670643205115</v>
       </c>
       <c r="F8" s="221">
         <f>Overall_Draft!P26</f>
@@ -26710,7 +26771,7 @@
       </c>
       <c r="G8" s="221">
         <f>Overall_Draft!Q26</f>
-        <v>3.6828876476190473</v>
+        <v>1.0228034761904756</v>
       </c>
       <c r="H8" s="123" t="str">
         <f>Overall_Draft!L10</f>
@@ -26721,12 +26782,12 @@
         <v>25</v>
       </c>
       <c r="J8" s="209">
-        <f ca="1">Overall_Draft!N10</f>
+        <f>Overall_Draft!N10</f>
         <v>0</v>
       </c>
       <c r="K8" s="209">
         <f>Overall_Draft!O10</f>
-        <v>1.2641908285714285</v>
+        <v>3.92332261904762</v>
       </c>
       <c r="L8" s="123">
         <f>Overall_Draft!P10</f>
@@ -26738,18 +26799,18 @@
       </c>
       <c r="N8" s="209">
         <f>Overall_Draft!R10</f>
-        <v>19.54784562857143</v>
+        <v>22.224215519047622</v>
       </c>
       <c r="O8" s="209">
         <f>Overall_Draft!S10</f>
-        <v>4.8549033190476196</v>
+        <v>2.1785335666666672</v>
       </c>
       <c r="P8" s="123">
         <f>Overall_Draft!T10</f>
         <v>3</v>
       </c>
       <c r="Q8" s="123">
-        <f ca="1">Overall_Draft!U10</f>
+        <f>Overall_Draft!U10</f>
         <v>1</v>
       </c>
       <c r="R8" s="123">
@@ -26772,11 +26833,11 @@
       </c>
       <c r="W8" s="209">
         <f>Overall_Draft!N42</f>
-        <v>0.15494892380952385</v>
+        <v>0.60045633333333326</v>
       </c>
       <c r="X8" s="210">
         <f>Overall_Draft!O42</f>
-        <v>0.1006161842918986</v>
+        <v>0.3899067099567099</v>
       </c>
       <c r="Y8" s="209">
         <f>Overall_Draft!P42</f>
@@ -26788,11 +26849,11 @@
       </c>
       <c r="AA8" s="209">
         <f>Overall_Draft!R42</f>
-        <v>4.7619047619047623E-2</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="210">
         <f>Overall_Draft!S42</f>
-        <v>0.25062656641604014</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="209">
         <f>Overall_Draft!T42</f>
@@ -26804,11 +26865,11 @@
       </c>
       <c r="AE8" s="209">
         <f>Overall_Draft!V42</f>
-        <v>0.34945942857142859</v>
+        <v>0.34850704761904766</v>
       </c>
       <c r="AF8" s="210">
         <f>Overall_Draft!W42</f>
-        <v>1.7472971428571429</v>
+        <v>1.7425352380952381</v>
       </c>
       <c r="AG8" s="209">
         <f>Overall_Draft!X42</f>
@@ -26852,18 +26913,18 @@
       </c>
       <c r="AQ8" s="209">
         <f>Overall_Draft!AH42</f>
-        <v>0.71216342857142856</v>
+        <v>2.9267401904761905</v>
       </c>
       <c r="AR8" s="210">
         <f>Overall_Draft!AI42</f>
-        <v>0.35787106963388371</v>
+        <v>1.470723713807131</v>
       </c>
       <c r="AS8" s="211">
         <f>Overall_Draft!AJ42</f>
         <v>1.99</v>
       </c>
     </row>
-    <row r="9" spans="2:53" ht="47.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:53" ht="47.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="223" t="str">
         <f>Overall_Draft!L27</f>
         <v>Overall</v>
@@ -26874,11 +26935,11 @@
       </c>
       <c r="D9" s="224">
         <f>Overall_Draft!N27</f>
-        <v>12.211792419047619</v>
+        <v>23.731437028571431</v>
       </c>
       <c r="E9" s="225">
         <f t="shared" si="0"/>
-        <v>0.31537351062219876</v>
+        <v>0.61287207896987006</v>
       </c>
       <c r="F9" s="224">
         <f>Overall_Draft!P27</f>
@@ -26886,7 +26947,7 @@
       </c>
       <c r="G9" s="224">
         <f>Overall_Draft!Q27</f>
-        <v>20.298207580952379</v>
+        <v>8.7785629714285669</v>
       </c>
       <c r="H9" s="226" t="str">
         <f>Overall_Draft!L11</f>
@@ -26894,39 +26955,39 @@
       </c>
       <c r="I9" s="226">
         <f>Overall_Draft!M11</f>
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J9" s="213">
-        <f ca="1">Overall_Draft!N11</f>
+        <f>Overall_Draft!N11</f>
         <v>0</v>
       </c>
       <c r="K9" s="213">
         <f>Overall_Draft!O11</f>
-        <v>14.762993866666665</v>
+        <v>27.529172719047626</v>
       </c>
       <c r="L9" s="226">
         <f>Overall_Draft!P11</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M9" s="213">
         <f>Overall_Draft!Q11</f>
-        <v>460.49450673000007</v>
+        <v>462.85943150000008</v>
       </c>
       <c r="N9" s="213">
         <f>Overall_Draft!R11</f>
-        <v>443.53780437619048</v>
+        <v>456.67245450952379</v>
       </c>
       <c r="O9" s="213">
         <f>Overall_Draft!S11</f>
-        <v>22.537933758571427</v>
+        <v>15.68149889047619</v>
       </c>
       <c r="P9" s="226">
         <f>Overall_Draft!T11</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q9" s="226">
-        <f ca="1">Overall_Draft!U11</f>
-        <v>26</v>
+        <f>Overall_Draft!U11</f>
+        <v>32</v>
       </c>
       <c r="R9" s="226">
         <f>Overall_Draft!V11</f>
@@ -26947,11 +27008,11 @@
       </c>
       <c r="W9" s="213">
         <f>Overall_Draft!N43</f>
-        <v>6.6289399190476193</v>
+        <v>9.3398698904761908</v>
       </c>
       <c r="X9" s="214">
         <f>Overall_Draft!O43</f>
-        <v>0.39273296083919096</v>
+        <v>0.55334258580314866</v>
       </c>
       <c r="Y9" s="213">
         <f>Overall_Draft!P43</f>
@@ -26963,11 +27024,11 @@
       </c>
       <c r="AA9" s="213">
         <f>Overall_Draft!R43</f>
-        <v>1.4211175190476191</v>
+        <v>0.41932514285714284</v>
       </c>
       <c r="AB9" s="214">
         <f>Overall_Draft!S43</f>
-        <v>0.70537744477210818</v>
+        <v>0.20813373548128042</v>
       </c>
       <c r="AC9" s="213">
         <f>Overall_Draft!T43</f>
@@ -26979,11 +27040,11 @@
       </c>
       <c r="AE9" s="213">
         <f>Overall_Draft!V43</f>
-        <v>0.94651043809523805</v>
+        <v>1.2693831047619049</v>
       </c>
       <c r="AF9" s="214">
         <f>Overall_Draft!W43</f>
-        <v>0.45505309523809517</v>
+        <v>0.61028033882783883</v>
       </c>
       <c r="AG9" s="213">
         <f>Overall_Draft!X43</f>
@@ -26995,11 +27056,11 @@
       </c>
       <c r="AI9" s="213">
         <f>Overall_Draft!Z43</f>
-        <v>2.8716789761904766</v>
+        <v>3.4387666428571433</v>
       </c>
       <c r="AJ9" s="214">
         <f>Overall_Draft!AA43</f>
-        <v>0.71565110678046417</v>
+        <v>0.85697502204272225</v>
       </c>
       <c r="AK9" s="213">
         <f>Overall_Draft!AB43</f>
@@ -27011,11 +27072,11 @@
       </c>
       <c r="AM9" s="213">
         <f>Overall_Draft!AD43</f>
-        <v>0.55087066666666673</v>
+        <v>2.8792148761904763</v>
       </c>
       <c r="AN9" s="214">
         <f>Overall_Draft!AE43</f>
-        <v>5.9682629107981222E-2</v>
+        <v>0.31194093999896816</v>
       </c>
       <c r="AO9" s="213">
         <f>Overall_Draft!AF43</f>
@@ -27027,20 +27088,20 @@
       </c>
       <c r="AQ9" s="213">
         <f>Overall_Draft!AH43</f>
-        <v>2.1603028571428569</v>
+        <v>8.0735856190476198</v>
       </c>
       <c r="AR9" s="214">
         <f>Overall_Draft!AI43</f>
-        <v>0.25119800664451825</v>
+        <v>0.93878902547065346</v>
       </c>
       <c r="AS9" s="215">
         <f>Overall_Draft!AJ43</f>
         <v>7.5600000000000005</v>
       </c>
     </row>
-    <row r="10" spans="2:53" ht="47.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="2:53" ht="47.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="2:53" ht="47.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="2:53" ht="47.4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="2:53" ht="47.4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="2:53" ht="47.4" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -27224,15 +27285,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="720fc211-b8f9-4216-8e59-f92e385e0bb9">
@@ -27256,6 +27308,15 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD55F499-65CE-441F-9D64-BBB026E75EFE}">
   <ds:schemaRefs>
@@ -27276,26 +27337,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{850BD086-9051-4567-AFD1-B7C8873D4F2D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="720fc211-b8f9-4216-8e59-f92e385e0bb9"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="1c221b64-27b2-4021-9af7-79dcbf083a1e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{037A7D67-D63F-48F5-85CA-5FAB13DF5982}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{850BD086-9051-4567-AFD1-B7C8873D4F2D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="720fc211-b8f9-4216-8e59-f92e385e0bb9"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="1c221b64-27b2-4021-9af7-79dcbf083a1e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>